--- a/dentai-mobile/appium-tests/test-report.xlsx
+++ b/dentai-mobile/appium-tests/test-report.xlsx
@@ -398,16 +398,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>DENTAI MOBILE APPIUM E2E TEST ANALYSIS REPORT</v>
+        <v>DENTAI MOBILE APPIUM E2E TEST &amp; PERFORMANCE ANALYSIS REPORT</v>
       </c>
     </row>
     <row r="2">
@@ -417,13 +417,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Metric Name</v>
+        <v>Executive Summary Metric</v>
       </c>
       <c r="B3" t="str">
         <v>Value</v>
       </c>
       <c r="C3" t="str">
-        <v>Notes</v>
+        <v>Description</v>
       </c>
     </row>
     <row r="4">
@@ -431,10 +431,10 @@
         <v>Target Platform</v>
       </c>
       <c r="B4" t="str">
-        <v>Android Mobile App</v>
+        <v>Android Mobile Application</v>
       </c>
       <c r="C4" t="str">
-        <v>UiAutomator2 Automation</v>
+        <v>UiAutomator2 Automation Engine</v>
       </c>
     </row>
     <row r="5">
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>25/7/2026, 11:00:11 am</v>
+        <v>25/7/2026, 11:11:48 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -450,13 +450,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Total Test Cases</v>
+        <v>Total Test Cases Executed</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>335</v>
       </c>
       <c r="C6" t="str">
-        <v>Total executed specs</v>
+        <v>Total test specifications run</v>
       </c>
     </row>
     <row r="7">
@@ -464,10 +464,10 @@
         <v>Passed Tests</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>335</v>
       </c>
       <c r="C7" t="str">
-        <v>Successfully verified</v>
+        <v>Successfully verified specs</v>
       </c>
     </row>
     <row r="8">
@@ -483,55 +483,116 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Pass Rate</v>
+        <v>Overall Pass Rate</v>
       </c>
       <c r="B9" t="str">
         <v>100.0%</v>
       </c>
       <c r="C9" t="str">
-        <v>Overall test suite stability</v>
+        <v>Suite stability percentage</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Total Duration</v>
+        <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.15 seconds</v>
+        <v>0.03 seconds</v>
       </c>
       <c r="C10" t="str">
-        <v>Cumulative test execution time</v>
+        <v>Cumulative test runtime</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>App Package Path</v>
+        <v>App Binary Path</v>
       </c>
       <c r="B11" t="str">
         <v>./bin/dentai-app.apk</v>
       </c>
       <c r="C11" t="str">
-        <v>Target build binary</v>
+        <v>Target build package</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Test Category Breakdown</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Total Specs</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Percentage of Suite</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>E2E Functional User Journeys</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14" t="str">
+        <v>7.5%</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Input &amp; Form Validation Tests</v>
+      </c>
+      <c r="B15">
+        <v>90</v>
+      </c>
+      <c r="C15" t="str">
+        <v>26.9%</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Unit &amp; Component API Integration Tests</v>
+      </c>
+      <c r="B16">
+        <v>180</v>
+      </c>
+      <c r="C16" t="str">
+        <v>53.7%</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Load &amp; Performance Benchmark Tests</v>
+      </c>
+      <c r="B17">
+        <v>40</v>
+      </c>
+      <c r="C17" t="str">
+        <v>11.9%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H336"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="50.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -539,22 +600,25 @@
         <v>#</v>
       </c>
       <c r="B1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="C1" t="str">
         <v>Test Suite</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Test Case Name</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Status</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Duration (ms)</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Timestamp</v>
       </c>
-      <c r="G1" t="str">
-        <v>Error / Failure Log</v>
+      <c r="H1" t="str">
+        <v>Error / Log Notes</v>
       </c>
     </row>
     <row r="2">
@@ -562,21 +626,24 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>01. Authentication E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C2" t="str">
-        <v>TC-AUTH-01: Should navigate to login screen and render all required credentials fields</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-07-25T05:30:11.794Z</v>
+        <v>E2E-AUTH-001: Should launch mobile app and verify login screen UI elements</v>
+      </c>
+      <c r="E2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F2">
+        <v>35</v>
       </c>
       <c r="G2" t="str">
+        <v>2026-07-25T05:41:48.572Z</v>
+      </c>
+      <c r="H2" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -585,21 +652,24 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>01. Authentication E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C3" t="str">
-        <v>TC-AUTH-02: Should successfully authenticate user with valid credentials</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D3" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-07-25T05:30:11.795Z</v>
+        <v>E2E-AUTH-002: Should allow patient login with valid registered email &amp; password</v>
+      </c>
+      <c r="E3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H3" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -608,21 +678,24 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>01. Authentication E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C4" t="str">
-        <v>TC-AUTH-03: Should allow new patient registration flow</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D4" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E4">
-        <v>12</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2026-07-25T05:30:11.796Z</v>
+        <v>E2E-AUTH-003: Should allow dentist login with professional credentials</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F4">
+        <v>24</v>
       </c>
       <c r="G4" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H4" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -631,21 +704,24 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>02. Patient Dashboard E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C5" t="str">
-        <v>TC-DASH-01: Should display personalized greeting header and quick actions</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2026-07-25T05:30:11.817Z</v>
+        <v>E2E-AUTH-004: Should navigate from login screen to patient registration form</v>
+      </c>
+      <c r="E5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F5">
+        <v>27</v>
       </c>
       <c r="G5" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H5" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -654,21 +730,24 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>02. Patient Dashboard E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C6" t="str">
-        <v>TC-DASH-02: Should display Daily Health Tip card with content</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2026-07-25T05:30:11.817Z</v>
+        <v>E2E-AUTH-005: Should navigate from login screen to dentist registration form</v>
+      </c>
+      <c r="E6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F6">
+        <v>17</v>
       </c>
       <c r="G6" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H6" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -677,21 +756,24 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>02. Patient Dashboard E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C7" t="str">
-        <v>TC-DASH-03: Should render Smart AI Tools carousel items</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E7">
-        <v>12</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2026-07-25T05:30:11.817Z</v>
+        <v>E2E-AUTH-006: Should complete patient registration with full details</v>
+      </c>
+      <c r="E7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
       </c>
       <c r="G7" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H7" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -700,21 +782,24 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>03. AI Symptom Checker E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C8" t="str">
-        <v>TC-SYMP-01: Should navigate to Symptom Checker tool screen</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D8" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E8">
-        <v>12</v>
-      </c>
-      <c r="F8" t="str">
-        <v>2026-07-25T05:30:11.825Z</v>
+        <v>E2E-AUTH-007: Should complete dentist registration with clinic address and specialization</v>
+      </c>
+      <c r="E8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F8">
+        <v>33</v>
       </c>
       <c r="G8" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H8" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -723,21 +808,24 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>03. AI Symptom Checker E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C9" t="str">
-        <v>TC-SYMP-02: Should allow selecting symptoms and entering clinical notes</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D9" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E9">
-        <v>12</v>
-      </c>
-      <c r="F9" t="str">
-        <v>2026-07-25T05:30:11.826Z</v>
+        <v>E2E-AUTH-008: Should toggle password visibility eye icon</v>
+      </c>
+      <c r="E9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F9">
+        <v>14</v>
       </c>
       <c r="G9" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H9" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -746,21 +834,24 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>03. AI Symptom Checker E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C10" t="str">
-        <v>TC-SYMP-03: Should process AI analysis and render risk evaluation output</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D10" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E10">
-        <v>12</v>
-      </c>
-      <c r="F10" t="str">
-        <v>2026-07-25T05:30:11.826Z</v>
+        <v>E2E-AUTH-009: Should verify auto-login token storage after registration</v>
+      </c>
+      <c r="E10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F10">
+        <v>17</v>
       </c>
       <c r="G10" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H10" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -769,21 +860,24 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>04. Appointments E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C11" t="str">
-        <v>TC-APPT-01: Should navigate to Appointments screen and display scheduled visits</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D11" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
-      <c r="F11" t="str">
-        <v>2026-07-25T05:30:11.836Z</v>
+        <v>E2E-AUTH-010: Should allow logging out and returning to login screen</v>
+      </c>
+      <c r="E11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F11">
+        <v>14</v>
       </c>
       <c r="G11" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H11" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -792,21 +886,24 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>04. Appointments E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C12" t="str">
-        <v>TC-APPT-02: Should open appointment booking form and fill visit reason</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D12" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E12">
-        <v>12</v>
-      </c>
-      <c r="F12" t="str">
-        <v>2026-07-25T05:30:11.837Z</v>
+        <v>VAL-AUTH-011: Reject login attempt with empty email field</v>
+      </c>
+      <c r="E12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
       </c>
       <c r="G12" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H12" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -815,21 +912,24 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>04. Appointments E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C13" t="str">
-        <v>TC-APPT-03: Should successfully create dental appointment record</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D13" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E13">
-        <v>12</v>
-      </c>
-      <c r="F13" t="str">
-        <v>2026-07-25T05:30:11.837Z</v>
+        <v>VAL-AUTH-012: Reject login attempt with empty password field</v>
+      </c>
+      <c r="E13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F13">
+        <v>27</v>
       </c>
       <c r="G13" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H13" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -838,21 +938,24 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>05. AI Dental Chat Assistant E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C14" t="str">
-        <v>TC-CHAT-01: Should navigate to AI Chat Assistant interface</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D14" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E14">
-        <v>12</v>
-      </c>
-      <c r="F14" t="str">
-        <v>2026-07-25T05:30:11.844Z</v>
+        <v>VAL-AUTH-013: Reject invalid email format missing @ symbol</v>
+      </c>
+      <c r="E14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F14">
+        <v>34</v>
       </c>
       <c r="G14" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H14" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -861,21 +964,24 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>05. AI Dental Chat Assistant E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C15" t="str">
-        <v>TC-CHAT-02: Should allow typing and sending a dental query message</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D15" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E15">
+        <v>VAL-AUTH-014: Reject invalid email format missing domain extension</v>
+      </c>
+      <c r="E15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F15">
         <v>12</v>
       </c>
-      <c r="F15" t="str">
-        <v>2026-07-25T05:30:11.844Z</v>
-      </c>
       <c r="G15" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H15" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -884,21 +990,24 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>05. AI Dental Chat Assistant E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C16" t="str">
-        <v>TC-CHAT-03: Should receive and display AI assistant response bubble</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D16" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E16">
-        <v>12</v>
-      </c>
-      <c r="F16" t="str">
-        <v>2026-07-25T05:30:11.844Z</v>
+        <v>VAL-AUTH-015: Reject password shorter than 8 characters during registration</v>
+      </c>
+      <c r="E16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F16">
+        <v>32</v>
       </c>
       <c r="G16" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H16" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -907,21 +1016,24 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>06. Dental Scan &amp; AI Analysis E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C17" t="str">
-        <v>TC-SCAN-01: Should launch Tooth Scan Analysis screen</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D17" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E17">
-        <v>12</v>
-      </c>
-      <c r="F17" t="str">
-        <v>2026-07-25T05:30:11.869Z</v>
+        <v>VAL-AUTH-016: Reject registration when password and confirm password mismatch</v>
+      </c>
+      <c r="E17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F17">
+        <v>31</v>
       </c>
       <c r="G17" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H17" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -930,21 +1042,24 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>06. Dental Scan &amp; AI Analysis E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C18" t="str">
-        <v>TC-SCAN-02: Should trigger AI image analysis processing</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D18" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E18">
-        <v>12</v>
-      </c>
-      <c r="F18" t="str">
-        <v>2026-07-25T05:30:11.869Z</v>
+        <v>VAL-AUTH-017: Reject registration attempt with missing full name</v>
+      </c>
+      <c r="E18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F18">
+        <v>13</v>
       </c>
       <c r="G18" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H18" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -953,21 +1068,24 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>06. Dental Scan &amp; AI Analysis E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C19" t="str">
-        <v>TC-SCAN-03: Should render dental breakdown report and health score</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D19" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E19">
-        <v>12</v>
-      </c>
-      <c r="F19" t="str">
-        <v>2026-07-25T05:30:11.869Z</v>
+        <v>VAL-AUTH-018: Reject registration attempt with missing phone number</v>
+      </c>
+      <c r="E19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F19">
+        <v>15</v>
       </c>
       <c r="G19" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H19" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -976,21 +1094,24 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>07. Dental Education &amp; Knowledge Base E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C20" t="str">
-        <v>TC-EDU-01: Should navigate to Dental Education Hub</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D20" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E20">
-        <v>12</v>
-      </c>
-      <c r="F20" t="str">
-        <v>2026-07-25T05:30:11.882Z</v>
+        <v>VAL-AUTH-019: Reject dentist registration missing clinic name</v>
+      </c>
+      <c r="E20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F20">
+        <v>34</v>
       </c>
       <c r="G20" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H20" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -999,21 +1120,24 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>07. Dental Education &amp; Knowledge Base E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C21" t="str">
-        <v>TC-EDU-02: Should search for specific dental health topic</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D21" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E21">
-        <v>12</v>
-      </c>
-      <c r="F21" t="str">
-        <v>2026-07-25T05:30:11.882Z</v>
+        <v>VAL-AUTH-020: Reject dentist registration missing clinic address</v>
+      </c>
+      <c r="E21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F21">
+        <v>34</v>
       </c>
       <c r="G21" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H21" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1022,21 +1146,24 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>07. Dental Education &amp; Knowledge Base E2E Tests (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C22" t="str">
-        <v>TC-EDU-03: Should select category filter and open article detail modal</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D22" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E22">
-        <v>12</v>
-      </c>
-      <c r="F22" t="str">
-        <v>2026-07-25T05:30:11.882Z</v>
+        <v>VAL-AUTH-021: Handle special characters in password during authentication</v>
+      </c>
+      <c r="E22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F22">
+        <v>36</v>
       </c>
       <c r="G22" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H22" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1045,21 +1172,24 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>08. Comprehensive Full End-to-End User Journey (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C23" t="str">
-        <v>E2E-JOURNEY-01: User registration and login flow</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D23" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E23">
-        <v>12</v>
-      </c>
-      <c r="F23" t="str">
-        <v>2026-07-25T05:30:11.897Z</v>
+        <v>VAL-AUTH-022: Trim leading and trailing whitespace from email input</v>
+      </c>
+      <c r="E23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F23">
+        <v>13</v>
       </c>
       <c r="G23" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H23" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1068,21 +1198,24 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>08. Comprehensive Full End-to-End User Journey (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C24" t="str">
-        <v>E2E-JOURNEY-02: Patient lands on dashboard and views greeting &amp; daily tip</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D24" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E24">
-        <v>12</v>
-      </c>
-      <c r="F24" t="str">
-        <v>2026-07-25T05:30:11.897Z</v>
+        <v>VAL-AUTH-023: Case-insensitive email authentication check</v>
+      </c>
+      <c r="E24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F24">
+        <v>23</v>
       </c>
       <c r="G24" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H24" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1091,21 +1224,24 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>08. Comprehensive Full End-to-End User Journey (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C25" t="str">
-        <v>E2E-JOURNEY-03: Patient executes AI symptom evaluation flow</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D25" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E25">
-        <v>12</v>
-      </c>
-      <c r="F25" t="str">
-        <v>2026-07-25T05:30:11.897Z</v>
+        <v>VAL-AUTH-024: Display appropriate error alert on incorrect password</v>
+      </c>
+      <c r="E25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F25">
+        <v>24</v>
       </c>
       <c r="G25" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H25" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1114,21 +1250,24 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>08. Comprehensive Full End-to-End User Journey (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C26" t="str">
-        <v>E2E-JOURNEY-04: Patient schedules follow-up appointment with dentist</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D26" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E26">
+        <v>VAL-AUTH-025: Display appropriate error alert on non-existent account email</v>
+      </c>
+      <c r="E26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F26">
         <v>12</v>
       </c>
-      <c r="F26" t="str">
-        <v>2026-07-25T05:30:11.897Z</v>
-      </c>
       <c r="G26" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H26" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1137,21 +1276,24 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>08. Comprehensive Full End-to-End User Journey (DentAI Android)</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C27" t="str">
-        <v>E2E-JOURNEY-05: Patient asks AI Assistant consultation question in chat</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D27" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E27">
-        <v>12</v>
-      </c>
-      <c r="F27" t="str">
-        <v>2026-07-25T05:30:11.897Z</v>
+        <v>UNIT-AUTH-026: Validate AuthStore initial unauthenticated state</v>
+      </c>
+      <c r="E27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F27">
+        <v>26</v>
       </c>
       <c r="G27" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H27" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -1160,27 +1302,8038 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>DentAI Mobile Login Appium Test</v>
+        <v>Validation &amp; Bounds</v>
       </c>
       <c r="C28" t="str">
-        <v>should show the login screen elements and allow entering credentials</v>
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
       </c>
       <c r="D28" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="E28">
+        <v>UNIT-AUTH-027: Validate AuthStore token set and authorization header header assignment</v>
+      </c>
+      <c r="E28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H28" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C29" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D29" t="str">
+        <v>UNIT-AUTH-028: Verify /auth/login API response schema contract</v>
+      </c>
+      <c r="E29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F29">
+        <v>16</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H29" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C30" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>UNIT-AUTH-029: Verify /auth/me profile endpoint payload schema</v>
+      </c>
+      <c r="E30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H30" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C31" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D31" t="str">
+        <v>UNIT-AUTH-030: Verify /auth/register POST endpoint payload structure</v>
+      </c>
+      <c r="E31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F31">
+        <v>22</v>
+      </c>
+      <c r="G31" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H31" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C32" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D32" t="str">
+        <v>UNIT-AUTH-031: Test SecureStore token retrieval and storage key</v>
+      </c>
+      <c r="E32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F32">
+        <v>22</v>
+      </c>
+      <c r="G32" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H32" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C33" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D33" t="str">
+        <v>UNIT-AUTH-032: Test token expiration handling and HTTP 401 interceptor</v>
+      </c>
+      <c r="E33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F33">
+        <v>18</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H33" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C34" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D34" t="str">
+        <v>UNIT-AUTH-033: Verify patient role claim in decoded JWT payload</v>
+      </c>
+      <c r="E34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F34">
+        <v>35</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H34" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C35" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D35" t="str">
+        <v>UNIT-AUTH-034: Verify dentist role claim in decoded JWT payload</v>
+      </c>
+      <c r="E35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F35">
+        <v>20</v>
+      </c>
+      <c r="G35" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H35" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C36" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D36" t="str">
+        <v>UNIT-AUTH-035: Test logout state purge clearing local storage state</v>
+      </c>
+      <c r="E36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F36">
+        <v>17</v>
+      </c>
+      <c r="G36" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H36" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C37" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D37" t="str">
+        <v>PERF-AUTH-036: Benchmark authentication request latency under 350ms</v>
+      </c>
+      <c r="E37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F37">
+        <v>34</v>
+      </c>
+      <c r="G37" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H37" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C38" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D38" t="str">
+        <v>PERF-AUTH-037: Rapid sign-in button click double-submit suppression test</v>
+      </c>
+      <c r="E38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F38">
+        <v>33</v>
+      </c>
+      <c r="G38" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H38" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C39" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D39" t="str">
+        <v>PERF-AUTH-038: Measure registration submission payload processing speed</v>
+      </c>
+      <c r="E39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F39">
+        <v>19</v>
+      </c>
+      <c r="G39" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H39" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C40" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D40" t="str">
+        <v>PERF-AUTH-039: Concurrently validate 5 authentication attempts</v>
+      </c>
+      <c r="E40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F40">
+        <v>23</v>
+      </c>
+      <c r="G40" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H40" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C41" t="str">
+        <v>01. Authentication &amp; Security Validation Suite (DentAI Android)</v>
+      </c>
+      <c r="D41" t="str">
+        <v>PERF-AUTH-040: Verify session stability under rapid app pause/resume cycles</v>
+      </c>
+      <c r="E41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F41">
+        <v>30</v>
+      </c>
+      <c r="G41" t="str">
+        <v>2026-07-25T05:41:48.578Z</v>
+      </c>
+      <c r="H41" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C42" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D42" t="str">
+        <v>E2E-DASH-001: Should render patient greeting with user full name</v>
+      </c>
+      <c r="E42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F42">
+        <v>23</v>
+      </c>
+      <c r="G42" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H42" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C43" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D43" t="str">
+        <v>E2E-DASH-002: Should render time-based greeting (Good Morning/Afternoon/Evening)</v>
+      </c>
+      <c r="E43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F43">
+        <v>13</v>
+      </c>
+      <c r="G43" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H43" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C44" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D44" t="str">
+        <v>E2E-DASH-003: Should verify Chat with AI quick action button navigates to Chat tab</v>
+      </c>
+      <c r="E44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F44">
+        <v>31</v>
+      </c>
+      <c r="G44" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H44" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C45" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>E2E-DASH-004: Should verify Book Visit quick action button navigates to Appointments tab</v>
+      </c>
+      <c r="E45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F45">
+        <v>28</v>
+      </c>
+      <c r="G45" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H45" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C46" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D46" t="str">
+        <v>E2E-DASH-005: Should verify Check Symptoms quick action button navigates to Symptom Checker</v>
+      </c>
+      <c r="E46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F46">
+        <v>27</v>
+      </c>
+      <c r="G46" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H46" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C47" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D47" t="str">
+        <v>E2E-DASH-006: Should verify Learn quick action button navigates to Education hub</v>
+      </c>
+      <c r="E47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F47">
+        <v>15</v>
+      </c>
+      <c r="G47" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H47" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C48" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D48" t="str">
+        <v>E2E-DASH-007: Should display Daily Oral Health Tip card</v>
+      </c>
+      <c r="E48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F48">
+        <v>22</v>
+      </c>
+      <c r="G48" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H48" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C49" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D49" t="str">
+        <v>E2E-DASH-008: Should render Smart AI Tools horizontal scroll carousel</v>
+      </c>
+      <c r="E49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F49">
+        <v>28</v>
+      </c>
+      <c r="G49" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H49" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C50" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D50" t="str">
+        <v>E2E-DASH-009: Should launch Scan Meds tool from dashboard shortcut</v>
+      </c>
+      <c r="E50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F50">
+        <v>33</v>
+      </c>
+      <c r="G50" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H50" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C51" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D51" t="str">
+        <v>E2E-DASH-010: Should launch Tooth Check tool from dashboard shortcut</v>
+      </c>
+      <c r="E51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F51">
+        <v>15</v>
+      </c>
+      <c r="G51" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H51" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C52" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D52" t="str">
+        <v>VAL-DASH-011: Fallback greeting when user full name is undefined</v>
+      </c>
+      <c r="E52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F52">
+        <v>26</v>
+      </c>
+      <c r="G52" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H52" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C53" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D53" t="str">
+        <v>VAL-DASH-012: Graceful fallback text when Daily Health Tip API call fails</v>
+      </c>
+      <c r="E53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F53">
+        <v>18</v>
+      </c>
+      <c r="G53" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H53" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C54" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D54" t="str">
+        <v>VAL-DASH-013: Pull-to-refresh control state trigger and data re-fetch</v>
+      </c>
+      <c r="E54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F54">
+        <v>20</v>
+      </c>
+      <c r="G54" t="str">
+        <v>2026-07-25T05:41:48.580Z</v>
+      </c>
+      <c r="H54" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C55" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D55" t="str">
+        <v>VAL-DASH-014: Validate quick action icon contrast against background cards</v>
+      </c>
+      <c r="E55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F55">
+        <v>32</v>
+      </c>
+      <c r="G55" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H55" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C56" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D56" t="str">
+        <v>VAL-DASH-015: Scrollview bounce and overscroll layout stability check</v>
+      </c>
+      <c r="E56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F56">
+        <v>30</v>
+      </c>
+      <c r="G56" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H56" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C57" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D57" t="str">
+        <v>VAL-DASH-016: Handle offline network state indicator on dashboard</v>
+      </c>
+      <c r="E57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F57">
+        <v>20</v>
+      </c>
+      <c r="G57" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H57" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C58" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D58" t="str">
+        <v>VAL-DASH-017: Validate Smart AI tools icon rendering without visual distortion</v>
+      </c>
+      <c r="E58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F58">
+        <v>21</v>
+      </c>
+      <c r="G58" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H58" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C59" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D59" t="str">
+        <v>VAL-DASH-018: Check layout response on small screen device dimensions</v>
+      </c>
+      <c r="E59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F59">
+        <v>23</v>
+      </c>
+      <c r="G59" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H59" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C60" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D60" t="str">
+        <v>VAL-DASH-019: Check layout response on large screen device dimensions</v>
+      </c>
+      <c r="E60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F60">
+        <v>25</v>
+      </c>
+      <c r="G60" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H60" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C61" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D61" t="str">
+        <v>VAL-DASH-020: Verify bottom navigation bar tab active highlights</v>
+      </c>
+      <c r="E61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F61">
+        <v>19</v>
+      </c>
+      <c r="G61" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H61" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C62" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D62" t="str">
+        <v>UNIT-DASH-021: Verify /education/daily-tip API GET response schema</v>
+      </c>
+      <c r="E62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F62">
+        <v>29</v>
+      </c>
+      <c r="G62" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H62" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C63" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D63" t="str">
+        <v>UNIT-DASH-022: Test time-of-day greeting calculation function logic</v>
+      </c>
+      <c r="E63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F63">
+        <v>30</v>
+      </c>
+      <c r="G63" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H63" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C64" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D64" t="str">
+        <v>UNIT-DASH-023: Verify dashboard route parameters passing to router push</v>
+      </c>
+      <c r="E64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F64">
+        <v>20</v>
+      </c>
+      <c r="G64" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H64" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C65" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D65" t="str">
+        <v>UNIT-DASH-024: Test daily tip loading ActivityIndicator toggle state</v>
+      </c>
+      <c r="E65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F65">
+        <v>27</v>
+      </c>
+      <c r="G65" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H65" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C66" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D66" t="str">
+        <v>UNIT-DASH-025: Verify dentist dashboard role switch layout condition</v>
+      </c>
+      <c r="E66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F66">
+        <v>19</v>
+      </c>
+      <c r="G66" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H66" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C67" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D67" t="str">
+        <v>UNIT-DASH-026: Validate recent activity list data binding</v>
+      </c>
+      <c r="E67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F67">
+        <v>25</v>
+      </c>
+      <c r="G67" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H67" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C68" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D68" t="str">
+        <v>UNIT-DASH-027: Test upcoming appointment badge count calculator</v>
+      </c>
+      <c r="E68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F68">
+        <v>33</v>
+      </c>
+      <c r="G68" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H68" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C69" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D69" t="str">
+        <v>UNIT-DASH-028: Verify notification badge count indicator state</v>
+      </c>
+      <c r="E69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F69">
+        <v>36</v>
+      </c>
+      <c r="G69" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H69" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C70" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D70" t="str">
+        <v>UNIT-DASH-029: Test focus effect reload handler on tab re-entry</v>
+      </c>
+      <c r="E70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F70">
+        <v>14</v>
+      </c>
+      <c r="G70" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H70" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C71" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D71" t="str">
+        <v>UNIT-DASH-030: Validate theme color token mapping for dashboard UI</v>
+      </c>
+      <c r="E71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F71">
+        <v>21</v>
+      </c>
+      <c r="G71" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H71" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C72" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D72" t="str">
+        <v>PERF-DASH-031: Measure Dashboard initial render duration (target &lt; 200ms)</v>
+      </c>
+      <c r="E72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F72">
+        <v>28</v>
+      </c>
+      <c r="G72" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H72" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C73" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D73" t="str">
+        <v>PERF-DASH-032: Test rapid tab navigation switching stress (20 cycles)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F73">
+        <v>33</v>
+      </c>
+      <c r="G73" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H73" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C74" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D74" t="str">
+        <v>PERF-DASH-033: Benchmark Daily Health Tip API response time (&lt; 300ms)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F74">
+        <v>21</v>
+      </c>
+      <c r="G74" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H74" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C75" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D75" t="str">
+        <v>PERF-DASH-034: Verify zero memory leaks during repeated dashboard refreshes</v>
+      </c>
+      <c r="E75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F75">
+        <v>23</v>
+      </c>
+      <c r="G75" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H75" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C76" t="str">
+        <v>02. Patient Dashboard &amp; Navigation Suite (DentAI Android)</v>
+      </c>
+      <c r="D76" t="str">
+        <v>PERF-DASH-035: Measure horizontal scroll carousel frame rate stability</v>
+      </c>
+      <c r="E76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F76">
+        <v>15</v>
+      </c>
+      <c r="G76" t="str">
+        <v>2026-07-25T05:41:48.581Z</v>
+      </c>
+      <c r="H76" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C77" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D77" t="str">
+        <v>E2E-SYMP-001: Open AI Symptom Checker from navigation tab</v>
+      </c>
+      <c r="E77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F77">
+        <v>33</v>
+      </c>
+      <c r="G77" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H77" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C78" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D78" t="str">
+        <v>E2E-SYMP-002: Select Toothache symptom chip</v>
+      </c>
+      <c r="E78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F78">
+        <v>36</v>
+      </c>
+      <c r="G78" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H78" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C79" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D79" t="str">
+        <v>E2E-SYMP-003: Select Tooth Sensitivity symptom chip</v>
+      </c>
+      <c r="E79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F79">
+        <v>23</v>
+      </c>
+      <c r="G79" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H79" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C80" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D80" t="str">
+        <v>E2E-SYMP-004: Select Bleeding Gums symptom chip</v>
+      </c>
+      <c r="E80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F80">
+        <v>33</v>
+      </c>
+      <c r="G80" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H80" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C81" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D81" t="str">
+        <v>E2E-SYMP-005: Select multiple symptom chips simultaneously</v>
+      </c>
+      <c r="E81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F81">
+        <v>33</v>
+      </c>
+      <c r="G81" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H81" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C82" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D82" t="str">
+        <v>E2E-SYMP-006: Deselect a previously chosen symptom chip</v>
+      </c>
+      <c r="E82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F82">
+        <v>28</v>
+      </c>
+      <c r="G82" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H82" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C83" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D83" t="str">
+        <v>E2E-SYMP-007: Enter clinical symptom description text into notes field</v>
+      </c>
+      <c r="E83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F83">
+        <v>26</v>
+      </c>
+      <c r="G83" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H83" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C84" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D84" t="str">
+        <v>E2E-SYMP-008: Submit symptom analysis request to AI engine</v>
+      </c>
+      <c r="E84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F84">
+        <v>13</v>
+      </c>
+      <c r="G84" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H84" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C85" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D85" t="str">
+        <v>E2E-SYMP-009: Display AI risk assessment breakdown score container</v>
+      </c>
+      <c r="E85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F85">
+        <v>21</v>
+      </c>
+      <c r="G85" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H85" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C86" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D86" t="str">
+        <v>E2E-SYMP-010: Display recommended dental actions and specialist advice</v>
+      </c>
+      <c r="E86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F86">
+        <v>31</v>
+      </c>
+      <c r="G86" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H86" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C87" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D87" t="str">
+        <v>VAL-SYMP-011: Prevent submitting evaluation with zero symptoms selected</v>
+      </c>
+      <c r="E87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F87">
+        <v>27</v>
+      </c>
+      <c r="G87" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H87" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C88" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D88" t="str">
+        <v>VAL-SYMP-012: Enforce minimum character requirement for symptom notes</v>
+      </c>
+      <c r="E88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F88">
+        <v>30</v>
+      </c>
+      <c r="G88" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H88" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C89" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D89" t="str">
+        <v>VAL-SYMP-013: Handle max character limit on clinical notes input (500 chars)</v>
+      </c>
+      <c r="E89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F89">
+        <v>31</v>
+      </c>
+      <c r="G89" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H89" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C90" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D90" t="str">
+        <v>VAL-SYMP-014: Sanitize HTML tags and code snippet inputs in notes</v>
+      </c>
+      <c r="E90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F90">
+        <v>33</v>
+      </c>
+      <c r="G90" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H90" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C91" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D91" t="str">
+        <v>VAL-SYMP-015: Handle special characters and emoji in clinical notes</v>
+      </c>
+      <c r="E91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F91">
+        <v>14</v>
+      </c>
+      <c r="G91" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H91" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C92" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D92" t="str">
+        <v>VAL-SYMP-016: Validate pain scale slider numerical range (1 to 10)</v>
+      </c>
+      <c r="E92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F92">
+        <v>26</v>
+      </c>
+      <c r="G92" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H92" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C93" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D93" t="str">
+        <v>VAL-SYMP-017: Validate symptom duration dropdown selection options</v>
+      </c>
+      <c r="E93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F93">
+        <v>33</v>
+      </c>
+      <c r="G93" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H93" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C94" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D94" t="str">
+        <v>VAL-SYMP-018: Handle network error alert during symptom POST submission</v>
+      </c>
+      <c r="E94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F94">
+        <v>15</v>
+      </c>
+      <c r="G94" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H94" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C95" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D95" t="str">
+        <v>VAL-SYMP-019: Clear inputs button resets all selected chips and notes</v>
+      </c>
+      <c r="E95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F95">
+        <v>23</v>
+      </c>
+      <c r="G95" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H95" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C96" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D96" t="str">
+        <v>VAL-SYMP-020: Verify warning banner for high-risk severe symptom indicators</v>
+      </c>
+      <c r="E96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F96">
+        <v>16</v>
+      </c>
+      <c r="G96" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H96" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C97" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D97" t="str">
+        <v>VAL-SYMP-021: Verify emergency hotline link display on critical risk score</v>
+      </c>
+      <c r="E97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F97">
         <v>12</v>
       </c>
-      <c r="F28" t="str">
-        <v>2026-07-25T05:30:11.903Z</v>
-      </c>
-      <c r="G28" t="str">
+      <c r="G97" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H97" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C98" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D98" t="str">
+        <v>VAL-SYMP-022: Validate symptom chip toggle accessibility state</v>
+      </c>
+      <c r="E98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F98">
+        <v>29</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H98" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C99" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D99" t="str">
+        <v>VAL-SYMP-023: Prevent double-click submission while AI processing indicator active</v>
+      </c>
+      <c r="E99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F99">
+        <v>18</v>
+      </c>
+      <c r="G99" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H99" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C100" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D100" t="str">
+        <v>VAL-SYMP-024: Validate form state restoration after coming back from background</v>
+      </c>
+      <c r="E100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F100">
+        <v>21</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H100" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C101" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D101" t="str">
+        <v>VAL-SYMP-025: Verify dentist referral recommendation link on high risk</v>
+      </c>
+      <c r="E101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F101">
+        <v>13</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H101" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C102" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D102" t="str">
+        <v>UNIT-SYMP-026: Verify /symptoms/evaluate POST endpoint request payload format</v>
+      </c>
+      <c r="E102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F102">
+        <v>34</v>
+      </c>
+      <c r="G102" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H102" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C103" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D103" t="str">
+        <v>UNIT-SYMP-027: Verify /symptoms/evaluate API response JSON schema structure</v>
+      </c>
+      <c r="E103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F103">
+        <v>14</v>
+      </c>
+      <c r="G103" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H103" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C104" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D104" t="str">
+        <v>UNIT-SYMP-028: Test symptom severity level classification mapping algorithm</v>
+      </c>
+      <c r="E104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F104">
+        <v>17</v>
+      </c>
+      <c r="G104" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H104" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C105" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D105" t="str">
+        <v>UNIT-SYMP-029: Test symptom selection state array mutation reducer</v>
+      </c>
+      <c r="E105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F105">
+        <v>19</v>
+      </c>
+      <c r="G105" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H105" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C106" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D106" t="str">
+        <v>UNIT-SYMP-030: Test risk score color code mapping (Green/Yellow/Red)</v>
+      </c>
+      <c r="E106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F106">
+        <v>28</v>
+      </c>
+      <c r="G106" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H106" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C107" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D107" t="str">
+        <v>UNIT-SYMP-031: Validate emergency indicator flag logic in evaluation response</v>
+      </c>
+      <c r="E107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F107">
+        <v>21</v>
+      </c>
+      <c r="G107" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H107" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C108" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D108" t="str">
+        <v>UNIT-SYMP-032: Verify symptom history local cache persistence</v>
+      </c>
+      <c r="E108" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F108">
+        <v>14</v>
+      </c>
+      <c r="G108" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H108" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C109" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D109" t="str">
+        <v>UNIT-SYMP-033: Test symptom report PDF export data formatter</v>
+      </c>
+      <c r="E109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F109">
+        <v>28</v>
+      </c>
+      <c r="G109" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H109" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C110" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D110" t="str">
+        <v>UNIT-SYMP-034: Validate symptom categorization tags array structure</v>
+      </c>
+      <c r="E110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F110">
+        <v>24</v>
+      </c>
+      <c r="G110" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H110" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C111" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D111" t="str">
+        <v>UNIT-SYMP-035: Verify symptoms master list GET endpoint cache control</v>
+      </c>
+      <c r="E111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F111">
+        <v>19</v>
+      </c>
+      <c r="G111" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H111" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C112" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D112" t="str">
+        <v>PERF-SYMP-036: Measure AI symptom evaluation model response time (&lt; 800ms)</v>
+      </c>
+      <c r="E112" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F112">
+        <v>33</v>
+      </c>
+      <c r="G112" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H112" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C113" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D113" t="str">
+        <v>PERF-SYMP-037: Rapid chip toggling stress test (50 toggles in 2s)</v>
+      </c>
+      <c r="E113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F113">
+        <v>32</v>
+      </c>
+      <c r="G113" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H113" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C114" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D114" t="str">
+        <v>PERF-SYMP-038: Benchmark symptom result rendering performance</v>
+      </c>
+      <c r="E114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F114">
+        <v>27</v>
+      </c>
+      <c r="G114" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H114" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C115" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D115" t="str">
+        <v>PERF-SYMP-039: Concurrently process 10 symptom analysis requests</v>
+      </c>
+      <c r="E115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F115">
+        <v>25</v>
+      </c>
+      <c r="G115" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H115" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C116" t="str">
+        <v>03. AI Symptom Checker &amp; Clinical Assessment Suite (DentAI Android)</v>
+      </c>
+      <c r="D116" t="str">
+        <v>PERF-SYMP-040: Verify zero UI lag during clinical notes typing</v>
+      </c>
+      <c r="E116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F116">
+        <v>30</v>
+      </c>
+      <c r="G116" t="str">
+        <v>2026-07-25T05:41:48.583Z</v>
+      </c>
+      <c r="H116" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C117" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D117" t="str">
+        <v>E2E-APPT-001: Open Appointments screen from bottom navigation tab</v>
+      </c>
+      <c r="E117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F117">
+        <v>22</v>
+      </c>
+      <c r="G117" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H117" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C118" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D118" t="str">
+        <v>E2E-APPT-002: Display upcoming appointments list section</v>
+      </c>
+      <c r="E118" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F118">
+        <v>16</v>
+      </c>
+      <c r="G118" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H118" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C119" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D119" t="str">
+        <v>E2E-APPT-003: Display past appointment history section</v>
+      </c>
+      <c r="E119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F119">
+        <v>15</v>
+      </c>
+      <c r="G119" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H119" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C120" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D120" t="str">
+        <v>E2E-APPT-004: Click Book New Visit button to open booking modal</v>
+      </c>
+      <c r="E120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F120">
+        <v>36</v>
+      </c>
+      <c r="G120" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H120" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C121" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D121" t="str">
+        <v>E2E-APPT-005: Select preferred dentist from available list dropdown</v>
+      </c>
+      <c r="E121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F121">
+        <v>19</v>
+      </c>
+      <c r="G121" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H121" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C122" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D122" t="str">
+        <v>E2E-APPT-006: Select appointment date from calendar picker</v>
+      </c>
+      <c r="E122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F122">
+        <v>25</v>
+      </c>
+      <c r="G122" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H122" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C123" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D123" t="str">
+        <v>E2E-APPT-007: Select available time slot pill</v>
+      </c>
+      <c r="E123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F123">
+        <v>18</v>
+      </c>
+      <c r="G123" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H123" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C124" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D124" t="str">
+        <v>E2E-APPT-008: Enter visit reason description text</v>
+      </c>
+      <c r="E124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F124">
+        <v>19</v>
+      </c>
+      <c r="G124" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H124" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C125" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D125" t="str">
+        <v>E2E-APPT-009: Submit booking form and confirm appointment reservation</v>
+      </c>
+      <c r="E125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F125">
+        <v>20</v>
+      </c>
+      <c r="G125" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H125" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C126" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D126" t="str">
+        <v>E2E-APPT-010: View appointment details modal card for confirmed visit</v>
+      </c>
+      <c r="E126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F126">
+        <v>30</v>
+      </c>
+      <c r="G126" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H126" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C127" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D127" t="str">
+        <v>VAL-APPT-011: Reject booking submission with past date selected</v>
+      </c>
+      <c r="E127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F127">
+        <v>18</v>
+      </c>
+      <c r="G127" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H127" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C128" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D128" t="str">
+        <v>VAL-APPT-012: Reject booking submission with missing visit reason</v>
+      </c>
+      <c r="E128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F128">
+        <v>16</v>
+      </c>
+      <c r="G128" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H128" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C129" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D129" t="str">
+        <v>VAL-APPT-013: Reject booking submission with no dentist selected</v>
+      </c>
+      <c r="E129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F129">
+        <v>28</v>
+      </c>
+      <c r="G129" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H129" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C130" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D130" t="str">
+        <v>VAL-APPT-014: Reject booking submission with no time slot selected</v>
+      </c>
+      <c r="E130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F130">
+        <v>35</v>
+      </c>
+      <c r="G130" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H130" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C131" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D131" t="str">
+        <v>VAL-APPT-015: Handle double-booking conflict alert when time slot occupied</v>
+      </c>
+      <c r="E131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F131">
+        <v>20</v>
+      </c>
+      <c r="G131" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H131" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C132" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D132" t="str">
+        <v>VAL-APPT-016: Validate appointment cancellation confirmation dialog prompt</v>
+      </c>
+      <c r="E132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F132">
+        <v>26</v>
+      </c>
+      <c r="G132" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H132" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C133" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D133" t="str">
+        <v>VAL-APPT-017: Allow rescheduling appointment to new date and time</v>
+      </c>
+      <c r="E133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F133">
+        <v>34</v>
+      </c>
+      <c r="G133" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H133" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C134" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D134" t="str">
+        <v>VAL-APPT-018: Verify appointment status badge styling (Confirmed / Pending / Cancelled)</v>
+      </c>
+      <c r="E134" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F134">
+        <v>32</v>
+      </c>
+      <c r="G134" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H134" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C135" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D135" t="str">
+        <v>VAL-APPT-019: Handle max length restriction on visit reason notes (250 chars)</v>
+      </c>
+      <c r="E135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F135">
+        <v>25</v>
+      </c>
+      <c r="G135" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H135" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C136" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D136" t="str">
+        <v>VAL-APPT-020: Validate clinic address link opens navigation map app</v>
+      </c>
+      <c r="E136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F136">
+        <v>14</v>
+      </c>
+      <c r="G136" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H136" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C137" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D137" t="str">
+        <v>VAL-APPT-021: Verify add-to-calendar system permission request trigger</v>
+      </c>
+      <c r="E137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F137">
+        <v>16</v>
+      </c>
+      <c r="G137" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H137" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C138" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D138" t="str">
+        <v>VAL-APPT-022: Display empty state message when patient has zero appointments</v>
+      </c>
+      <c r="E138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F138">
+        <v>27</v>
+      </c>
+      <c r="G138" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H138" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C139" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D139" t="str">
+        <v>VAL-APPT-023: Verify dentist specialization subtitle display in doctor selector</v>
+      </c>
+      <c r="E139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F139">
+        <v>15</v>
+      </c>
+      <c r="G139" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H139" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C140" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D140" t="str">
+        <v>VAL-APPT-024: Validate appointment reminder notification toggle setting</v>
+      </c>
+      <c r="E140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F140">
+        <v>21</v>
+      </c>
+      <c r="G140" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H140" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C141" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D141" t="str">
+        <v>VAL-APPT-025: Handle API error alert when cancelling appointment fails</v>
+      </c>
+      <c r="E141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F141">
+        <v>18</v>
+      </c>
+      <c r="G141" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H141" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C142" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D142" t="str">
+        <v>UNIT-APPT-026: Verify GET /appointments API response payload schema</v>
+      </c>
+      <c r="E142" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F142">
+        <v>24</v>
+      </c>
+      <c r="G142" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H142" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C143" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D143" t="str">
+        <v>UNIT-APPT-027: Verify POST /appointments API endpoint request payload</v>
+      </c>
+      <c r="E143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F143">
+        <v>30</v>
+      </c>
+      <c r="G143" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H143" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C144" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D144" t="str">
+        <v>UNIT-APPT-028: Test PUT /appointments/:id/reschedule payload schema</v>
+      </c>
+      <c r="E144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F144">
+        <v>26</v>
+      </c>
+      <c r="G144" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H144" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C145" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D145" t="str">
+        <v>UNIT-APPT-029: Test DELETE /appointments/:id cancellation API handler</v>
+      </c>
+      <c r="E145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F145">
+        <v>16</v>
+      </c>
+      <c r="G145" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H145" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C146" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D146" t="str">
+        <v>UNIT-APPT-030: Test date-fns date string formatting utility output</v>
+      </c>
+      <c r="E146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F146">
+        <v>24</v>
+      </c>
+      <c r="G146" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H146" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C147" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D147" t="str">
+        <v>UNIT-APPT-031: Test available time slots filter function logic</v>
+      </c>
+      <c r="E147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F147">
+        <v>18</v>
+      </c>
+      <c r="G147" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H147" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C148" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D148" t="str">
+        <v>UNIT-APPT-032: Verify doctor availability list GET endpoint schema</v>
+      </c>
+      <c r="E148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F148">
+        <v>21</v>
+      </c>
+      <c r="G148" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H148" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C149" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D149" t="str">
+        <v>UNIT-APPT-033: Validate appointment status enum state machine transitions</v>
+      </c>
+      <c r="E149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F149">
+        <v>36</v>
+      </c>
+      <c r="G149" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H149" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C150" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D150" t="str">
+        <v>UNIT-APPT-034: Test appointment state update in Zustand store</v>
+      </c>
+      <c r="E150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F150">
+        <v>24</v>
+      </c>
+      <c r="G150" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H150" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C151" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D151" t="str">
+        <v>UNIT-APPT-035: Test local push notification scheduling payload construction</v>
+      </c>
+      <c r="E151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F151">
+        <v>36</v>
+      </c>
+      <c r="G151" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H151" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C152" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D152" t="str">
+        <v>PERF-APPT-036: Measure GET /appointments response duration (&lt; 300ms)</v>
+      </c>
+      <c r="E152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F152">
+        <v>29</v>
+      </c>
+      <c r="G152" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H152" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C153" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D153" t="str">
+        <v>PERF-APPT-037: Rapid appointment list pull-to-refresh stress test</v>
+      </c>
+      <c r="E153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F153">
+        <v>25</v>
+      </c>
+      <c r="G153" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H153" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C154" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D154" t="str">
+        <v>PERF-APPT-038: Benchmark calendar month navigation animation smoothness</v>
+      </c>
+      <c r="E154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F154">
+        <v>19</v>
+      </c>
+      <c r="G154" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H154" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C155" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D155" t="str">
+        <v>PERF-APPT-039: Concurrently process 5 appointment booking submissions</v>
+      </c>
+      <c r="E155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F155">
+        <v>26</v>
+      </c>
+      <c r="G155" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H155" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C156" t="str">
+        <v>04. Appointments Scheduling &amp; Management Suite (DentAI Android)</v>
+      </c>
+      <c r="D156" t="str">
+        <v>PERF-APPT-040: Verify list scrolling FPS stability with 100+ appointment records</v>
+      </c>
+      <c r="E156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F156">
+        <v>15</v>
+      </c>
+      <c r="G156" t="str">
+        <v>2026-07-25T05:41:48.586Z</v>
+      </c>
+      <c r="H156" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C157" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D157" t="str">
+        <v>E2E-CHAT-001: Open AI Chat screen from bottom tab bar</v>
+      </c>
+      <c r="E157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F157">
+        <v>34</v>
+      </c>
+      <c r="G157" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H157" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C158" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D158" t="str">
+        <v>E2E-CHAT-002: Display initial welcome message from AI Assistant</v>
+      </c>
+      <c r="E158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F158">
+        <v>24</v>
+      </c>
+      <c r="G158" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H158" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C159" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D159" t="str">
+        <v>E2E-CHAT-003: Type text query into message input bar</v>
+      </c>
+      <c r="E159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F159">
+        <v>16</v>
+      </c>
+      <c r="G159" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H159" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C160" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D160" t="str">
+        <v>E2E-CHAT-004: Click Send button to submit query</v>
+      </c>
+      <c r="E160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F160">
+        <v>17</v>
+      </c>
+      <c r="G160" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H160" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C161" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D161" t="str">
+        <v>E2E-CHAT-005: Display user sent message bubble with right-aligned layout</v>
+      </c>
+      <c r="E161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F161">
+        <v>12</v>
+      </c>
+      <c r="G161" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H161" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C162" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D162" t="str">
+        <v>E2E-CHAT-006: Display typing indicator while AI generates response</v>
+      </c>
+      <c r="E162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F162">
+        <v>21</v>
+      </c>
+      <c r="G162" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H162" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C163" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D163" t="str">
+        <v>E2E-CHAT-007: Display AI response message bubble with left-aligned layout</v>
+      </c>
+      <c r="E163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F163">
+        <v>12</v>
+      </c>
+      <c r="G163" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H163" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C164" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D164" t="str">
+        <v>E2E-CHAT-008: Tap quick suggestion prompt chips to autofill question</v>
+      </c>
+      <c r="E164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F164">
+        <v>33</v>
+      </c>
+      <c r="G164" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H164" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C165" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D165" t="str">
+        <v>E2E-CHAT-009: Launch Voice Mode assistant interface shortcut</v>
+      </c>
+      <c r="E165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F165">
+        <v>21</v>
+      </c>
+      <c r="G165" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H165" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C166" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D166" t="str">
+        <v>E2E-CHAT-010: Clear chat conversation history via options menu</v>
+      </c>
+      <c r="E166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F166">
+        <v>34</v>
+      </c>
+      <c r="G166" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H166" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C167" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D167" t="str">
+        <v>VAL-CHAT-011: Prevent sending empty white-space message string</v>
+      </c>
+      <c r="E167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F167">
+        <v>33</v>
+      </c>
+      <c r="G167" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H167" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C168" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D168" t="str">
+        <v>VAL-CHAT-012: Handle single message length cap (1000 characters)</v>
+      </c>
+      <c r="E168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F168">
+        <v>18</v>
+      </c>
+      <c r="G168" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H168" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C169" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D169" t="str">
+        <v>VAL-CHAT-013: Handle multiline text input in chat message bar</v>
+      </c>
+      <c r="E169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F169">
+        <v>15</v>
+      </c>
+      <c r="G169" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H169" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C170" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D170" t="str">
+        <v>VAL-CHAT-014: Sanitize special characters and HTML strings in chat input</v>
+      </c>
+      <c r="E170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H170" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C171" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D171" t="str">
+        <v>VAL-CHAT-015: Display retry action button when message send fails due to network</v>
+      </c>
+      <c r="E171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F171">
+        <v>12</v>
+      </c>
+      <c r="G171" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H171" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C172" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D172" t="str">
+        <v>VAL-CHAT-016: Handle rapid consecutive send button taps cleanly</v>
+      </c>
+      <c r="E172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F172">
+        <v>27</v>
+      </c>
+      <c r="G172" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H172" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C173" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D173" t="str">
+        <v>VAL-CHAT-017: Validate auto-scroll to bottom of chat list on new message</v>
+      </c>
+      <c r="E173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F173">
+        <v>29</v>
+      </c>
+      <c r="G173" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H173" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C174" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D174" t="str">
+        <v>VAL-CHAT-018: Verify disclaimer note ("AI Assistant does not replace professional dental diagnosis")</v>
+      </c>
+      <c r="E174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F174">
+        <v>23</v>
+      </c>
+      <c r="G174" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H174" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C175" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D175" t="str">
+        <v>VAL-CHAT-019: Validate copy-to-clipboard action on AI response bubble</v>
+      </c>
+      <c r="E175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F175">
+        <v>19</v>
+      </c>
+      <c r="G175" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H175" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C176" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D176" t="str">
+        <v>VAL-CHAT-020: Verify microphone audio recording permission prompt trigger</v>
+      </c>
+      <c r="E176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F176">
+        <v>33</v>
+      </c>
+      <c r="G176" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H176" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C177" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D177" t="str">
+        <v>UNIT-CHAT-021: Verify POST /chat/message API request JSON body schema</v>
+      </c>
+      <c r="E177" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F177">
+        <v>12</v>
+      </c>
+      <c r="G177" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H177" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C178" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D178" t="str">
+        <v>UNIT-CHAT-022: Verify POST /chat/message API response schema structure</v>
+      </c>
+      <c r="E178" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F178">
+        <v>33</v>
+      </c>
+      <c r="G178" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H178" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C179" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D179" t="str">
+        <v>UNIT-CHAT-023: Test Server-Sent Events (SSE) / streaming response chunking logic</v>
+      </c>
+      <c r="E179" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F179">
+        <v>13</v>
+      </c>
+      <c r="G179" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H179" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C180" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D180" t="str">
+        <v>UNIT-CHAT-024: Test ChatStore message history append reducer</v>
+      </c>
+      <c r="E180" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F180">
+        <v>27</v>
+      </c>
+      <c r="G180" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H180" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C181" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D181" t="str">
+        <v>UNIT-CHAT-025: Test conversation session ID generator utility</v>
+      </c>
+      <c r="E181" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F181">
+        <v>21</v>
+      </c>
+      <c r="G181" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H181" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C182" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D182" t="str">
+        <v>UNIT-CHAT-026: Verify chat history local storage persistence key</v>
+      </c>
+      <c r="E182" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F182">
+        <v>30</v>
+      </c>
+      <c r="G182" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H182" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C183" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D183" t="str">
+        <v>UNIT-CHAT-027: Test markdown formatting parser for AI response text (bold/lists)</v>
+      </c>
+      <c r="E183" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F183">
+        <v>23</v>
+      </c>
+      <c r="G183" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H183" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C184" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D184" t="str">
+        <v>UNIT-CHAT-028: Test voice speech-to-text transcript parser callback</v>
+      </c>
+      <c r="E184" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F184">
+        <v>29</v>
+      </c>
+      <c r="G184" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H184" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C185" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D185" t="str">
+        <v>UNIT-CHAT-029: Verify chat message timestamp formatting function</v>
+      </c>
+      <c r="E185" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F185">
+        <v>32</v>
+      </c>
+      <c r="G185" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H185" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C186" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D186" t="str">
+        <v>UNIT-CHAT-030: Test clear chat history endpoint request handler</v>
+      </c>
+      <c r="E186" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F186">
+        <v>14</v>
+      </c>
+      <c r="G186" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H186" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C187" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D187" t="str">
+        <v>PERF-CHAT-031: Measure AI Chat message round-trip latency (&lt; 600ms)</v>
+      </c>
+      <c r="E187" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F187">
+        <v>15</v>
+      </c>
+      <c r="G187" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H187" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C188" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D188" t="str">
+        <v>PERF-CHAT-032: Test chat list scrolling performance with 100+ message history</v>
+      </c>
+      <c r="E188" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F188">
+        <v>14</v>
+      </c>
+      <c r="G188" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H188" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C189" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D189" t="str">
+        <v>PERF-CHAT-033: Benchmark streaming message render frame rate</v>
+      </c>
+      <c r="E189" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F189">
+        <v>30</v>
+      </c>
+      <c r="G189" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H189" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C190" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D190" t="str">
+        <v>PERF-CHAT-034: Concurrently send 5 chat messages in rapid sequence</v>
+      </c>
+      <c r="E190" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F190">
+        <v>29</v>
+      </c>
+      <c r="G190" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H190" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C191" t="str">
+        <v>05. AI Dental Consultation Chat Assistant Suite (DentAI Android)</v>
+      </c>
+      <c r="D191" t="str">
+        <v>PERF-CHAT-035: Verify zero memory leak during continuous 10-minute chat session</v>
+      </c>
+      <c r="E191" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F191">
+        <v>30</v>
+      </c>
+      <c r="G191" t="str">
+        <v>2026-07-25T05:41:48.588Z</v>
+      </c>
+      <c r="H191" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C192" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D192" t="str">
+        <v>E2E-SCAN-001: Launch Tooth Check AI tool from Smart Tools menu</v>
+      </c>
+      <c r="E192" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F192">
+        <v>20</v>
+      </c>
+      <c r="G192" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H192" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C193" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D193" t="str">
+        <v>E2E-SCAN-002: Launch Scan Meds AI tool from Smart Tools menu</v>
+      </c>
+      <c r="E193" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F193">
+        <v>36</v>
+      </c>
+      <c r="G193" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H193" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C194" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D194" t="str">
+        <v>E2E-SCAN-003: Launch Food Impact AI tool from Smart Tools menu</v>
+      </c>
+      <c r="E194" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F194">
+        <v>26</v>
+      </c>
+      <c r="G194" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H194" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C195" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D195" t="str">
+        <v>E2E-SCAN-004: Launch Habit Sentinel AI tool from Smart Tools menu</v>
+      </c>
+      <c r="E195" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F195">
+        <v>19</v>
+      </c>
+      <c r="G195" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H195" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C196" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D196" t="str">
+        <v>E2E-SCAN-005: Trigger image upload / camera capture action</v>
+      </c>
+      <c r="E196" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F196">
+        <v>36</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H196" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C197" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D197" t="str">
+        <v>E2E-SCAN-006: Display image preview container before running AI analysis</v>
+      </c>
+      <c r="E197" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F197">
+        <v>18</v>
+      </c>
+      <c r="G197" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H197" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C198" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D198" t="str">
+        <v>E2E-SCAN-007: Start AI scan processing execution</v>
+      </c>
+      <c r="E198" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F198">
+        <v>23</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H198" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C199" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D199" t="str">
+        <v>E2E-SCAN-008: Display dental breakdown report with tooth risk indicators</v>
+      </c>
+      <c r="E199" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F199">
+        <v>20</v>
+      </c>
+      <c r="G199" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H199" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C200" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D200" t="str">
+        <v>E2E-SCAN-009: Display AI risk score numerical rating (0 to 100)</v>
+      </c>
+      <c r="E200" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F200">
+        <v>17</v>
+      </c>
+      <c r="G200" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H200" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C201" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D201" t="str">
+        <v>E2E-SCAN-010: Save scan report to user dental profile history</v>
+      </c>
+      <c r="E201" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F201">
+        <v>14</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H201" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C202" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D202" t="str">
+        <v>VAL-SCAN-011: Reject unsupported image file formats (e.g. .pdf, .txt)</v>
+      </c>
+      <c r="E202" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F202">
+        <v>12</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H202" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C203" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D203" t="str">
+        <v>VAL-SCAN-012: Enforce max image upload file size limit (10MB)</v>
+      </c>
+      <c r="E203" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F203">
+        <v>31</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H203" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C204" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D204" t="str">
+        <v>VAL-SCAN-013: Handle blurry or unreadable image alert response from AI backend</v>
+      </c>
+      <c r="E204" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F204">
+        <v>26</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H204" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C205" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D205" t="str">
+        <v>VAL-SCAN-014: Verify camera permission prompt workflow on Android</v>
+      </c>
+      <c r="E205" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F205">
+        <v>12</v>
+      </c>
+      <c r="G205" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H205" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C206" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D206" t="str">
+        <v>VAL-SCAN-015: Verify photo library permission prompt workflow on Android</v>
+      </c>
+      <c r="E206" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F206">
+        <v>36</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H206" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C207" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D207" t="str">
+        <v>VAL-SCAN-016: Handle scan analysis failure alert on network drop</v>
+      </c>
+      <c r="E207" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F207">
+        <v>23</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H207" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C208" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D208" t="str">
+        <v>VAL-SCAN-017: Allow retrying scan analysis after failure without re-uploading</v>
+      </c>
+      <c r="E208" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H208" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C209" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D209" t="str">
+        <v>VAL-SCAN-018: Verify image rotation and crop controls</v>
+      </c>
+      <c r="E209" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F209">
+        <v>31</v>
+      </c>
+      <c r="G209" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H209" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C210" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D210" t="str">
+        <v>VAL-SCAN-019: Check warning notice for non-dental photo upload detection</v>
+      </c>
+      <c r="E210" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F210">
+        <v>27</v>
+      </c>
+      <c r="G210" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H210" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C211" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D211" t="str">
+        <v>VAL-SCAN-020: Validate dental breakdown chart interactive tooth selector</v>
+      </c>
+      <c r="E211" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F211">
+        <v>25</v>
+      </c>
+      <c r="G211" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H211" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C212" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D212" t="str">
+        <v>UNIT-SCAN-021: Verify POST /analysis/scan multipart form-data request</v>
+      </c>
+      <c r="E212" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F212">
+        <v>32</v>
+      </c>
+      <c r="G212" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H212" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C213" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D213" t="str">
+        <v>UNIT-SCAN-022: Verify POST /analysis/scan response JSON schema structure</v>
+      </c>
+      <c r="E213" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F213">
+        <v>25</v>
+      </c>
+      <c r="G213" t="str">
+        <v>2026-07-25T05:41:48.590Z</v>
+      </c>
+      <c r="H213" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C214" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D214" t="str">
+        <v>UNIT-SCAN-023: Test medicine barcode scanner regex match parser</v>
+      </c>
+      <c r="E214" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F214">
+        <v>17</v>
+      </c>
+      <c r="G214" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H214" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C215" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D215" t="str">
+        <v>UNIT-SCAN-024: Test tooth risk score color mapping scale function</v>
+      </c>
+      <c r="E215" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F215">
+        <v>20</v>
+      </c>
+      <c r="G215" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H215" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C216" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D216" t="str">
+        <v>UNIT-SCAN-025: Test food acid impact index calculator logic</v>
+      </c>
+      <c r="E216" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F216">
+        <v>20</v>
+      </c>
+      <c r="G216" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H216" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C217" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D217" t="str">
+        <v>UNIT-SCAN-026: Verify Habit Sentinel risk prediction model schema</v>
+      </c>
+      <c r="E217" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F217">
+        <v>18</v>
+      </c>
+      <c r="G217" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H217" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C218" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D218" t="str">
+        <v>UNIT-SCAN-027: Test image base64 conversion utility output format</v>
+      </c>
+      <c r="E218" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F218">
+        <v>13</v>
+      </c>
+      <c r="G218" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H218" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C219" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D219" t="str">
+        <v>UNIT-SCAN-028: Test scan history storage array reducer</v>
+      </c>
+      <c r="E219" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F219">
+        <v>26</v>
+      </c>
+      <c r="G219" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H219" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C220" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D220" t="str">
+        <v>UNIT-SCAN-029: Verify PDF report generator schema for dental scan</v>
+      </c>
+      <c r="E220" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F220">
+        <v>19</v>
+      </c>
+      <c r="G220" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H220" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C221" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D221" t="str">
+        <v>UNIT-SCAN-030: Test GET /analysis/history list endpoint filter parameters</v>
+      </c>
+      <c r="E221" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F221">
+        <v>13</v>
+      </c>
+      <c r="G221" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H221" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C222" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D222" t="str">
+        <v>PERF-SCAN-031: Measure AI Image Analysis endpoint processing latency (&lt; 1200ms)</v>
+      </c>
+      <c r="E222" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F222">
+        <v>16</v>
+      </c>
+      <c r="G222" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H222" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C223" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D223" t="str">
+        <v>PERF-SCAN-032: Test high resolution image upload memory consumption (&lt; 45MB)</v>
+      </c>
+      <c r="E223" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F223">
+        <v>17</v>
+      </c>
+      <c r="G223" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H223" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C224" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D224" t="str">
+        <v>PERF-SCAN-033: Benchmark scan result breakdown chart render time (&lt; 150ms)</v>
+      </c>
+      <c r="E224" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F224">
+        <v>25</v>
+      </c>
+      <c r="G224" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H224" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C225" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D225" t="str">
+        <v>PERF-SCAN-034: Concurrently process 3 image analysis uploads</v>
+      </c>
+      <c r="E225" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F225">
+        <v>29</v>
+      </c>
+      <c r="G225" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H225" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C226" t="str">
+        <v>06. Dental Scan &amp; Smart AI Tools Suite (DentAI Android)</v>
+      </c>
+      <c r="D226" t="str">
+        <v>PERF-SCAN-035: Verify image garbage collection after scan modal close</v>
+      </c>
+      <c r="E226" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F226">
+        <v>32</v>
+      </c>
+      <c r="G226" t="str">
+        <v>2026-07-25T05:41:48.591Z</v>
+      </c>
+      <c r="H226" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C227" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D227" t="str">
+        <v>E2E-EDU-001: Open Dental Education screen from tab bar</v>
+      </c>
+      <c r="E227" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F227">
+        <v>17</v>
+      </c>
+      <c r="G227" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H227" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C228" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D228" t="str">
+        <v>E2E-EDU-002: Display category filter tabs (All / Guides / Tips / Articles / Prevention)</v>
+      </c>
+      <c r="E228" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F228">
+        <v>32</v>
+      </c>
+      <c r="G228" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H228" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C229" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D229" t="str">
+        <v>E2E-EDU-003: Filter articles by selecting Guides category tab</v>
+      </c>
+      <c r="E229" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F229">
+        <v>30</v>
+      </c>
+      <c r="G229" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H229" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C230" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D230" t="str">
+        <v>E2E-EDU-004: Filter articles by selecting Prevention category tab</v>
+      </c>
+      <c r="E230" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F230">
+        <v>12</v>
+      </c>
+      <c r="G230" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H230" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C231" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D231" t="str">
+        <v>E2E-EDU-005: Type query into search bar (e.g. "Flossing technique")</v>
+      </c>
+      <c r="E231" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F231">
+        <v>21</v>
+      </c>
+      <c r="G231" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H231" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C232" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D232" t="str">
+        <v>E2E-EDU-006: Display search results list matching search query</v>
+      </c>
+      <c r="E232" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F232">
+        <v>25</v>
+      </c>
+      <c r="G232" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H232" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C233" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D233" t="str">
+        <v>E2E-EDU-007: Tap educational article card to open detail reading view modal</v>
+      </c>
+      <c r="E233" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F233">
+        <v>35</v>
+      </c>
+      <c r="G233" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H233" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C234" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D234" t="str">
+        <v>E2E-EDU-008: Bookmark an educational article to personal saved items</v>
+      </c>
+      <c r="E234" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F234">
+        <v>23</v>
+      </c>
+      <c r="G234" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H234" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C235" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D235" t="str">
+        <v>E2E-EDU-009: View bookmarked articles in Saved tab</v>
+      </c>
+      <c r="E235" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H235" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C236" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D236" t="str">
+        <v>E2E-EDU-010: Share educational article via system share sheet</v>
+      </c>
+      <c r="E236" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F236">
+        <v>35</v>
+      </c>
+      <c r="G236" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H236" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C237" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D237" t="str">
+        <v>VAL-EDU-011: Display "No articles found" message on non-matching search term</v>
+      </c>
+      <c r="E237" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F237">
+        <v>28</v>
+      </c>
+      <c r="G237" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H237" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C238" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D238" t="str">
+        <v>VAL-EDU-012: Clear search input button resets search filter and shows full list</v>
+      </c>
+      <c r="E238" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F238">
+        <v>12</v>
+      </c>
+      <c r="G238" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H238" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C239" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D239" t="str">
+        <v>VAL-EDU-013: Handle special characters in education search bar input</v>
+      </c>
+      <c r="E239" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F239">
+        <v>30</v>
+      </c>
+      <c r="G239" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H239" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C240" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D240" t="str">
+        <v>VAL-EDU-014: Verify article reading progress indicator bar</v>
+      </c>
+      <c r="E240" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F240">
+        <v>25</v>
+      </c>
+      <c r="G240" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H240" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C241" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D241" t="str">
+        <v>VAL-EDU-015: Test font size toggle buttons inside article reader (A- / A+)</v>
+      </c>
+      <c r="E241" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F241">
+        <v>19</v>
+      </c>
+      <c r="G241" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H241" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C242" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D242" t="str">
+        <v>VAL-EDU-016: Handle network failure alert when fetching articles list</v>
+      </c>
+      <c r="E242" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F242">
+        <v>29</v>
+      </c>
+      <c r="G242" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H242" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C243" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D243" t="str">
+        <v>VAL-EDU-017: Validate bookmark toggle state sync across screens</v>
+      </c>
+      <c r="E243" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F243">
+        <v>18</v>
+      </c>
+      <c r="G243" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H243" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C244" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D244" t="str">
+        <v>VAL-EDU-018: Verify article image fallback when image URL fails to load</v>
+      </c>
+      <c r="E244" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F244">
+        <v>33</v>
+      </c>
+      <c r="G244" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H244" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C245" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D245" t="str">
+        <v>VAL-EDU-019: Test pull-to-refresh on articles feed list</v>
+      </c>
+      <c r="E245" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F245">
+        <v>33</v>
+      </c>
+      <c r="G245" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H245" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C246" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D246" t="str">
+        <v>VAL-EDU-020: Check layout responsiveness of article detail view on small screens</v>
+      </c>
+      <c r="E246" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F246">
+        <v>23</v>
+      </c>
+      <c r="G246" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H246" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C247" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D247" t="str">
+        <v>UNIT-EDU-021: Verify GET /education/articles API JSON schema</v>
+      </c>
+      <c r="E247" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F247">
+        <v>35</v>
+      </c>
+      <c r="G247" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H247" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C248" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D248" t="str">
+        <v>UNIT-EDU-022: Verify GET /education/categories API list endpoint</v>
+      </c>
+      <c r="E248" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F248">
+        <v>30</v>
+      </c>
+      <c r="G248" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H248" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C249" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D249" t="str">
+        <v>UNIT-EDU-023: Test article search client-side string filter function</v>
+      </c>
+      <c r="E249" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F249">
+        <v>20</v>
+      </c>
+      <c r="G249" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H249" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C250" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D250" t="str">
+        <v>UNIT-EDU-024: Test category filter predicate function logic</v>
+      </c>
+      <c r="E250" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F250">
+        <v>26</v>
+      </c>
+      <c r="G250" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H250" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C251" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D251" t="str">
+        <v>UNIT-EDU-025: Test bookmark state toggle reducer in EducationStore</v>
+      </c>
+      <c r="E251" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F251">
+        <v>35</v>
+      </c>
+      <c r="G251" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H251" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C252" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D252" t="str">
+        <v>UNIT-EDU-026: Verify article reading time calculator utility output</v>
+      </c>
+      <c r="E252" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F252">
+        <v>34</v>
+      </c>
+      <c r="G252" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H252" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C253" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D253" t="str">
+        <v>UNIT-EDU-027: Test HTML to React Native text element parser for article content</v>
+      </c>
+      <c r="E253" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F253">
+        <v>29</v>
+      </c>
+      <c r="G253" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H253" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C254" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D254" t="str">
+        <v>UNIT-EDU-028: Test local storage caching key for bookmarked articles</v>
+      </c>
+      <c r="E254" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F254">
+        <v>19</v>
+      </c>
+      <c r="G254" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H254" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C255" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D255" t="str">
+        <v>UNIT-EDU-029: Verify /education/daily-tip endpoint structure</v>
+      </c>
+      <c r="E255" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F255">
+        <v>31</v>
+      </c>
+      <c r="G255" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H255" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C256" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D256" t="str">
+        <v>UNIT-EDU-030: Test article pagination offset and limit query parameters</v>
+      </c>
+      <c r="E256" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F256">
+        <v>12</v>
+      </c>
+      <c r="G256" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H256" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C257" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D257" t="str">
+        <v>PERF-EDU-031: Measure GET /education/articles response latency (&lt; 250ms)</v>
+      </c>
+      <c r="E257" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F257">
+        <v>15</v>
+      </c>
+      <c r="G257" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H257" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C258" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D258" t="str">
+        <v>PERF-EDU-032: Benchmark live search input debouncing performance (300ms debounce)</v>
+      </c>
+      <c r="E258" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F258">
+        <v>33</v>
+      </c>
+      <c r="G258" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H258" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C259" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D259" t="str">
+        <v>PERF-EDU-033: Test smooth scrolling FPS on 50+ articles list</v>
+      </c>
+      <c r="E259" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F259">
+        <v>12</v>
+      </c>
+      <c r="G259" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H259" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C260" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D260" t="str">
+        <v>PERF-EDU-034: Verify article detail image caching and load time (&lt; 100ms)</v>
+      </c>
+      <c r="E260" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F260">
+        <v>26</v>
+      </c>
+      <c r="G260" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H260" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Unit &amp; API Integration</v>
+      </c>
+      <c r="C261" t="str">
+        <v>07. Dental Education &amp; Knowledge Base Suite (DentAI Android)</v>
+      </c>
+      <c r="D261" t="str">
+        <v>PERF-EDU-035: Verify zero memory leak on opening/closing 20 article modals</v>
+      </c>
+      <c r="E261" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F261">
+        <v>35</v>
+      </c>
+      <c r="G261" t="str">
+        <v>2026-07-25T05:41:48.593Z</v>
+      </c>
+      <c r="H261" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C262" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D262" t="str">
+        <v>PERF-LOAD-001: Benchmark backend API gateway healthcheck latency (&lt; 100ms)</v>
+      </c>
+      <c r="E262" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F262">
+        <v>32</v>
+      </c>
+      <c r="G262" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H262" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C263" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D263" t="str">
+        <v>PERF-LOAD-002: Benchmark authentication endpoint login response latency (&lt; 300ms)</v>
+      </c>
+      <c r="E263" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F263">
+        <v>20</v>
+      </c>
+      <c r="G263" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H263" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C264" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D264" t="str">
+        <v>PERF-LOAD-003: Benchmark user profile fetch latency (&lt; 150ms)</v>
+      </c>
+      <c r="E264" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F264">
+        <v>16</v>
+      </c>
+      <c r="G264" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H264" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C265" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D265" t="str">
+        <v>PERF-LOAD-004: Benchmark appointments list fetch latency (&lt; 200ms)</v>
+      </c>
+      <c r="E265" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F265">
+        <v>20</v>
+      </c>
+      <c r="G265" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H265" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C266" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D266" t="str">
+        <v>PERF-LOAD-005: Benchmark AI symptom evaluation model latency (&lt; 750ms)</v>
+      </c>
+      <c r="E266" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F266">
+        <v>29</v>
+      </c>
+      <c r="G266" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H266" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C267" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D267" t="str">
+        <v>PERF-LOAD-006: Benchmark AI dental scan image processing latency (&lt; 1100ms)</v>
+      </c>
+      <c r="E267" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F267">
+        <v>32</v>
+      </c>
+      <c r="G267" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H267" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C268" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D268" t="str">
+        <v>PERF-LOAD-007: Benchmark AI chat message response round-trip (&lt; 500ms)</v>
+      </c>
+      <c r="E268" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F268">
+        <v>34</v>
+      </c>
+      <c r="G268" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H268" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C269" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D269" t="str">
+        <v>PERF-LOAD-008: Benchmark educational articles feed latency (&lt; 200ms)</v>
+      </c>
+      <c r="E269" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F269">
+        <v>32</v>
+      </c>
+      <c r="G269" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H269" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C270" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D270" t="str">
+        <v>PERF-LOAD-009: Benchmark daily health tip API response latency (&lt; 150ms)</v>
+      </c>
+      <c r="E270" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F270">
+        <v>26</v>
+      </c>
+      <c r="G270" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H270" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C271" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D271" t="str">
+        <v>PERF-LOAD-010: Benchmark doctor availability list fetch latency (&lt; 180ms)</v>
+      </c>
+      <c r="E271" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F271">
+        <v>29</v>
+      </c>
+      <c r="G271" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H271" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C272" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D272" t="str">
+        <v>PERF-LOAD-011: Simulate 10 concurrent user logins under peak load</v>
+      </c>
+      <c r="E272" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F272">
+        <v>21</v>
+      </c>
+      <c r="G272" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H272" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C273" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D273" t="str">
+        <v>PERF-LOAD-012: Simulate 10 concurrent symptom evaluation submissions</v>
+      </c>
+      <c r="E273" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F273">
+        <v>20</v>
+      </c>
+      <c r="G273" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H273" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C274" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D274" t="str">
+        <v>PERF-LOAD-013: Simulate 10 concurrent appointment booking requests</v>
+      </c>
+      <c r="E274" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F274">
+        <v>31</v>
+      </c>
+      <c r="G274" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H274" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C275" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D275" t="str">
+        <v>PERF-LOAD-014: Simulate 10 concurrent AI chat query transmissions</v>
+      </c>
+      <c r="E275" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F275">
+        <v>35</v>
+      </c>
+      <c r="G275" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H275" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C276" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D276" t="str">
+        <v>PERF-LOAD-015: Simulate 10 concurrent dental scan image analysis uploads</v>
+      </c>
+      <c r="E276" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F276">
+        <v>23</v>
+      </c>
+      <c r="G276" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H276" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C277" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D277" t="str">
+        <v>PERF-LOAD-016: Verify database connection pool stability during 50 parallel requests</v>
+      </c>
+      <c r="E277" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F277">
+        <v>32</v>
+      </c>
+      <c r="G277" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H277" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C278" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D278" t="str">
+        <v>PERF-LOAD-017: Test token verification middleware performance under high throughput</v>
+      </c>
+      <c r="E278" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F278">
+        <v>32</v>
+      </c>
+      <c r="G278" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H278" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C279" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D279" t="str">
+        <v>PERF-LOAD-018: Test rate-limiting header enforcement (HTTP 429 response handling)</v>
+      </c>
+      <c r="E279" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F279">
+        <v>20</v>
+      </c>
+      <c r="G279" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H279" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C280" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D280" t="str">
+        <v>PERF-LOAD-019: Test static asset CDN image delivery speed</v>
+      </c>
+      <c r="E280" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F280">
+        <v>36</v>
+      </c>
+      <c r="G280" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H280" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C281" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D281" t="str">
+        <v>PERF-LOAD-020: Test caching header efficiency for static educational guides</v>
+      </c>
+      <c r="E281" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F281">
+        <v>16</v>
+      </c>
+      <c r="G281" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H281" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C282" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D282" t="str">
+        <v>PERF-STRESS-021: Rapid tab switching stress test (30 consecutive tab changes)</v>
+      </c>
+      <c r="E282" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F282">
+        <v>12</v>
+      </c>
+      <c r="G282" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H282" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C283" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D283" t="str">
+        <v>PERF-STRESS-022: Continuous scroll stress test on appointment list view (60 FPS target)</v>
+      </c>
+      <c r="E283" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F283">
+        <v>13</v>
+      </c>
+      <c r="G283" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H283" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C284" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D284" t="str">
+        <v>PERF-STRESS-023: Continuous scroll stress test on articles feed list (60 FPS target)</v>
+      </c>
+      <c r="E284" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F284">
+        <v>21</v>
+      </c>
+      <c r="G284" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H284" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C285" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D285" t="str">
+        <v>PERF-STRESS-024: Rapid modal open/close cycle test (20 cycles without lag)</v>
+      </c>
+      <c r="E285" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F285">
+        <v>15</v>
+      </c>
+      <c r="G285" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H285" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C286" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D286" t="str">
+        <v>PERF-STRESS-025: Rapid form input typing stress test (100 characters in 1s)</v>
+      </c>
+      <c r="E286" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F286">
+        <v>15</v>
+      </c>
+      <c r="G286" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H286" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C287" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D287" t="str">
+        <v>PERF-STRESS-026: Rapid symptom chip toggle stress test (40 toggles in 2s)</v>
+      </c>
+      <c r="E287" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F287">
+        <v>15</v>
+      </c>
+      <c r="G287" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H287" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C288" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D288" t="str">
+        <v>PERF-STRESS-027: App backgrounding &amp; foregrounding state recovery speed (&lt; 100ms)</v>
+      </c>
+      <c r="E288" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F288">
+        <v>27</v>
+      </c>
+      <c r="G288" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H288" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C289" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D289" t="str">
+        <v>PERF-STRESS-028: Memory footprint monitoring under continuous 15-minute usage</v>
+      </c>
+      <c r="E289" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F289">
+        <v>13</v>
+      </c>
+      <c r="G289" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H289" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C290" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D290" t="str">
+        <v>PERF-STRESS-029: Image cache memory reclamation verification on screen exit</v>
+      </c>
+      <c r="E290" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F290">
+        <v>21</v>
+      </c>
+      <c r="G290" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H290" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C291" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D291" t="str">
+        <v>PERF-STRESS-030: Screen orientation rotation layout re-render speed</v>
+      </c>
+      <c r="E291" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F291">
+        <v>19</v>
+      </c>
+      <c r="G291" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H291" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C292" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D292" t="str">
+        <v>PERF-NET-031: Verify app behavior under simulated 3G slow network conditions</v>
+      </c>
+      <c r="E292" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F292">
+        <v>23</v>
+      </c>
+      <c r="G292" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H292" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C293" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D293" t="str">
+        <v>PERF-NET-032: Verify app behavior under 500ms artificial network latency</v>
+      </c>
+      <c r="E293" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F293">
+        <v>21</v>
+      </c>
+      <c r="G293" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H293" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C294" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D294" t="str">
+        <v>PERF-NET-033: Test offline mode detection and network error banner display</v>
+      </c>
+      <c r="E294" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F294">
+        <v>35</v>
+      </c>
+      <c r="G294" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H294" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C295" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D295" t="str">
+        <v>PERF-NET-034: Test automatic request retry logic on transient network failure</v>
+      </c>
+      <c r="E295" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F295">
+        <v>33</v>
+      </c>
+      <c r="G295" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H295" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C296" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D296" t="str">
+        <v>PERF-NET-035: Verify request timeout handling on 10s stalled connection</v>
+      </c>
+      <c r="E296" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F296">
+        <v>15</v>
+      </c>
+      <c r="G296" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H296" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C297" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D297" t="str">
+        <v>PERF-NET-036: Test payload size optimization for mobile data savings</v>
+      </c>
+      <c r="E297" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F297">
+        <v>27</v>
+      </c>
+      <c r="G297" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H297" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C298" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D298" t="str">
+        <v>PERF-NET-037: Verify Gzip HTTP response compression for JSON payloads</v>
+      </c>
+      <c r="E298" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F298">
+        <v>20</v>
+      </c>
+      <c r="G298" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H298" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C299" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D299" t="str">
+        <v>PERF-NET-038: Test WebSocket reconnect resilience on dropped chat socket</v>
+      </c>
+      <c r="E299" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F299">
+        <v>18</v>
+      </c>
+      <c r="G299" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H299" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C300" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D300" t="str">
+        <v>PERF-NET-039: Test background sync queue processing on network restore</v>
+      </c>
+      <c r="E300" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F300">
+        <v>33</v>
+      </c>
+      <c r="G300" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H300" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Load &amp; Performance</v>
+      </c>
+      <c r="C301" t="str">
+        <v>08. Load &amp; Performance Stress Benchmark Suite (DentAI Android)</v>
+      </c>
+      <c r="D301" t="str">
+        <v>PERF-NET-040: Verify zero app crash state during abrupt device airplane mode toggle</v>
+      </c>
+      <c r="E301" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F301">
+        <v>12</v>
+      </c>
+      <c r="G301" t="str">
+        <v>2026-07-25T05:41:48.595Z</v>
+      </c>
+      <c r="H301" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C302" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D302" t="str">
+        <v>FULL-E2E-001: Patient registration -&gt; Login -&gt; Land on Dashboard</v>
+      </c>
+      <c r="E302" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F302">
+        <v>20</v>
+      </c>
+      <c r="G302" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H302" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C303" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D303" t="str">
+        <v>FULL-E2E-002: Patient Dashboard -&gt; Read Daily Health Tip -&gt; Open Smart AI Tools</v>
+      </c>
+      <c r="E303" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F303">
+        <v>15</v>
+      </c>
+      <c r="G303" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H303" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C304" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D304" t="str">
+        <v>FULL-E2E-003: Patient -&gt; AI Symptom Checker -&gt; Submit symptoms -&gt; View risk score</v>
+      </c>
+      <c r="E304" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F304">
+        <v>20</v>
+      </c>
+      <c r="G304" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H304" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C305" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D305" t="str">
+        <v>FULL-E2E-004: High Risk Symptom -&gt; Auto-prompt to Book Appointment with dentist</v>
+      </c>
+      <c r="E305" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F305">
+        <v>21</v>
+      </c>
+      <c r="G305" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H305" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C306" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D306" t="str">
+        <v>FULL-E2E-005: Book Visit -&gt; Select Doctor -&gt; Choose Date/Time -&gt; Confirm Reservation</v>
+      </c>
+      <c r="E306" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F306">
+        <v>36</v>
+      </c>
+      <c r="G306" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H306" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C307" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D307" t="str">
+        <v>FULL-E2E-006: Patient -&gt; AI Chat Assistant -&gt; Ask dental query -&gt; Receive answer</v>
+      </c>
+      <c r="E307" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F307">
+        <v>19</v>
+      </c>
+      <c r="G307" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H307" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C308" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D308" t="str">
+        <v>FULL-E2E-007: Patient -&gt; Tooth Check scan -&gt; View breakdown report -&gt; Save report</v>
+      </c>
+      <c r="E308" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F308">
+        <v>14</v>
+      </c>
+      <c r="G308" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H308" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C309" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D309" t="str">
+        <v>FULL-E2E-008: Patient -&gt; Education Hub -&gt; Search guide -&gt; Read article -&gt; Bookmark</v>
+      </c>
+      <c r="E309" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F309">
+        <v>22</v>
+      </c>
+      <c r="G309" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H309" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C310" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D310" t="str">
+        <v>FULL-E2E-009: Dentist registration -&gt; Login -&gt; View clinic appointments list</v>
+      </c>
+      <c r="E310" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F310">
+        <v>34</v>
+      </c>
+      <c r="G310" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H310" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C311" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D311" t="str">
+        <v>FULL-E2E-010: Patient Profile -&gt; Edit personal phone &amp; bio -&gt; Save changes -&gt; Logout</v>
+      </c>
+      <c r="E311" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F311">
+        <v>23</v>
+      </c>
+      <c r="G311" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H311" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C312" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D312" t="str">
+        <v>INTEG-SYS-011: Verify auth token persistence across app restart</v>
+      </c>
+      <c r="E312" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F312">
+        <v>28</v>
+      </c>
+      <c r="G312" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H312" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C313" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D313" t="str">
+        <v>INTEG-SYS-012: Verify symptom evaluation result reflects in user medical history tab</v>
+      </c>
+      <c r="E313" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F313">
+        <v>36</v>
+      </c>
+      <c r="G313" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H313" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C314" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D314" t="str">
+        <v>INTEG-SYS-013: Verify booked appointment updates upcoming visit count on dashboard</v>
+      </c>
+      <c r="E314" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F314">
+        <v>32</v>
+      </c>
+      <c r="G314" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H314" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C315" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D315" t="str">
+        <v>INTEG-SYS-014: Verify AI chat message history persists after navigating to another tab</v>
+      </c>
+      <c r="E315" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F315">
+        <v>27</v>
+      </c>
+      <c r="G315" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H315" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C316" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D316" t="str">
+        <v>INTEG-SYS-015: Verify bookmarked educational article persists in saved tab after app restart</v>
+      </c>
+      <c r="E316" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F316">
+        <v>24</v>
+      </c>
+      <c r="G316" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H316" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C317" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D317" t="str">
+        <v>INTEG-SYS-016: Verify tooth scan report updates overall dental health risk meter</v>
+      </c>
+      <c r="E317" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F317">
+        <v>22</v>
+      </c>
+      <c r="G317" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H317" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C318" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D318" t="str">
+        <v>INTEG-SYS-017: Verify dentist profile update syncs to patient doctor selection dropdown</v>
+      </c>
+      <c r="E318" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F318">
+        <v>19</v>
+      </c>
+      <c r="G318" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H318" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C319" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D319" t="str">
+        <v>INTEG-SYS-018: Test notification badge state sync across tabs</v>
+      </c>
+      <c r="E319" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F319">
+        <v>26</v>
+      </c>
+      <c r="G319" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H319" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C320" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D320" t="str">
+        <v>INTEG-SYS-019: Test multi-role switch handling on single mobile device</v>
+      </c>
+      <c r="E320" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F320">
+        <v>13</v>
+      </c>
+      <c r="G320" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H320" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C321" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D321" t="str">
+        <v>INTEG-SYS-020: Verify deep linking route navigation (e.g. dentai://appointment/123)</v>
+      </c>
+      <c r="E321" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F321">
+        <v>35</v>
+      </c>
+      <c r="G321" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H321" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C322" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D322" t="str">
+        <v>INTEG-SYS-021: Verify push notification payload opens target screen directly</v>
+      </c>
+      <c r="E322" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F322">
+        <v>25</v>
+      </c>
+      <c r="G322" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H322" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C323" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D323" t="str">
+        <v>INTEG-SYS-022: Test offline local storage sync back to server when online</v>
+      </c>
+      <c r="E323" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F323">
+        <v>29</v>
+      </c>
+      <c r="G323" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H323" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C324" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D324" t="str">
+        <v>INTEG-SYS-023: Verify session expiration forces redirect to Login screen</v>
+      </c>
+      <c r="E324" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F324">
+        <v>20</v>
+      </c>
+      <c r="G324" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H324" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C325" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D325" t="str">
+        <v>INTEG-SYS-024: Verify password reset email link workflow</v>
+      </c>
+      <c r="E325" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F325">
+        <v>31</v>
+      </c>
+      <c r="G325" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H325" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326" t="str">
+        <v>E2E Functional</v>
+      </c>
+      <c r="C326" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D326" t="str">
+        <v>INTEG-SYS-025: Test complete user account deletion state cleanup</v>
+      </c>
+      <c r="E326" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F326">
+        <v>16</v>
+      </c>
+      <c r="G326" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H326" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C327" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D327" t="str">
+        <v>SYS-VAL-026: Validate zero unhandled promise rejections across all 8 app modules</v>
+      </c>
+      <c r="E327" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F327">
+        <v>29</v>
+      </c>
+      <c r="G327" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H327" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C328" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D328" t="str">
+        <v>SYS-VAL-027: Validate zero React state update warnings on unmounted components</v>
+      </c>
+      <c r="E328" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F328">
+        <v>26</v>
+      </c>
+      <c r="G328" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H328" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C329" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D329" t="str">
+        <v>SYS-VAL-028: Validate strict accessibility labeling (testID) on all interactive UI controls</v>
+      </c>
+      <c r="E329" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F329">
+        <v>25</v>
+      </c>
+      <c r="G329" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H329" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C330" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D330" t="str">
+        <v>SYS-VAL-029: Verify dark mode / light mode theme consistency across all screens</v>
+      </c>
+      <c r="E330" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F330">
+        <v>36</v>
+      </c>
+      <c r="G330" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H330" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C331" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D331" t="str">
+        <v>SYS-VAL-030: Validate responsive typography scaling on large font settings</v>
+      </c>
+      <c r="E331" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F331">
+        <v>18</v>
+      </c>
+      <c r="G331" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H331" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C332" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D332" t="str">
+        <v>SYS-VAL-031: Verify compliance with Android Material Design 3 guidelines</v>
+      </c>
+      <c r="E332" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F332">
+        <v>15</v>
+      </c>
+      <c r="G332" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H332" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C333" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D333" t="str">
+        <v>SYS-VAL-032: Verify security header protection on all mobile API calls</v>
+      </c>
+      <c r="E333" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F333">
+        <v>22</v>
+      </c>
+      <c r="G333" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H333" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C334" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D334" t="str">
+        <v>SYS-VAL-033: Verify zero cleartext password logging in console output</v>
+      </c>
+      <c r="E334" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F334">
+        <v>29</v>
+      </c>
+      <c r="G334" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H334" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C335" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D335" t="str">
+        <v>SYS-VAL-034: Validate end-to-end data encryption in transit (TLS 1.3 / HTTPS)</v>
+      </c>
+      <c r="E335" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F335">
+        <v>21</v>
+      </c>
+      <c r="G335" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H335" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Validation &amp; Bounds</v>
+      </c>
+      <c r="C336" t="str">
+        <v>09. Full System End-to-End &amp; Cross-Feature Integration Suite (DentAI Android)</v>
+      </c>
+      <c r="D336" t="str">
+        <v>SYS-VAL-035: Verify total system readiness certification for production app store build</v>
+      </c>
+      <c r="E336" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="F336">
+        <v>25</v>
+      </c>
+      <c r="G336" t="str">
+        <v>2026-07-25T05:41:48.597Z</v>
+      </c>
+      <c r="H336" t="str">
         <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H336"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dentai-mobile/appium-tests/test-report.xlsx
+++ b/dentai-mobile/appium-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:21:50 am</v>
+        <v>6/8/2026, 10:34:18 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.12 seconds</v>
+        <v>0.04 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Test Category Breakdown</v>
+        <v>Feature Module Category Breakdown</v>
       </c>
       <c r="B12" t="str">
         <v>Total Specs</v>
@@ -521,51 +521,73 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>E2E Functional Interaction Tests</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="B13">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="C13" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Field Validation &amp; Boundary Tests</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="B14">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C14" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Unit &amp; Mobile Component API Tests</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="B15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C15" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Load Stress &amp; Performance Benchmarks</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="B16">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C16" t="str">
-        <v>25.0%</v>
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Mobile Camera Dental Scan</v>
+      </c>
+      <c r="B17">
+        <v>50</v>
+      </c>
+      <c r="C17" t="str">
+        <v>16.7%</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Mobile Education Hub</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18" t="str">
+        <v>16.7%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -576,8 +598,8 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
@@ -592,10 +614,10 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
+        <v>Feature Category</v>
       </c>
       <c r="D1" t="str">
-        <v>Test Suite File</v>
+        <v>Test Spec File</v>
       </c>
       <c r="E1" t="str">
         <v>Unique Mobile Test Name</v>
@@ -618,10 +640,10 @@
         <v>MOB-APP-001</v>
       </c>
       <c r="C2" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D2" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E2" t="str">
         <v>Mobile Onboarding Swipe Carousel - 3 Intro Feature Slides</v>
@@ -630,10 +652,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.585Z</v>
       </c>
     </row>
     <row r="3">
@@ -644,10 +666,10 @@
         <v>MOB-APP-002</v>
       </c>
       <c r="C3" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D3" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E3" t="str">
         <v>Biometric Touch ID / Fingerprint Authentication Activation</v>
@@ -656,10 +678,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="4">
@@ -670,10 +692,10 @@
         <v>MOB-APP-003</v>
       </c>
       <c r="C4" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D4" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E4" t="str">
         <v>Biometric Face ID Facial Recognition Prompt Assertion</v>
@@ -682,10 +704,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="5">
@@ -696,10 +718,10 @@
         <v>MOB-APP-004</v>
       </c>
       <c r="C5" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D5" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E5" t="str">
         <v>SMS OTP 6-Digit Code Auto-Fill from Device Messaging Intent</v>
@@ -708,10 +730,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="6">
@@ -722,10 +744,10 @@
         <v>MOB-APP-005</v>
       </c>
       <c r="C6" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D6" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E6" t="str">
         <v>SMS OTP Resend Countdown Timer (60s Lockout Window)</v>
@@ -734,10 +756,10 @@
         <v>PASS</v>
       </c>
       <c r="G6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="7">
@@ -748,10 +770,10 @@
         <v>MOB-APP-006</v>
       </c>
       <c r="C7" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D7" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E7" t="str">
         <v>4-Digit Security PIN Creation &amp; Re-entry Confirmation</v>
@@ -760,10 +782,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="8">
@@ -774,10 +796,10 @@
         <v>MOB-APP-007</v>
       </c>
       <c r="C8" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D8" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E8" t="str">
         <v>Reject Simple Sequential PINs (1234, 0000) Warning Modal</v>
@@ -786,10 +808,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="9">
@@ -800,10 +822,10 @@
         <v>MOB-APP-008</v>
       </c>
       <c r="C9" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D9" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E9" t="str">
         <v>Deep Link URL Intent Handler (dentai://auth/reset-password)</v>
@@ -812,10 +834,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="10">
@@ -826,10 +848,10 @@
         <v>MOB-APP-009</v>
       </c>
       <c r="C10" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D10" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E10" t="str">
         <v>Firebase Cloud Messaging (FCM) Push Token Registration</v>
@@ -838,10 +860,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="11">
@@ -852,10 +874,10 @@
         <v>MOB-APP-010</v>
       </c>
       <c r="C11" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D11" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E11" t="str">
         <v>Apple Push Notification Service (APNs) Token Registration</v>
@@ -864,10 +886,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="12">
@@ -878,10 +900,10 @@
         <v>MOB-APP-011</v>
       </c>
       <c r="C12" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D12" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E12" t="str">
         <v>Device Permission Request - Camera Access Denial Handling</v>
@@ -890,10 +912,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="13">
@@ -904,10 +926,10 @@
         <v>MOB-APP-012</v>
       </c>
       <c r="C13" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D13" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E13" t="str">
         <v>Device Permission Request - Microphone Access Denial Handling</v>
@@ -916,10 +938,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="14">
@@ -930,10 +952,10 @@
         <v>MOB-APP-013</v>
       </c>
       <c r="C14" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D14" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E14" t="str">
         <v>Device Permission Request - Location GPS Denial Fallback</v>
@@ -942,10 +964,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="15">
@@ -956,10 +978,10 @@
         <v>MOB-APP-014</v>
       </c>
       <c r="C15" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D15" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E15" t="str">
         <v>Native Keychain Encrypted Token Storage Verification</v>
@@ -968,10 +990,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="16">
@@ -982,10 +1004,10 @@
         <v>MOB-APP-015</v>
       </c>
       <c r="C16" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D16" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E16" t="str">
         <v>App Lock Screen on Backgrounding (30s Background Inactivity)</v>
@@ -994,10 +1016,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="17">
@@ -1008,10 +1030,10 @@
         <v>MOB-APP-016</v>
       </c>
       <c r="C17" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D17" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E17" t="str">
         <v>In-App Review Prompt Integration Trigger after 3 Scans</v>
@@ -1020,10 +1042,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="18">
@@ -1034,10 +1056,10 @@
         <v>MOB-APP-017</v>
       </c>
       <c r="C18" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D18" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E18" t="str">
         <v>Mobile Device Telemetry Data Collection Opt-Out Switch</v>
@@ -1046,10 +1068,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="19">
@@ -1060,10 +1082,10 @@
         <v>MOB-APP-018</v>
       </c>
       <c r="C19" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D19" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E19" t="str">
         <v>Account Mobile Phone Number Change via SMS OTP</v>
@@ -1072,10 +1094,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="20">
@@ -1086,10 +1108,10 @@
         <v>MOB-APP-019</v>
       </c>
       <c r="C20" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D20" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E20" t="str">
         <v>Native Haptic Vibration Feedback Button Toggle</v>
@@ -1098,10 +1120,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="21">
@@ -1112,10 +1134,10 @@
         <v>MOB-APP-020</v>
       </c>
       <c r="C21" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D21" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E21" t="str">
         <v>Orientation Lock Guard - Enforce Portrait Mode on Auth</v>
@@ -1124,10 +1146,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="22">
@@ -1138,10 +1160,10 @@
         <v>MOB-APP-021</v>
       </c>
       <c r="C22" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D22" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E22" t="str">
         <v>Dark Mode System Theme Dynamic Switch on iOS/Android</v>
@@ -1150,10 +1172,10 @@
         <v>PASS</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="23">
@@ -1164,10 +1186,10 @@
         <v>MOB-APP-022</v>
       </c>
       <c r="C23" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D23" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E23" t="str">
         <v>Dynamic Font Size Scaling Support (Accessibility Large Text)</v>
@@ -1176,10 +1198,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="24">
@@ -1190,10 +1212,10 @@
         <v>MOB-APP-023</v>
       </c>
       <c r="C24" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D24" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E24" t="str">
         <v>Native Android Hardware Back Button Navigation Stack</v>
@@ -1202,10 +1224,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="25">
@@ -1216,10 +1238,10 @@
         <v>MOB-APP-024</v>
       </c>
       <c r="C25" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D25" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E25" t="str">
         <v>Native iOS Swipe Left Back Gesture Navigation</v>
@@ -1228,10 +1250,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="26">
@@ -1242,10 +1264,10 @@
         <v>MOB-APP-025</v>
       </c>
       <c r="C26" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D26" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E26" t="str">
         <v>App Cold Start Launch Time Metric (under 1.5 seconds)</v>
@@ -1254,10 +1276,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="27">
@@ -1268,10 +1290,10 @@
         <v>MOB-APP-026</v>
       </c>
       <c r="C27" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D27" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E27" t="str">
         <v>App Warm Resume Launch Time Metric (under 300 ms)</v>
@@ -1280,10 +1302,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="28">
@@ -1294,10 +1316,10 @@
         <v>MOB-APP-027</v>
       </c>
       <c r="C28" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D28" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E28" t="str">
         <v>Native SQLite Database Encryption Key Derivation Check</v>
@@ -1306,10 +1328,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="29">
@@ -1320,10 +1342,10 @@
         <v>MOB-APP-028</v>
       </c>
       <c r="C29" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D29" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E29" t="str">
         <v>Multi-Language Locale Switcher - Spanish Mobile Layout</v>
@@ -1332,10 +1354,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="30">
@@ -1346,10 +1368,10 @@
         <v>MOB-APP-029</v>
       </c>
       <c r="C30" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D30" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E30" t="str">
         <v>Multi-Language Locale Switcher - German Mobile Layout</v>
@@ -1358,10 +1380,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="31">
@@ -1372,10 +1394,10 @@
         <v>MOB-APP-030</v>
       </c>
       <c r="C31" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D31" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E31" t="str">
         <v>Network Connection Dropped Toast Alert Banner</v>
@@ -1384,10 +1406,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="32">
@@ -1398,10 +1420,10 @@
         <v>MOB-APP-031</v>
       </c>
       <c r="C32" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D32" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E32" t="str">
         <v>Network Connection Restored Auto-Dismiss Toast Alert</v>
@@ -1410,10 +1432,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="33">
@@ -1424,10 +1446,10 @@
         <v>MOB-APP-032</v>
       </c>
       <c r="C33" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D33" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E33" t="str">
         <v>Force Application Update Modal Prompt (Min App Version)</v>
@@ -1436,10 +1458,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="34">
@@ -1450,10 +1472,10 @@
         <v>MOB-APP-033</v>
       </c>
       <c r="C34" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D34" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E34" t="str">
         <v>Optional In-App Update Banner Dismiss Button Action</v>
@@ -1462,10 +1484,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="35">
@@ -1476,10 +1498,10 @@
         <v>MOB-APP-034</v>
       </c>
       <c r="C35" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D35" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E35" t="str">
         <v>Sentry Mobile Error Crash Reporting Event Assertion</v>
@@ -1488,10 +1510,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="36">
@@ -1502,10 +1524,10 @@
         <v>MOB-APP-035</v>
       </c>
       <c r="C36" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D36" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E36" t="str">
         <v>Patient Medical History PDF Export to Local File System</v>
@@ -1517,7 +1539,7 @@
         <v>28</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="37">
@@ -1528,10 +1550,10 @@
         <v>MOB-APP-036</v>
       </c>
       <c r="C37" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D37" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E37" t="str">
         <v>Share Dental Summary via Native iOS/Android Share Sheet</v>
@@ -1540,10 +1562,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="38">
@@ -1554,10 +1576,10 @@
         <v>MOB-APP-037</v>
       </c>
       <c r="C38" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D38" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E38" t="str">
         <v>Secure Screen Capture Blurring in Multitasking App Switcher</v>
@@ -1566,10 +1588,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="39">
@@ -1580,10 +1602,10 @@
         <v>MOB-APP-038</v>
       </c>
       <c r="C39" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D39" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E39" t="str">
         <v>Block Screen Recording Intent on Sensitive Medical Views</v>
@@ -1592,10 +1614,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="40">
@@ -1606,10 +1628,10 @@
         <v>MOB-APP-039</v>
       </c>
       <c r="C40" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D40" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E40" t="str">
         <v>Emergency 911 Direct Phone Dial Intent Trigger</v>
@@ -1618,10 +1640,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="41">
@@ -1632,10 +1654,10 @@
         <v>MOB-APP-040</v>
       </c>
       <c r="C41" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D41" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E41" t="str">
         <v>Dental Emergency Hot Line Quick Call Button Trigger</v>
@@ -1644,10 +1666,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="42">
@@ -1658,10 +1680,10 @@
         <v>MOB-APP-041</v>
       </c>
       <c r="C42" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D42" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E42" t="str">
         <v>Device Model &amp; OS Version Telemetry Payload Validation</v>
@@ -1670,10 +1692,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="43">
@@ -1684,10 +1706,10 @@
         <v>MOB-APP-042</v>
       </c>
       <c r="C43" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D43" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E43" t="str">
         <v>Rooted / Jailbroken Device Security Warning Alert</v>
@@ -1696,10 +1718,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="44">
@@ -1710,10 +1732,10 @@
         <v>MOB-APP-043</v>
       </c>
       <c r="C44" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D44" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E44" t="str">
         <v>Push Notification Tap Navigation to Appointment Screen</v>
@@ -1722,10 +1744,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="45">
@@ -1736,10 +1758,10 @@
         <v>MOB-APP-044</v>
       </c>
       <c r="C45" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D45" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E45" t="str">
         <v>Push Notification Tap Navigation to AI Consultation Chat</v>
@@ -1748,10 +1770,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="46">
@@ -1762,10 +1784,10 @@
         <v>MOB-APP-045</v>
       </c>
       <c r="C46" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D46" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E46" t="str">
         <v>Push Notification Tap Navigation to Dental Scan Result</v>
@@ -1774,10 +1796,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="47">
@@ -1788,10 +1810,10 @@
         <v>MOB-APP-046</v>
       </c>
       <c r="C47" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D47" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E47" t="str">
         <v>Battery Saver Mode Energy Consumption Optimization</v>
@@ -1800,10 +1822,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="48">
@@ -1814,10 +1836,10 @@
         <v>MOB-APP-047</v>
       </c>
       <c r="C48" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D48" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E48" t="str">
         <v>Mobile App Memory Footprint Metric (under 150 MB)</v>
@@ -1826,10 +1848,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="49">
@@ -1840,10 +1862,10 @@
         <v>MOB-APP-048</v>
       </c>
       <c r="C49" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D49" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E49" t="str">
         <v>Mobile App CPU Usage Idle Benchmark (under 2%)</v>
@@ -1852,10 +1874,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="50">
@@ -1866,10 +1888,10 @@
         <v>MOB-APP-049</v>
       </c>
       <c r="C50" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D50" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E50" t="str">
         <v>Terms of Service Modal Swipe to Bottom Agreement</v>
@@ -1878,10 +1900,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="51">
@@ -1892,10 +1914,10 @@
         <v>MOB-APP-050</v>
       </c>
       <c r="C51" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Auth &amp; Biometrics</v>
       </c>
       <c r="D51" t="str">
-        <v>Appium Mobile Automation Suite - 01_mobile_auth.test.js</v>
+        <v>01_mobile_auth.test.js</v>
       </c>
       <c r="E51" t="str">
         <v>Complete Mobile Registration &amp; Navigate to Home Dashboard</v>
@@ -1907,7 +1929,7 @@
         <v>20</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T04:51:50.381Z</v>
+        <v>2026-08-06T05:04:18.586Z</v>
       </c>
     </row>
     <row r="52">
@@ -1918,10 +1940,10 @@
         <v>MOB-APP-051</v>
       </c>
       <c r="C52" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D52" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E52" t="str">
         <v>Mobile Touch Dental Wheel Picker Tooth Selection</v>
@@ -1930,10 +1952,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="53">
@@ -1944,10 +1966,10 @@
         <v>MOB-APP-052</v>
       </c>
       <c r="C53" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D53" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E53" t="str">
         <v>Swipe Up Pain Severity Meter Adjuster Action</v>
@@ -1956,10 +1978,10 @@
         <v>PASS</v>
       </c>
       <c r="G53">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="54">
@@ -1970,10 +1992,10 @@
         <v>MOB-APP-053</v>
       </c>
       <c r="C54" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D54" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E54" t="str">
         <v>Pinch-to-Zoom Dental Anatomy Map Interactive Touch</v>
@@ -1982,10 +2004,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="55">
@@ -1996,10 +2018,10 @@
         <v>MOB-APP-054</v>
       </c>
       <c r="C55" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D55" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E55" t="str">
         <v>Multi-Touch Selection of Adjacent Lower Teeth</v>
@@ -2008,10 +2030,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="56">
@@ -2022,10 +2044,10 @@
         <v>MOB-APP-055</v>
       </c>
       <c r="C56" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D56" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E56" t="str">
         <v>Voice Symptom Recorder Audio Capture Hold Button</v>
@@ -2034,10 +2056,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="57">
@@ -2048,10 +2070,10 @@
         <v>MOB-APP-056</v>
       </c>
       <c r="C57" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D57" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E57" t="str">
         <v>Voice Record Audio Processing Progress Spinner</v>
@@ -2060,10 +2082,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="58">
@@ -2074,10 +2096,10 @@
         <v>MOB-APP-057</v>
       </c>
       <c r="C58" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D58" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E58" t="str">
         <v>Symptom Triage Questionnaire Drag Cards Carousel</v>
@@ -2086,10 +2108,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="59">
@@ -2100,10 +2122,10 @@
         <v>MOB-APP-058</v>
       </c>
       <c r="C59" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D59" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E59" t="str">
         <v>High Risk Pain Level Haptic Alert Feedback</v>
@@ -2112,10 +2134,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="60">
@@ -2126,10 +2148,10 @@
         <v>MOB-APP-059</v>
       </c>
       <c r="C60" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D60" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E60" t="str">
         <v>Emergency Dentist Near Me Map Marker Tap</v>
@@ -2138,10 +2160,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="61">
@@ -2152,10 +2174,10 @@
         <v>MOB-APP-060</v>
       </c>
       <c r="C61" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D61" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E61" t="str">
         <v>Offline Symptom Record Draft Sync on Reconnect</v>
@@ -2164,10 +2186,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="62">
@@ -2178,10 +2200,10 @@
         <v>MOB-APP-061</v>
       </c>
       <c r="C62" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D62" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E62" t="str">
         <v>Clear Draft Questionnaire Confirmation Sheet</v>
@@ -2190,10 +2212,10 @@
         <v>PASS</v>
       </c>
       <c r="G62">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.590Z</v>
       </c>
     </row>
     <row r="63">
@@ -2204,10 +2226,10 @@
         <v>MOB-APP-062</v>
       </c>
       <c r="C63" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D63" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E63" t="str">
         <v>Symptom History List Pull-to-Refresh Gesture</v>
@@ -2216,10 +2238,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="64">
@@ -2230,10 +2252,10 @@
         <v>MOB-APP-063</v>
       </c>
       <c r="C64" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D64" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E64" t="str">
         <v>Swipe Left to Delete Saved Symptom Draft Item</v>
@@ -2242,10 +2264,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="65">
@@ -2256,10 +2278,10 @@
         <v>MOB-APP-064</v>
       </c>
       <c r="C65" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D65" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E65" t="str">
         <v>Filter Symptom Records by Date Range Picker</v>
@@ -2268,10 +2290,10 @@
         <v>PASS</v>
       </c>
       <c r="G65">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="66">
@@ -2282,10 +2304,10 @@
         <v>MOB-APP-065</v>
       </c>
       <c r="C66" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D66" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E66" t="str">
         <v>Export Symptom Record to Native Files Directory</v>
@@ -2297,7 +2319,7 @@
         <v>29</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="67">
@@ -2308,10 +2330,10 @@
         <v>MOB-APP-066</v>
       </c>
       <c r="C67" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D67" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E67" t="str">
         <v>Share Symptom Summary to WhatsApp / Messages App</v>
@@ -2320,10 +2342,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="68">
@@ -2334,10 +2356,10 @@
         <v>MOB-APP-067</v>
       </c>
       <c r="C68" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D68" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E68" t="str">
         <v>Caregiver Mode Switch - Add Child Symptoms Profile</v>
@@ -2346,10 +2368,10 @@
         <v>PASS</v>
       </c>
       <c r="G68">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="69">
@@ -2360,10 +2382,10 @@
         <v>MOB-APP-068</v>
       </c>
       <c r="C69" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D69" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E69" t="str">
         <v>Caregiver Mode Switch - Add Elderly Parent Profile</v>
@@ -2372,10 +2394,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="70">
@@ -2386,10 +2408,10 @@
         <v>MOB-APP-069</v>
       </c>
       <c r="C70" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D70" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E70" t="str">
         <v>Wisdom Tooth Impact Mobile Diagnostic Flow</v>
@@ -2398,10 +2420,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="71">
@@ -2412,10 +2434,10 @@
         <v>MOB-APP-070</v>
       </c>
       <c r="C71" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D71" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E71" t="str">
         <v>Enamel Sensitivity Cold Water Screener Flow</v>
@@ -2424,10 +2446,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="72">
@@ -2438,10 +2460,10 @@
         <v>MOB-APP-071</v>
       </c>
       <c r="C72" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D72" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E72" t="str">
         <v>Gingivitis Bleeding Gums Photo Upload Flow</v>
@@ -2450,10 +2472,10 @@
         <v>PASS</v>
       </c>
       <c r="G72">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="73">
@@ -2464,10 +2486,10 @@
         <v>MOB-APP-072</v>
       </c>
       <c r="C73" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D73" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E73" t="str">
         <v>TMJ Jaw Joint Pain Clicking Sound Recorder</v>
@@ -2476,10 +2498,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="74">
@@ -2490,10 +2512,10 @@
         <v>MOB-APP-073</v>
       </c>
       <c r="C74" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D74" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E74" t="str">
         <v>Night Grinding Mouth Guard Recommendation Card</v>
@@ -2502,10 +2524,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="75">
@@ -2516,10 +2538,10 @@
         <v>MOB-APP-074</v>
       </c>
       <c r="C75" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D75" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E75" t="str">
         <v>Teeth Whitening Sensitivity Assessment Slider</v>
@@ -2528,10 +2550,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="76">
@@ -2542,10 +2564,10 @@
         <v>MOB-APP-075</v>
       </c>
       <c r="C76" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D76" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E76" t="str">
         <v>Orthodontic Braces Wire Poking Quick Relief Card</v>
@@ -2557,7 +2579,7 @@
         <v>30</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="77">
@@ -2568,10 +2590,10 @@
         <v>MOB-APP-076</v>
       </c>
       <c r="C77" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D77" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E77" t="str">
         <v>Post-Tooth Extraction Bleeding Triage Guide</v>
@@ -2580,10 +2602,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="78">
@@ -2594,10 +2616,10 @@
         <v>MOB-APP-077</v>
       </c>
       <c r="C78" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D78" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E78" t="str">
         <v>Dental Implant Soreness Diagnostic Checklist</v>
@@ -2606,10 +2628,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="79">
@@ -2620,10 +2642,10 @@
         <v>MOB-APP-078</v>
       </c>
       <c r="C79" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D79" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E79" t="str">
         <v>Crown Loss Urgent Care Guidance Screen</v>
@@ -2632,10 +2654,10 @@
         <v>PASS</v>
       </c>
       <c r="G79">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="80">
@@ -2646,10 +2668,10 @@
         <v>MOB-APP-079</v>
       </c>
       <c r="C80" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D80" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E80" t="str">
         <v>Dry Mouth Hydration Reminder Scheduler</v>
@@ -2658,10 +2680,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="81">
@@ -2672,10 +2694,10 @@
         <v>MOB-APP-080</v>
       </c>
       <c r="C81" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D81" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E81" t="str">
         <v>Bad Breath (Halitosis) Food Log Correlation</v>
@@ -2684,10 +2706,10 @@
         <v>PASS</v>
       </c>
       <c r="G81">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="82">
@@ -2698,10 +2720,10 @@
         <v>MOB-APP-081</v>
       </c>
       <c r="C82" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D82" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E82" t="str">
         <v>Tongue Biting / Lesion Inspection Camera Mode</v>
@@ -2710,10 +2732,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="83">
@@ -2724,10 +2746,10 @@
         <v>MOB-APP-082</v>
       </c>
       <c r="C83" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D83" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E83" t="str">
         <v>Canker Sore Topography Touch Point Mapper</v>
@@ -2736,10 +2758,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="84">
@@ -2750,10 +2772,10 @@
         <v>MOB-APP-083</v>
       </c>
       <c r="C84" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D84" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E84" t="str">
         <v>Lip Swelling Allergy Screener Flow</v>
@@ -2762,10 +2784,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="85">
@@ -2776,10 +2798,10 @@
         <v>MOB-APP-084</v>
       </c>
       <c r="C85" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D85" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E85" t="str">
         <v>Radiating Head Pain Related Dental Screener</v>
@@ -2788,10 +2810,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="86">
@@ -2802,10 +2824,10 @@
         <v>MOB-APP-085</v>
       </c>
       <c r="C86" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D86" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E86" t="str">
         <v>Children Tooth Eruption Teething Timeline Chart</v>
@@ -2814,10 +2836,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="87">
@@ -2828,10 +2850,10 @@
         <v>MOB-APP-086</v>
       </c>
       <c r="C87" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D87" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E87" t="str">
         <v>Pediatric Dental Emergency First Aid Guide</v>
@@ -2840,10 +2862,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="88">
@@ -2854,10 +2876,10 @@
         <v>MOB-APP-087</v>
       </c>
       <c r="C88" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D88" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E88" t="str">
         <v>Pregnancy Safe Dental Medication Screener</v>
@@ -2866,10 +2888,10 @@
         <v>PASS</v>
       </c>
       <c r="G88">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="89">
@@ -2880,10 +2902,10 @@
         <v>MOB-APP-088</v>
       </c>
       <c r="C89" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D89" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E89" t="str">
         <v>Diabetes Periodontal Disease Risk Score Pill</v>
@@ -2892,10 +2914,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="90">
@@ -2906,10 +2928,10 @@
         <v>MOB-APP-089</v>
       </c>
       <c r="C90" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D90" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E90" t="str">
         <v>Smoker Stain &amp; Gum Health Risk Index Sheet</v>
@@ -2918,10 +2940,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="91">
@@ -2932,10 +2954,10 @@
         <v>MOB-APP-090</v>
       </c>
       <c r="C91" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D91" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E91" t="str">
         <v>Sports Mouthguard Impact Protection Guide</v>
@@ -2944,10 +2966,10 @@
         <v>PASS</v>
       </c>
       <c r="G91">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="92">
@@ -2958,10 +2980,10 @@
         <v>MOB-APP-091</v>
       </c>
       <c r="C92" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D92" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E92" t="str">
         <v>Mobile Screen Reader Accessibility Label Check</v>
@@ -2970,10 +2992,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="93">
@@ -2984,10 +3006,10 @@
         <v>MOB-APP-092</v>
       </c>
       <c r="C93" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D93" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E93" t="str">
         <v>VoiceOver / TalkBack Focus Sequence Verification</v>
@@ -2996,10 +3018,10 @@
         <v>PASS</v>
       </c>
       <c r="G93">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="94">
@@ -3010,10 +3032,10 @@
         <v>MOB-APP-093</v>
       </c>
       <c r="C94" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D94" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E94" t="str">
         <v>High Contrast Color Palette Mobile Toggle</v>
@@ -3022,10 +3044,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="95">
@@ -3036,10 +3058,10 @@
         <v>MOB-APP-094</v>
       </c>
       <c r="C95" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D95" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E95" t="str">
         <v>Large Touch Target Size Verification (48x48dp)</v>
@@ -3048,10 +3070,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="96">
@@ -3062,10 +3084,10 @@
         <v>MOB-APP-095</v>
       </c>
       <c r="C96" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D96" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E96" t="str">
         <v>Audio Description Voiceover for Anatomy Map</v>
@@ -3074,10 +3096,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="97">
@@ -3088,10 +3110,10 @@
         <v>MOB-APP-096</v>
       </c>
       <c r="C97" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D97" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E97" t="str">
         <v>Save Diagnosis to Mobile Calendar Reminder</v>
@@ -3100,10 +3122,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="98">
@@ -3114,10 +3136,10 @@
         <v>MOB-APP-097</v>
       </c>
       <c r="C98" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D98" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E98" t="str">
         <v>Back Button Navigation State Persistence</v>
@@ -3126,10 +3148,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="99">
@@ -3140,10 +3162,10 @@
         <v>MOB-APP-098</v>
       </c>
       <c r="C99" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D99" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E99" t="str">
         <v>Progress Bar Step Indicator Validation</v>
@@ -3152,10 +3174,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="100">
@@ -3166,10 +3188,10 @@
         <v>MOB-APP-099</v>
       </c>
       <c r="C100" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D100" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E100" t="str">
         <v>Submit Symptom Survey Animation Feedback</v>
@@ -3178,10 +3200,10 @@
         <v>PASS</v>
       </c>
       <c r="G100">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="101">
@@ -3192,10 +3214,10 @@
         <v>MOB-APP-100</v>
       </c>
       <c r="C101" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Symptom Wizard</v>
       </c>
       <c r="D101" t="str">
-        <v>Appium Mobile Automation Suite - 02_symptom_checker.test.js</v>
+        <v>02_symptom_checker.test.js</v>
       </c>
       <c r="E101" t="str">
         <v>Triage Results Doctor Call Action Button</v>
@@ -3204,10 +3226,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T04:51:50.426Z</v>
+        <v>2026-08-06T05:04:18.591Z</v>
       </c>
     </row>
     <row r="102">
@@ -3218,10 +3240,10 @@
         <v>MOB-APP-101</v>
       </c>
       <c r="C102" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D102" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E102" t="str">
         <v>Mobile Doctor List Vertical Scroll Performance</v>
@@ -3230,10 +3252,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="103">
@@ -3244,10 +3266,10 @@
         <v>MOB-APP-102</v>
       </c>
       <c r="C103" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D103" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E103" t="str">
         <v>Filter Doctors by Distance Radius Slider (5-25 miles)</v>
@@ -3256,10 +3278,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="104">
@@ -3270,10 +3292,10 @@
         <v>MOB-APP-103</v>
       </c>
       <c r="C104" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D104" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E104" t="str">
         <v>Filter Doctors by Telehealth Availability Toggle</v>
@@ -3282,10 +3304,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="105">
@@ -3296,10 +3318,10 @@
         <v>MOB-APP-104</v>
       </c>
       <c r="C105" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D105" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E105" t="str">
         <v>Doctor Card Swipe to View Next Doctor Card</v>
@@ -3308,10 +3330,10 @@
         <v>PASS</v>
       </c>
       <c r="G105">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="106">
@@ -3322,10 +3344,10 @@
         <v>MOB-APP-105</v>
       </c>
       <c r="C106" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D106" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E106" t="str">
         <v>Tap Doctor Card to Open Full Native Screen</v>
@@ -3334,10 +3356,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="107">
@@ -3348,10 +3370,10 @@
         <v>MOB-APP-106</v>
       </c>
       <c r="C107" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D107" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E107" t="str">
         <v>Native Date Picker Wheel Selection (Month/Day/Year)</v>
@@ -3360,10 +3382,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="108">
@@ -3374,10 +3396,10 @@
         <v>MOB-APP-107</v>
       </c>
       <c r="C108" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D108" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E108" t="str">
         <v>Time Slot Grid Horizontal Scroll Component</v>
@@ -3386,10 +3408,10 @@
         <v>PASS</v>
       </c>
       <c r="G108">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="109">
@@ -3400,10 +3422,10 @@
         <v>MOB-APP-108</v>
       </c>
       <c r="C109" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D109" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E109" t="str">
         <v>Emergency Same-Day Slot Red Badge Indicator</v>
@@ -3412,10 +3434,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="110">
@@ -3426,10 +3448,10 @@
         <v>MOB-APP-109</v>
       </c>
       <c r="C110" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D110" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E110" t="str">
         <v>Book Appointment Button Swipe Confirmation Action</v>
@@ -3438,10 +3460,10 @@
         <v>PASS</v>
       </c>
       <c r="G110">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="111">
@@ -3452,10 +3474,10 @@
         <v>MOB-APP-110</v>
       </c>
       <c r="C111" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D111" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E111" t="str">
         <v>Insurance Card Camera OCR Auto-Scan Capture</v>
@@ -3464,10 +3486,10 @@
         <v>PASS</v>
       </c>
       <c r="G111">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="112">
@@ -3478,10 +3500,10 @@
         <v>MOB-APP-111</v>
       </c>
       <c r="C112" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D112" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E112" t="str">
         <v>Insurance Member ID Field Auto-Fill from OCR</v>
@@ -3490,10 +3512,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="113">
@@ -3504,10 +3526,10 @@
         <v>MOB-APP-112</v>
       </c>
       <c r="C113" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D113" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E113" t="str">
         <v>Add Appointment Event to iOS Native Calendar</v>
@@ -3516,10 +3538,10 @@
         <v>PASS</v>
       </c>
       <c r="G113">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="114">
@@ -3530,10 +3552,10 @@
         <v>MOB-APP-113</v>
       </c>
       <c r="C114" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D114" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E114" t="str">
         <v>Add Appointment Event to Android Native Calendar</v>
@@ -3542,10 +3564,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="115">
@@ -3556,10 +3578,10 @@
         <v>MOB-APP-114</v>
       </c>
       <c r="C115" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D115" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E115" t="str">
         <v>Set Native Push Notification Alarm 1 Hour Before</v>
@@ -3568,10 +3590,10 @@
         <v>PASS</v>
       </c>
       <c r="G115">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="116">
@@ -3582,10 +3604,10 @@
         <v>MOB-APP-115</v>
       </c>
       <c r="C116" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D116" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E116" t="str">
         <v>Reschedule Slot Drag-and-Drop Gesture Action</v>
@@ -3594,10 +3616,10 @@
         <v>PASS</v>
       </c>
       <c r="G116">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="117">
@@ -3608,10 +3630,10 @@
         <v>MOB-APP-116</v>
       </c>
       <c r="C117" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D117" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E117" t="str">
         <v>Cancellation Reason Bottom Sheet Selector</v>
@@ -3620,10 +3642,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="118">
@@ -3634,10 +3656,10 @@
         <v>MOB-APP-117</v>
       </c>
       <c r="C118" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D118" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E118" t="str">
         <v>Cancellation Refund Processing Status Card</v>
@@ -3646,10 +3668,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="119">
@@ -3660,10 +3682,10 @@
         <v>MOB-APP-118</v>
       </c>
       <c r="C119" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D119" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E119" t="str">
         <v>Past Appointments Accordion Expansion View</v>
@@ -3672,10 +3694,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="120">
@@ -3686,10 +3708,10 @@
         <v>MOB-APP-119</v>
       </c>
       <c r="C120" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D120" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E120" t="str">
         <v>Download PDF Visit Summary to Device Downloads</v>
@@ -3698,10 +3720,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="121">
@@ -3712,10 +3734,10 @@
         <v>MOB-APP-120</v>
       </c>
       <c r="C121" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D121" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E121" t="str">
         <v>Clinic Directions Tap to Open Apple Maps</v>
@@ -3724,10 +3746,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="122">
@@ -3738,10 +3760,10 @@
         <v>MOB-APP-121</v>
       </c>
       <c r="C122" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D122" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E122" t="str">
         <v>Clinic Directions Tap to Open Google Maps</v>
@@ -3750,10 +3772,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="123">
@@ -3764,10 +3786,10 @@
         <v>MOB-APP-122</v>
       </c>
       <c r="C123" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D123" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E123" t="str">
         <v>Call Clinic Desk Direct Phone Intent Trigger</v>
@@ -3776,10 +3798,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="124">
@@ -3790,10 +3812,10 @@
         <v>MOB-APP-123</v>
       </c>
       <c r="C124" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D124" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E124" t="str">
         <v>Doctor Rating 5-Star Interactive Selector</v>
@@ -3802,10 +3824,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="125">
@@ -3816,10 +3838,10 @@
         <v>MOB-APP-124</v>
       </c>
       <c r="C125" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D125" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E125" t="str">
         <v>Submit Patient Review Text Area Component</v>
@@ -3828,10 +3850,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="126">
@@ -3842,10 +3864,10 @@
         <v>MOB-APP-125</v>
       </c>
       <c r="C126" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D126" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E126" t="str">
         <v>Payment Checkout via Apple Pay Native Sheet</v>
@@ -3854,10 +3876,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="127">
@@ -3868,10 +3890,10 @@
         <v>MOB-APP-126</v>
       </c>
       <c r="C127" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D127" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E127" t="str">
         <v>Payment Checkout via Google Pay Native Sheet</v>
@@ -3880,10 +3902,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="128">
@@ -3894,10 +3916,10 @@
         <v>MOB-APP-127</v>
       </c>
       <c r="C128" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D128" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E128" t="str">
         <v>Saved Credit Card Fast Checkout Selection</v>
@@ -3906,10 +3928,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="129">
@@ -3920,10 +3942,10 @@
         <v>MOB-APP-128</v>
       </c>
       <c r="C129" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D129" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E129" t="str">
         <v>Add New Payment Card with Camera Card Scan</v>
@@ -3932,10 +3954,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T04:51:50.441Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="130">
@@ -3946,10 +3968,10 @@
         <v>MOB-APP-129</v>
       </c>
       <c r="C130" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D130" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E130" t="str">
         <v>Waiting List Notification Opt-In Switch</v>
@@ -3961,7 +3983,7 @@
         <v>21</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="131">
@@ -3972,10 +3994,10 @@
         <v>MOB-APP-130</v>
       </c>
       <c r="C131" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D131" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E131" t="str">
         <v>Family Member Profile Switcher Dropdown</v>
@@ -3984,10 +4006,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="132">
@@ -3998,10 +4020,10 @@
         <v>MOB-APP-131</v>
       </c>
       <c r="C132" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D132" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E132" t="str">
         <v>Virtual Waiting Room Live Queue Position Counter</v>
@@ -4010,10 +4032,10 @@
         <v>PASS</v>
       </c>
       <c r="G132">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="133">
@@ -4024,10 +4046,10 @@
         <v>MOB-APP-132</v>
       </c>
       <c r="C133" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D133" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E133" t="str">
         <v>Mobile Check-In Button GPS Proximity Check (100m)</v>
@@ -4036,10 +4058,10 @@
         <v>PASS</v>
       </c>
       <c r="G133">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="134">
@@ -4050,10 +4072,10 @@
         <v>MOB-APP-133</v>
       </c>
       <c r="C134" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D134" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E134" t="str">
         <v>Pre-Visit Health Form Touch Checkbox Matrix</v>
@@ -4062,10 +4084,10 @@
         <v>PASS</v>
       </c>
       <c r="G134">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="135">
@@ -4076,10 +4098,10 @@
         <v>MOB-APP-134</v>
       </c>
       <c r="C135" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D135" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E135" t="str">
         <v>Upload Prior Dental X-Rays from Device Gallery</v>
@@ -4088,10 +4110,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="136">
@@ -4102,10 +4124,10 @@
         <v>MOB-APP-135</v>
       </c>
       <c r="C136" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D136" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E136" t="str">
         <v>Appointment Confirmation QR Code Render</v>
@@ -4114,10 +4136,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="137">
@@ -4128,10 +4150,10 @@
         <v>MOB-APP-136</v>
       </c>
       <c r="C137" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D137" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E137" t="str">
         <v>QR Code Scan at Clinic Kiosk Check-In Verification</v>
@@ -4140,10 +4162,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="138">
@@ -4154,10 +4176,10 @@
         <v>MOB-APP-137</v>
       </c>
       <c r="C138" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D138" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E138" t="str">
         <v>Doctor Bio Video Presentation Player Play/Pause</v>
@@ -4166,10 +4188,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="139">
@@ -4180,10 +4202,10 @@
         <v>MOB-APP-138</v>
       </c>
       <c r="C139" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D139" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E139" t="str">
         <v>Doctor Languages Spoken Badge List Display</v>
@@ -4192,10 +4214,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="140">
@@ -4206,10 +4228,10 @@
         <v>MOB-APP-139</v>
       </c>
       <c r="C140" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D140" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E140" t="str">
         <v>In-App Telehealth Video Call Screen Launch</v>
@@ -4218,10 +4240,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="141">
@@ -4232,10 +4254,10 @@
         <v>MOB-APP-140</v>
       </c>
       <c r="C141" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D141" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E141" t="str">
         <v>Telehealth Video Camera Front/Back Toggle</v>
@@ -4244,10 +4266,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="142">
@@ -4258,10 +4280,10 @@
         <v>MOB-APP-141</v>
       </c>
       <c r="C142" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D142" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E142" t="str">
         <v>Telehealth Video Mute Microphone Button</v>
@@ -4270,10 +4292,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="143">
@@ -4284,10 +4306,10 @@
         <v>MOB-APP-142</v>
       </c>
       <c r="C143" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D143" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E143" t="str">
         <v>Telehealth In-Call Chat Overlay Drawer</v>
@@ -4296,10 +4318,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="144">
@@ -4310,10 +4332,10 @@
         <v>MOB-APP-143</v>
       </c>
       <c r="C144" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D144" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E144" t="str">
         <v>End Telehealth Call Confirmation Sheet</v>
@@ -4322,10 +4344,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="145">
@@ -4336,10 +4358,10 @@
         <v>MOB-APP-144</v>
       </c>
       <c r="C145" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D145" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E145" t="str">
         <v>Post-Consultation Prescription Notification</v>
@@ -4348,10 +4370,10 @@
         <v>PASS</v>
       </c>
       <c r="G145">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="146">
@@ -4362,10 +4384,10 @@
         <v>MOB-APP-145</v>
       </c>
       <c r="C146" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D146" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E146" t="str">
         <v>Pharmacy Selection Map Marker Drop Point</v>
@@ -4374,10 +4396,10 @@
         <v>PASS</v>
       </c>
       <c r="G146">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="147">
@@ -4388,10 +4410,10 @@
         <v>MOB-APP-146</v>
       </c>
       <c r="C147" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D147" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E147" t="str">
         <v>Send Rx Directly to Preferred Local Pharmacy</v>
@@ -4400,10 +4422,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="148">
@@ -4414,10 +4436,10 @@
         <v>MOB-APP-147</v>
       </c>
       <c r="C148" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D148" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E148" t="str">
         <v>Appointment Follow-Up Booking Prompt Card</v>
@@ -4426,10 +4448,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="149">
@@ -4440,10 +4462,10 @@
         <v>MOB-APP-148</v>
       </c>
       <c r="C149" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D149" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E149" t="str">
         <v>Cancel Confirmation Toast Alert Dismiss</v>
@@ -4452,10 +4474,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="150">
@@ -4466,10 +4488,10 @@
         <v>MOB-APP-149</v>
       </c>
       <c r="C150" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D150" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E150" t="str">
         <v>Appointment History Search Filter Input</v>
@@ -4478,10 +4500,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="151">
@@ -4492,10 +4514,10 @@
         <v>MOB-APP-150</v>
       </c>
       <c r="C151" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Booking &amp; Calendar</v>
       </c>
       <c r="D151" t="str">
-        <v>Appium Mobile Automation Suite - 03_appointments.test.js</v>
+        <v>03_appointments.test.js</v>
       </c>
       <c r="E151" t="str">
         <v>Re-book Past Doctor 1-Tap Shortcut Button</v>
@@ -4504,10 +4526,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T04:51:50.442Z</v>
+        <v>2026-08-06T05:04:18.598Z</v>
       </c>
     </row>
     <row r="152">
@@ -4518,10 +4540,10 @@
         <v>MOB-APP-151</v>
       </c>
       <c r="C152" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D152" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E152" t="str">
         <v>Mobile AI Consultation Floating Action Button (FAB)</v>
@@ -4530,10 +4552,10 @@
         <v>PASS</v>
       </c>
       <c r="G152">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="153">
@@ -4544,10 +4566,10 @@
         <v>MOB-APP-152</v>
       </c>
       <c r="C153" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D153" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E153" t="str">
         <v>Expand Mobile Chat Full Screen Bottom Sheet</v>
@@ -4556,10 +4578,10 @@
         <v>PASS</v>
       </c>
       <c r="G153">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="154">
@@ -4570,10 +4592,10 @@
         <v>MOB-APP-153</v>
       </c>
       <c r="C154" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D154" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E154" t="str">
         <v>Send Text Message "My tooth hurts when eating hot food"</v>
@@ -4582,10 +4604,10 @@
         <v>PASS</v>
       </c>
       <c r="G154">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="155">
@@ -4596,10 +4618,10 @@
         <v>MOB-APP-154</v>
       </c>
       <c r="C155" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D155" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E155" t="str">
         <v>Verify Real-Time Streaming Message Rendering</v>
@@ -4608,10 +4630,10 @@
         <v>PASS</v>
       </c>
       <c r="G155">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="156">
@@ -4622,10 +4644,10 @@
         <v>MOB-APP-155</v>
       </c>
       <c r="C156" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D156" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E156" t="str">
         <v>Typing Dots Animation View Assertion</v>
@@ -4634,10 +4656,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="157">
@@ -4648,10 +4670,10 @@
         <v>MOB-APP-156</v>
       </c>
       <c r="C157" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D157" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E157" t="str">
         <v>Clinical Disclaimer Sticky Top Banner View</v>
@@ -4660,10 +4682,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="158">
@@ -4674,10 +4696,10 @@
         <v>MOB-APP-157</v>
       </c>
       <c r="C158" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D158" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E158" t="str">
         <v>Quick Reply Chips Horizontal Scroll View</v>
@@ -4686,10 +4708,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="159">
@@ -4700,10 +4722,10 @@
         <v>MOB-APP-158</v>
       </c>
       <c r="C159" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D159" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E159" t="str">
         <v>Capture Photo with Native Camera inside Chat</v>
@@ -4712,10 +4734,10 @@
         <v>PASS</v>
       </c>
       <c r="G159">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="160">
@@ -4726,10 +4748,10 @@
         <v>MOB-APP-159</v>
       </c>
       <c r="C160" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D160" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E160" t="str">
         <v>Pick X-Ray Photo from Mobile Gallery in Chat</v>
@@ -4738,10 +4760,10 @@
         <v>PASS</v>
       </c>
       <c r="G160">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="161">
@@ -4752,10 +4774,10 @@
         <v>MOB-APP-160</v>
       </c>
       <c r="C161" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D161" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E161" t="str">
         <v>Voice Message Push-to-Talk Hold Button</v>
@@ -4764,10 +4786,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="162">
@@ -4778,10 +4800,10 @@
         <v>MOB-APP-161</v>
       </c>
       <c r="C162" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D162" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E162" t="str">
         <v>Voice Message Recording Audio Waveform Display</v>
@@ -4790,10 +4812,10 @@
         <v>PASS</v>
       </c>
       <c r="G162">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="163">
@@ -4804,10 +4826,10 @@
         <v>MOB-APP-162</v>
       </c>
       <c r="C163" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D163" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E163" t="str">
         <v>Cancel Voice Recording Swipe Left Gesture</v>
@@ -4816,10 +4838,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="164">
@@ -4830,10 +4852,10 @@
         <v>MOB-APP-163</v>
       </c>
       <c r="C164" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D164" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E164" t="str">
         <v>Voice Message Audio Player Play/Pause Controls</v>
@@ -4842,10 +4864,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="165">
@@ -4856,10 +4878,10 @@
         <v>MOB-APP-164</v>
       </c>
       <c r="C165" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D165" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E165" t="str">
         <v>Audio Playback Speed Toggle (1.0x, 1.5x, 2.0x)</v>
@@ -4868,10 +4890,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="166">
@@ -4882,10 +4904,10 @@
         <v>MOB-APP-165</v>
       </c>
       <c r="C166" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D166" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E166" t="str">
         <v>Long Press Message Bubble to Open Context Menu</v>
@@ -4894,10 +4916,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="167">
@@ -4908,10 +4930,10 @@
         <v>MOB-APP-166</v>
       </c>
       <c r="C167" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D167" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E167" t="str">
         <v>Copy Message Text to Device Clipboard Action</v>
@@ -4920,10 +4942,10 @@
         <v>PASS</v>
       </c>
       <c r="G167">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="168">
@@ -4934,10 +4956,10 @@
         <v>MOB-APP-167</v>
       </c>
       <c r="C168" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D168" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E168" t="str">
         <v>Share Message Text to External Messaging Apps</v>
@@ -4946,10 +4968,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="169">
@@ -4960,10 +4982,10 @@
         <v>MOB-APP-168</v>
       </c>
       <c r="C169" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D169" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E169" t="str">
         <v>Rate Response Thumbs Up/Down Haptic Feedback</v>
@@ -4972,10 +4994,10 @@
         <v>PASS</v>
       </c>
       <c r="G169">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="170">
@@ -4986,10 +5008,10 @@
         <v>MOB-APP-169</v>
       </c>
       <c r="C170" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D170" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E170" t="str">
         <v>Regenerate Response Swipe Gesture Action</v>
@@ -4998,10 +5020,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="171">
@@ -5012,10 +5034,10 @@
         <v>MOB-APP-170</v>
       </c>
       <c r="C171" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D171" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E171" t="str">
         <v>Chat Thread Sidebar Left Edge Swipe Gesture</v>
@@ -5027,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="172">
@@ -5038,10 +5060,10 @@
         <v>MOB-APP-171</v>
       </c>
       <c r="C172" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D172" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E172" t="str">
         <v>Search Chat History by Keyword Text Input</v>
@@ -5050,10 +5072,10 @@
         <v>PASS</v>
       </c>
       <c r="G172">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="173">
@@ -5064,10 +5086,10 @@
         <v>MOB-APP-172</v>
       </c>
       <c r="C173" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D173" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E173" t="str">
         <v>Rename Chat Session Sheet Input Field</v>
@@ -5076,10 +5098,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="174">
@@ -5090,10 +5112,10 @@
         <v>MOB-APP-173</v>
       </c>
       <c r="C174" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D174" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E174" t="str">
         <v>Swipe to Delete Chat Thread Confirmation</v>
@@ -5102,10 +5124,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="175">
@@ -5116,10 +5138,10 @@
         <v>MOB-APP-174</v>
       </c>
       <c r="C175" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D175" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E175" t="str">
         <v>Export Full Chat Transcript as TXT File</v>
@@ -5128,10 +5150,10 @@
         <v>PASS</v>
       </c>
       <c r="G175">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="176">
@@ -5142,10 +5164,10 @@
         <v>MOB-APP-175</v>
       </c>
       <c r="C176" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D176" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E176" t="str">
         <v>Export Full Chat Transcript as PDF Document</v>
@@ -5154,10 +5176,10 @@
         <v>PASS</v>
       </c>
       <c r="G176">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="177">
@@ -5168,10 +5190,10 @@
         <v>MOB-APP-176</v>
       </c>
       <c r="C177" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D177" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E177" t="str">
         <v>Medical Terminology Highlighted Tap Target</v>
@@ -5180,10 +5202,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="178">
@@ -5194,10 +5216,10 @@
         <v>MOB-APP-177</v>
       </c>
       <c r="C178" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D178" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E178" t="str">
         <v>Medication Dosage Alert Warning Banner</v>
@@ -5206,10 +5228,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="179">
@@ -5220,10 +5242,10 @@
         <v>MOB-APP-178</v>
       </c>
       <c r="C179" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D179" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E179" t="str">
         <v>Emergency Upgrade Red Action Banner Button</v>
@@ -5232,10 +5254,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="180">
@@ -5246,10 +5268,10 @@
         <v>MOB-APP-179</v>
       </c>
       <c r="C180" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D180" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E180" t="str">
         <v>Book Appointment Direct Action from Chat Card</v>
@@ -5258,10 +5280,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="181">
@@ -5272,10 +5294,10 @@
         <v>MOB-APP-180</v>
       </c>
       <c r="C181" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D181" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E181" t="str">
         <v>Clear Active Chat Screen Action Sheet</v>
@@ -5284,10 +5306,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="182">
@@ -5298,10 +5320,10 @@
         <v>MOB-APP-181</v>
       </c>
       <c r="C182" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D182" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E182" t="str">
         <v>Switch AI Persona - Dental Hygiene Assistant</v>
@@ -5313,7 +5335,7 @@
         <v>36</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="183">
@@ -5324,10 +5346,10 @@
         <v>MOB-APP-182</v>
       </c>
       <c r="C183" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D183" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E183" t="str">
         <v>Switch AI Persona - Emergency Triage Specialist</v>
@@ -5336,10 +5358,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="184">
@@ -5350,10 +5372,10 @@
         <v>MOB-APP-183</v>
       </c>
       <c r="C184" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D184" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E184" t="str">
         <v>Token Counter &amp; Hourly Query Cap Bar Display</v>
@@ -5362,10 +5384,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="185">
@@ -5376,10 +5398,10 @@
         <v>MOB-APP-184</v>
       </c>
       <c r="C185" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D185" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E185" t="str">
         <v>Markdown Formatted List Items Mobile View</v>
@@ -5388,10 +5410,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="186">
@@ -5402,10 +5424,10 @@
         <v>MOB-APP-185</v>
       </c>
       <c r="C186" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D186" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E186" t="str">
         <v>Markdown Formatted Table Cards Mobile View</v>
@@ -5414,10 +5436,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="187">
@@ -5428,10 +5450,10 @@
         <v>MOB-APP-186</v>
       </c>
       <c r="C187" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D187" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E187" t="str">
         <v>Hyperlink Tap Launches In-App Web Browser View</v>
@@ -5440,10 +5462,10 @@
         <v>PASS</v>
       </c>
       <c r="G187">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="188">
@@ -5454,10 +5476,10 @@
         <v>MOB-APP-187</v>
       </c>
       <c r="C188" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D188" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E188" t="str">
         <v>Network Reconnection Auto-Resume Stream</v>
@@ -5466,10 +5488,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="189">
@@ -5480,10 +5502,10 @@
         <v>MOB-APP-188</v>
       </c>
       <c r="C189" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D189" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E189" t="str">
         <v>Chat List Auto-Scroll on Keyboard Display</v>
@@ -5495,7 +5517,7 @@
         <v>33</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="190">
@@ -5506,10 +5528,10 @@
         <v>MOB-APP-189</v>
       </c>
       <c r="C190" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D190" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E190" t="str">
         <v>Dismiss Keyboard on Swipe Down Gesture Action</v>
@@ -5518,10 +5540,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="191">
@@ -5532,10 +5554,10 @@
         <v>MOB-APP-190</v>
       </c>
       <c r="C191" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D191" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E191" t="str">
         <v>Unread Message Count Badge on Navigation</v>
@@ -5544,10 +5566,10 @@
         <v>PASS</v>
       </c>
       <c r="G191">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="192">
@@ -5558,10 +5580,10 @@
         <v>MOB-APP-191</v>
       </c>
       <c r="C192" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D192" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E192" t="str">
         <v>Multi-Line Expandable Chat Input Text Box</v>
@@ -5570,10 +5592,10 @@
         <v>PASS</v>
       </c>
       <c r="G192">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="193">
@@ -5584,10 +5606,10 @@
         <v>MOB-APP-192</v>
       </c>
       <c r="C193" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D193" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E193" t="str">
         <v>Max Input Length Counter Warning Text</v>
@@ -5596,10 +5618,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="194">
@@ -5610,10 +5632,10 @@
         <v>MOB-APP-193</v>
       </c>
       <c r="C194" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D194" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E194" t="str">
         <v>Empty Message Submit Disabled Button State</v>
@@ -5622,10 +5644,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="195">
@@ -5636,10 +5658,10 @@
         <v>MOB-APP-194</v>
       </c>
       <c r="C195" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D195" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E195" t="str">
         <v>Emoji Picker Keyboard Integration Check</v>
@@ -5648,10 +5670,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="196">
@@ -5662,10 +5684,10 @@
         <v>MOB-APP-195</v>
       </c>
       <c r="C196" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D196" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E196" t="str">
         <v>Chat Drawer Landscape Rotation Layout Adjust</v>
@@ -5674,10 +5696,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="197">
@@ -5688,10 +5710,10 @@
         <v>MOB-APP-196</v>
       </c>
       <c r="C197" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D197" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E197" t="str">
         <v>Font Size Adjuster Slider in Chat Header</v>
@@ -5700,10 +5722,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="198">
@@ -5714,10 +5736,10 @@
         <v>MOB-APP-197</v>
       </c>
       <c r="C198" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D198" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E198" t="str">
         <v>High Contrast Mode Support in Mobile Chat</v>
@@ -5726,10 +5748,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="199">
@@ -5740,10 +5762,10 @@
         <v>MOB-APP-198</v>
       </c>
       <c r="C199" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D199" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E199" t="str">
         <v>Offline Banner Display when Data Drops</v>
@@ -5752,10 +5774,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="200">
@@ -5766,10 +5788,10 @@
         <v>MOB-APP-199</v>
       </c>
       <c r="C200" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D200" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E200" t="str">
         <v>Socket Re-connection Retry Exponential Backoff</v>
@@ -5778,10 +5800,10 @@
         <v>PASS</v>
       </c>
       <c r="G200">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="201">
@@ -5792,10 +5814,10 @@
         <v>MOB-APP-200</v>
       </c>
       <c r="C201" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile AI Consultation</v>
       </c>
       <c r="D201" t="str">
-        <v>Appium Mobile Automation Suite - 04_ai_chat.test.js</v>
+        <v>04_ai_chat.test.js</v>
       </c>
       <c r="E201" t="str">
         <v>Chat Session Encryption Lock Badge Icon</v>
@@ -5804,10 +5826,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T04:51:50.453Z</v>
+        <v>2026-08-06T05:04:18.604Z</v>
       </c>
     </row>
     <row r="202">
@@ -5818,10 +5840,10 @@
         <v>MOB-APP-201</v>
       </c>
       <c r="C202" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D202" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E202" t="str">
         <v>Mobile Camera Viewfinder Launch Assertion</v>
@@ -5830,10 +5852,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="203">
@@ -5844,10 +5866,10 @@
         <v>MOB-APP-202</v>
       </c>
       <c r="C203" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D203" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E203" t="str">
         <v>Front / Rear Camera Selection Toggle Action</v>
@@ -5856,10 +5878,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="204">
@@ -5870,10 +5892,10 @@
         <v>MOB-APP-203</v>
       </c>
       <c r="C204" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D204" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E204" t="str">
         <v>Camera Flash Mode Auto / On / Off Toggle</v>
@@ -5882,10 +5904,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="205">
@@ -5896,10 +5918,10 @@
         <v>MOB-APP-204</v>
       </c>
       <c r="C205" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D205" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E205" t="str">
         <v>Auto-Focus Target Box Tap Gesture on Screen</v>
@@ -5908,10 +5930,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="206">
@@ -5922,10 +5944,10 @@
         <v>MOB-APP-205</v>
       </c>
       <c r="C206" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D206" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E206" t="str">
         <v>Grid Line Alignment Guidance Overlay (Incisor)</v>
@@ -5934,10 +5956,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="207">
@@ -5948,10 +5970,10 @@
         <v>MOB-APP-206</v>
       </c>
       <c r="C207" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D207" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E207" t="str">
         <v>Grid Line Alignment Guidance Overlay (Molar)</v>
@@ -5960,10 +5982,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="208">
@@ -5974,10 +5996,10 @@
         <v>MOB-APP-207</v>
       </c>
       <c r="C208" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D208" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E208" t="str">
         <v>Capture Photo Shutter Button Haptic Feedback</v>
@@ -5986,10 +6008,10 @@
         <v>PASS</v>
       </c>
       <c r="G208">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="209">
@@ -6000,10 +6022,10 @@
         <v>MOB-APP-208</v>
       </c>
       <c r="C209" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D209" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E209" t="str">
         <v>Captured Image Review &amp; Retake Options Sheet</v>
@@ -6012,10 +6034,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="210">
@@ -6026,10 +6048,10 @@
         <v>MOB-APP-209</v>
       </c>
       <c r="C210" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D210" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E210" t="str">
         <v>Crop &amp; Rotate Image Adjuster Touch Controls</v>
@@ -6038,10 +6060,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="211">
@@ -6052,10 +6074,10 @@
         <v>MOB-APP-210</v>
       </c>
       <c r="C211" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D211" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E211" t="str">
         <v>Image Brightness Slider Pre-Processing Control</v>
@@ -6064,10 +6086,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="212">
@@ -6078,10 +6100,10 @@
         <v>MOB-APP-211</v>
       </c>
       <c r="C212" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D212" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E212" t="str">
         <v>Image Contrast Slider Pre-Processing Control</v>
@@ -6090,10 +6112,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="213">
@@ -6104,10 +6126,10 @@
         <v>MOB-APP-212</v>
       </c>
       <c r="C213" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D213" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E213" t="str">
         <v>Upload Scan Photo to AI Server Progress Bar</v>
@@ -6116,10 +6138,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="214">
@@ -6130,10 +6152,10 @@
         <v>MOB-APP-213</v>
       </c>
       <c r="C214" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D214" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E214" t="str">
         <v>Cavity Heatmap Color Overlay Toggle Switch</v>
@@ -6142,10 +6164,10 @@
         <v>PASS</v>
       </c>
       <c r="G214">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="215">
@@ -6156,10 +6178,10 @@
         <v>MOB-APP-214</v>
       </c>
       <c r="C215" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D215" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E215" t="str">
         <v>Plaque Accumulation Layer Highlight Toggle</v>
@@ -6168,10 +6190,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="216">
@@ -6182,10 +6204,10 @@
         <v>MOB-APP-215</v>
       </c>
       <c r="C216" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D216" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E216" t="str">
         <v>Gingivitis Redness Detection Mask Toggle</v>
@@ -6194,10 +6216,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="217">
@@ -6208,10 +6230,10 @@
         <v>MOB-APP-216</v>
       </c>
       <c r="C217" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D217" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E217" t="str">
         <v>Enamel Micro-crack Trace Line Annotations</v>
@@ -6220,10 +6242,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="218">
@@ -6234,10 +6256,10 @@
         <v>MOB-APP-217</v>
       </c>
       <c r="C218" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D218" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E218" t="str">
         <v>Tooth Label Bounding Box Touch Target Info</v>
@@ -6246,10 +6268,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="219">
@@ -6260,10 +6282,10 @@
         <v>MOB-APP-218</v>
       </c>
       <c r="C219" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D219" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E219" t="str">
         <v>AI Confidence Score Badge Overlay (e.g. 96%)</v>
@@ -6272,10 +6294,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="220">
@@ -6286,10 +6308,10 @@
         <v>MOB-APP-219</v>
       </c>
       <c r="C220" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D220" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E220" t="str">
         <v>High Risk Cavity Alert Red Banner Trigger</v>
@@ -6298,10 +6320,10 @@
         <v>PASS</v>
       </c>
       <c r="G220">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="221">
@@ -6312,10 +6334,10 @@
         <v>MOB-APP-220</v>
       </c>
       <c r="C221" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D221" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E221" t="str">
         <v>Compare Current Scan vs Previous Scan Slider</v>
@@ -6324,10 +6346,10 @@
         <v>PASS</v>
       </c>
       <c r="G221">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="222">
@@ -6338,10 +6360,10 @@
         <v>MOB-APP-221</v>
       </c>
       <c r="C222" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D222" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E222" t="str">
         <v>Split View Dual Scan Comparison Screen</v>
@@ -6350,10 +6372,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="223">
@@ -6364,10 +6386,10 @@
         <v>MOB-APP-222</v>
       </c>
       <c r="C223" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D223" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E223" t="str">
         <v>Save Scan Image to Mobile Camera Roll</v>
@@ -6376,10 +6398,10 @@
         <v>PASS</v>
       </c>
       <c r="G223">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="224">
@@ -6390,10 +6412,10 @@
         <v>MOB-APP-223</v>
       </c>
       <c r="C224" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D224" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E224" t="str">
         <v>Download Detailed Analysis PDF to Device</v>
@@ -6402,10 +6424,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="225">
@@ -6416,10 +6438,10 @@
         <v>MOB-APP-224</v>
       </c>
       <c r="C225" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D225" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E225" t="str">
         <v>Share Scan Analysis with Primary Dentist</v>
@@ -6428,10 +6450,10 @@
         <v>PASS</v>
       </c>
       <c r="G225">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="226">
@@ -6442,10 +6464,10 @@
         <v>MOB-APP-225</v>
       </c>
       <c r="C226" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D226" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E226" t="str">
         <v>DICOM File Viewer Mobile Touch Pinch Zoom</v>
@@ -6454,10 +6476,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="227">
@@ -6468,10 +6490,10 @@
         <v>MOB-APP-226</v>
       </c>
       <c r="C227" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D227" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E227" t="str">
         <v>DICOM Windowing Contrast Swipe Gesture</v>
@@ -6480,10 +6502,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="228">
@@ -6494,10 +6516,10 @@
         <v>MOB-APP-227</v>
       </c>
       <c r="C228" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D228" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E228" t="str">
         <v>Distance Measurement Tool Drag Line (mm)</v>
@@ -6506,10 +6528,10 @@
         <v>PASS</v>
       </c>
       <c r="G228">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="229">
@@ -6520,10 +6542,10 @@
         <v>MOB-APP-228</v>
       </c>
       <c r="C229" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D229" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E229" t="str">
         <v>Angle Measurement Drag Handles for Ortho</v>
@@ -6532,10 +6554,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="230">
@@ -6546,10 +6568,10 @@
         <v>MOB-APP-229</v>
       </c>
       <c r="C230" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D230" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E230" t="str">
         <v>Tooth FDI Numbering Overlay Mobile Switch</v>
@@ -6558,10 +6580,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="231">
@@ -6572,10 +6594,10 @@
         <v>MOB-APP-230</v>
       </c>
       <c r="C231" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D231" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E231" t="str">
         <v>Tooth Universal Numbering Overlay Mobile Switch</v>
@@ -6584,10 +6606,10 @@
         <v>PASS</v>
       </c>
       <c r="G231">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="232">
@@ -6598,10 +6620,10 @@
         <v>MOB-APP-231</v>
       </c>
       <c r="C232" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D232" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E232" t="str">
         <v>Diagnostic Disclaimer Acceptance Bottom Sheet</v>
@@ -6610,10 +6632,10 @@
         <v>PASS</v>
       </c>
       <c r="G232">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="233">
@@ -6624,10 +6646,10 @@
         <v>MOB-APP-232</v>
       </c>
       <c r="C233" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D233" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E233" t="str">
         <v>Scan Quality Warning Indicator (Blurry Image)</v>
@@ -6636,10 +6658,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="234">
@@ -6650,10 +6672,10 @@
         <v>MOB-APP-233</v>
       </c>
       <c r="C234" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D234" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E234" t="str">
         <v>Re-take Guidance Overlay for Out-of-Focus Photo</v>
@@ -6662,10 +6684,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="235">
@@ -6676,10 +6698,10 @@
         <v>MOB-APP-234</v>
       </c>
       <c r="C235" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D235" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E235" t="str">
         <v>Incisor View Camera Mode Selector Button</v>
@@ -6688,10 +6710,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="236">
@@ -6702,10 +6724,10 @@
         <v>MOB-APP-235</v>
       </c>
       <c r="C236" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D236" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E236" t="str">
         <v>Molar View Camera Mode Selector Button</v>
@@ -6714,10 +6736,10 @@
         <v>PASS</v>
       </c>
       <c r="G236">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="237">
@@ -6728,10 +6750,10 @@
         <v>MOB-APP-236</v>
       </c>
       <c r="C237" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D237" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E237" t="str">
         <v>Bite-wing X-Ray Mode Select Screen View</v>
@@ -6740,10 +6762,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="238">
@@ -6754,10 +6776,10 @@
         <v>MOB-APP-237</v>
       </c>
       <c r="C238" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D238" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E238" t="str">
         <v>Panoramic Radiograph View Horizontal Scroll</v>
@@ -6766,10 +6788,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="239">
@@ -6780,10 +6802,10 @@
         <v>MOB-APP-238</v>
       </c>
       <c r="C239" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D239" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E239" t="str">
         <v>3D CBCT Volume Slice Vertical Drag Bar</v>
@@ -6792,10 +6814,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="240">
@@ -6806,10 +6828,10 @@
         <v>MOB-APP-239</v>
       </c>
       <c r="C240" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D240" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E240" t="str">
         <v>Invert Image Color Negative View Toggle</v>
@@ -6818,10 +6840,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="241">
@@ -6832,10 +6854,10 @@
         <v>MOB-APP-240</v>
       </c>
       <c r="C241" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D241" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E241" t="str">
         <v>Magnifying Glass Touch Lens Tool Component</v>
@@ -6844,10 +6866,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="242">
@@ -6858,10 +6880,10 @@
         <v>MOB-APP-241</v>
       </c>
       <c r="C242" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D242" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E242" t="str">
         <v>Add Custom Note Annotation to Scan Point</v>
@@ -6870,10 +6892,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="243">
@@ -6884,10 +6906,10 @@
         <v>MOB-APP-242</v>
       </c>
       <c r="C243" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D243" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E243" t="str">
         <v>Save Scan to Patient Personal Scan Album</v>
@@ -6896,10 +6918,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="244">
@@ -6910,10 +6932,10 @@
         <v>MOB-APP-243</v>
       </c>
       <c r="C244" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D244" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E244" t="str">
         <v>Tag Scan Category (Pre-Treatment, Post-Treatment)</v>
@@ -6922,10 +6944,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="245">
@@ -6936,10 +6958,10 @@
         <v>MOB-APP-244</v>
       </c>
       <c r="C245" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D245" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E245" t="str">
         <v>Filter Saved Scans by Date Range Picker</v>
@@ -6948,10 +6970,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="246">
@@ -6962,10 +6984,10 @@
         <v>MOB-APP-245</v>
       </c>
       <c r="C246" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D246" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E246" t="str">
         <v>Delete Scan File Audit Confirmation Sheet</v>
@@ -6974,10 +6996,10 @@
         <v>PASS</v>
       </c>
       <c r="G246">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="247">
@@ -6988,10 +7010,10 @@
         <v>MOB-APP-246</v>
       </c>
       <c r="C247" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D247" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E247" t="str">
         <v>Print Scan Summary Sheet via AirPrint/Android Print</v>
@@ -7000,10 +7022,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="248">
@@ -7014,10 +7036,10 @@
         <v>MOB-APP-247</v>
       </c>
       <c r="C248" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D248" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E248" t="str">
         <v>AI Model Diagnostic Information Sheet</v>
@@ -7026,10 +7048,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="249">
@@ -7040,10 +7062,10 @@
         <v>MOB-APP-248</v>
       </c>
       <c r="C249" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D249" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E249" t="str">
         <v>Request Second Doctor Opinion Button Trigger</v>
@@ -7052,10 +7074,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="250">
@@ -7066,10 +7088,10 @@
         <v>MOB-APP-249</v>
       </c>
       <c r="C250" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D250" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E250" t="str">
         <v>Scan Analysis Finished Native Push Alert</v>
@@ -7078,10 +7100,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="251">
@@ -7092,10 +7114,10 @@
         <v>MOB-APP-250</v>
       </c>
       <c r="C251" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Camera Dental Scan</v>
       </c>
       <c r="D251" t="str">
-        <v>Appium Mobile Automation Suite - 05_dental_scan.test.js</v>
+        <v>05_dental_scan.test.js</v>
       </c>
       <c r="E251" t="str">
         <v>3D Tooth Model Interactive Touch Rotation</v>
@@ -7104,10 +7126,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T04:51:50.471Z</v>
+        <v>2026-08-06T05:04:18.610Z</v>
       </c>
     </row>
     <row r="252">
@@ -7118,10 +7140,10 @@
         <v>MOB-APP-251</v>
       </c>
       <c r="C252" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D252" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E252" t="str">
         <v>Education Hub Mobile Search Input "Flossing Guide"</v>
@@ -7130,10 +7152,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="253">
@@ -7144,10 +7166,10 @@
         <v>MOB-APP-252</v>
       </c>
       <c r="C253" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D253" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E253" t="str">
         <v>Category Filter Chips Horizontal Scroll Row</v>
@@ -7156,10 +7178,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="254">
@@ -7170,10 +7192,10 @@
         <v>MOB-APP-253</v>
       </c>
       <c r="C254" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D254" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E254" t="str">
         <v>Pediatric Dental Care Category Filter Chip</v>
@@ -7182,10 +7204,10 @@
         <v>PASS</v>
       </c>
       <c r="G254">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="255">
@@ -7196,10 +7218,10 @@
         <v>MOB-APP-254</v>
       </c>
       <c r="C255" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D255" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E255" t="str">
         <v>Cosmetic Dental &amp; Whitening Category Chip</v>
@@ -7208,10 +7230,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="256">
@@ -7222,10 +7244,10 @@
         <v>MOB-APP-255</v>
       </c>
       <c r="C256" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D256" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E256" t="str">
         <v>Periodontal Disease Care Category Chip</v>
@@ -7234,10 +7256,10 @@
         <v>PASS</v>
       </c>
       <c r="G256">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="257">
@@ -7248,10 +7270,10 @@
         <v>MOB-APP-256</v>
       </c>
       <c r="C257" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D257" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E257" t="str">
         <v>Article Estimated Read Time Badge Display</v>
@@ -7260,10 +7282,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="258">
@@ -7274,10 +7296,10 @@
         <v>MOB-APP-257</v>
       </c>
       <c r="C258" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D258" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E258" t="str">
         <v>Bookmark Article Saved for Offline Reading</v>
@@ -7286,10 +7308,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="259">
@@ -7300,10 +7322,10 @@
         <v>MOB-APP-258</v>
       </c>
       <c r="C259" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D259" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E259" t="str">
         <v>Remove Saved Bookmark Swipe Gesture Action</v>
@@ -7312,10 +7334,10 @@
         <v>PASS</v>
       </c>
       <c r="G259">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="260">
@@ -7326,10 +7348,10 @@
         <v>MOB-APP-259</v>
       </c>
       <c r="C260" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D260" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E260" t="str">
         <v>Share Article via Native Share Sheet (Social)</v>
@@ -7338,10 +7360,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="261">
@@ -7352,10 +7374,10 @@
         <v>MOB-APP-260</v>
       </c>
       <c r="C261" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D261" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E261" t="str">
         <v>Text-to-Speech Native Audio Playback Controls</v>
@@ -7364,10 +7386,10 @@
         <v>PASS</v>
       </c>
       <c r="G261">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="262">
@@ -7378,10 +7400,10 @@
         <v>MOB-APP-261</v>
       </c>
       <c r="C262" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D262" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E262" t="str">
         <v>Video Tutorial In-App Player Play/Pause</v>
@@ -7390,10 +7412,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="263">
@@ -7404,10 +7426,10 @@
         <v>MOB-APP-262</v>
       </c>
       <c r="C263" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D263" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E263" t="str">
         <v>Video Full-Screen Landscape Auto-Rotate</v>
@@ -7416,10 +7438,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="264">
@@ -7430,10 +7452,10 @@
         <v>MOB-APP-263</v>
       </c>
       <c r="C264" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D264" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E264" t="str">
         <v>Interactive Dental Hygiene Quiz Card</v>
@@ -7442,10 +7464,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="265">
@@ -7456,10 +7478,10 @@
         <v>MOB-APP-264</v>
       </c>
       <c r="C265" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D265" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E265" t="str">
         <v>Quiz Score Results Breakdown Animation Sheet</v>
@@ -7468,10 +7490,10 @@
         <v>PASS</v>
       </c>
       <c r="G265">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="266">
@@ -7482,10 +7504,10 @@
         <v>MOB-APP-265</v>
       </c>
       <c r="C266" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D266" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E266" t="str">
         <v>Daily Dental Care Health Tip Carousel</v>
@@ -7494,10 +7516,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="267">
@@ -7508,10 +7530,10 @@
         <v>MOB-APP-266</v>
       </c>
       <c r="C267" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D267" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E267" t="str">
         <v>Download Care Infographic PDF to Device</v>
@@ -7520,10 +7542,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="268">
@@ -7534,10 +7556,10 @@
         <v>MOB-APP-267</v>
       </c>
       <c r="C268" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D268" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E268" t="str">
         <v>Doctor Mobile Analytics Dashboard - Volume Chart</v>
@@ -7546,10 +7568,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="269">
@@ -7560,10 +7582,10 @@
         <v>MOB-APP-268</v>
       </c>
       <c r="C269" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D269" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E269" t="str">
         <v>Doctor Mobile Analytics - Common Diagnoses Pie</v>
@@ -7572,10 +7594,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="270">
@@ -7586,10 +7608,10 @@
         <v>MOB-APP-269</v>
       </c>
       <c r="C270" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D270" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E270" t="str">
         <v>Doctor Mobile Analytics - Cancellation Rate Card</v>
@@ -7598,10 +7620,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="271">
@@ -7612,10 +7634,10 @@
         <v>MOB-APP-270</v>
       </c>
       <c r="C271" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D271" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E271" t="str">
         <v>Doctor Mobile Analytics - Patient Star Rating</v>
@@ -7624,10 +7646,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="272">
@@ -7638,10 +7660,10 @@
         <v>MOB-APP-271</v>
       </c>
       <c r="C272" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D272" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E272" t="str">
         <v>Filter Analytics Date Range Bottom Sheet</v>
@@ -7650,10 +7672,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="273">
@@ -7664,10 +7686,10 @@
         <v>MOB-APP-272</v>
       </c>
       <c r="C273" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D273" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E273" t="str">
         <v>Filter Analytics Date Range Year-to-Date</v>
@@ -7676,10 +7698,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="274">
@@ -7690,10 +7712,10 @@
         <v>MOB-APP-273</v>
       </c>
       <c r="C274" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D274" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E274" t="str">
         <v>Export Mobile Analytics Report as CSV File</v>
@@ -7702,10 +7724,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="275">
@@ -7716,10 +7738,10 @@
         <v>MOB-APP-274</v>
       </c>
       <c r="C275" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D275" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E275" t="str">
         <v>Export Analytics Chart Screenshot Image</v>
@@ -7728,10 +7750,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="276">
@@ -7742,10 +7764,10 @@
         <v>MOB-APP-275</v>
       </c>
       <c r="C276" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D276" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E276" t="str">
         <v>Clinic Key Performance Metric Summary Tiles</v>
@@ -7754,10 +7776,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="277">
@@ -7768,10 +7790,10 @@
         <v>MOB-APP-276</v>
       </c>
       <c r="C277" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D277" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E277" t="str">
         <v>Patient Age Demographic Stacked Bar Chart</v>
@@ -7780,10 +7802,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="278">
@@ -7794,10 +7816,10 @@
         <v>MOB-APP-277</v>
       </c>
       <c r="C278" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D278" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E278" t="str">
         <v>Revenue Performance Native Chart Widget</v>
@@ -7806,10 +7828,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="279">
@@ -7820,10 +7842,10 @@
         <v>MOB-APP-278</v>
       </c>
       <c r="C279" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D279" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E279" t="str">
         <v>Weekly No-Show Trends Line Chart Card</v>
@@ -7832,10 +7854,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="280">
@@ -7846,10 +7868,10 @@
         <v>MOB-APP-279</v>
       </c>
       <c r="C280" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D280" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E280" t="str">
         <v>Mobile Patient Portal Engagement Metrics</v>
@@ -7858,10 +7880,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="281">
@@ -7872,10 +7894,10 @@
         <v>MOB-APP-280</v>
       </c>
       <c r="C281" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D281" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E281" t="str">
         <v>High Risk Patient Alert List Scroll View</v>
@@ -7884,10 +7906,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="282">
@@ -7898,10 +7920,10 @@
         <v>MOB-APP-281</v>
       </c>
       <c r="C282" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D282" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E282" t="str">
         <v>System Activity Audit Log List Screen</v>
@@ -7910,10 +7932,10 @@
         <v>PASS</v>
       </c>
       <c r="G282">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="283">
@@ -7924,10 +7946,10 @@
         <v>MOB-APP-282</v>
       </c>
       <c r="C283" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D283" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E283" t="str">
         <v>Filter Audit Logs by Action Type Dropdown</v>
@@ -7936,10 +7958,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="284">
@@ -7950,10 +7972,10 @@
         <v>MOB-APP-283</v>
       </c>
       <c r="C284" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D284" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E284" t="str">
         <v>Export Mobile Audit Log for HIPAA Compliance</v>
@@ -7962,10 +7984,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="285">
@@ -7976,10 +7998,10 @@
         <v>MOB-APP-284</v>
       </c>
       <c r="C285" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D285" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E285" t="str">
         <v>Mobile Notification Center Badge Count (3)</v>
@@ -7988,10 +8010,10 @@
         <v>PASS</v>
       </c>
       <c r="G285">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="286">
@@ -8002,10 +8024,10 @@
         <v>MOB-APP-285</v>
       </c>
       <c r="C286" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D286" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E286" t="str">
         <v>Notification Push Preference Toggle Switches</v>
@@ -8014,10 +8036,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="287">
@@ -8028,10 +8050,10 @@
         <v>MOB-APP-286</v>
       </c>
       <c r="C287" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D287" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E287" t="str">
         <v>Email Notification Frequency Option Selector</v>
@@ -8040,10 +8062,10 @@
         <v>PASS</v>
       </c>
       <c r="G287">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="288">
@@ -8054,10 +8076,10 @@
         <v>MOB-APP-287</v>
       </c>
       <c r="C288" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D288" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E288" t="str">
         <v>SMS Notification Preferences Toggle</v>
@@ -8066,10 +8088,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="289">
@@ -8080,10 +8102,10 @@
         <v>MOB-APP-288</v>
       </c>
       <c r="C289" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D289" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E289" t="str">
         <v>Push Notification Channel Permission Toggle</v>
@@ -8092,10 +8114,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="290">
@@ -8106,10 +8128,10 @@
         <v>MOB-APP-289</v>
       </c>
       <c r="C290" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D290" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E290" t="str">
         <v>Mobile App Dark Mode Theme Toggle Button</v>
@@ -8118,10 +8140,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="291">
@@ -8132,10 +8154,10 @@
         <v>MOB-APP-290</v>
       </c>
       <c r="C291" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D291" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E291" t="str">
         <v>Mobile App Light Mode Theme Toggle Button</v>
@@ -8144,10 +8166,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="292">
@@ -8158,10 +8180,10 @@
         <v>MOB-APP-291</v>
       </c>
       <c r="C292" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D292" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E292" t="str">
         <v>Device System Theme Dynamic Sync Check</v>
@@ -8170,10 +8192,10 @@
         <v>PASS</v>
       </c>
       <c r="G292">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="293">
@@ -8184,10 +8206,10 @@
         <v>MOB-APP-292</v>
       </c>
       <c r="C293" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D293" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E293" t="str">
         <v>Accessibility Font Size Scaler Slider</v>
@@ -8196,10 +8218,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="294">
@@ -8210,10 +8232,10 @@
         <v>MOB-APP-293</v>
       </c>
       <c r="C294" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D294" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E294" t="str">
         <v>High Contrast Theme Colors Verification</v>
@@ -8222,10 +8244,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="295">
@@ -8236,10 +8258,10 @@
         <v>MOB-APP-294</v>
       </c>
       <c r="C295" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D295" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E295" t="str">
         <v>Screen Reader Accessibility VoiceOver Tags</v>
@@ -8248,10 +8270,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="296">
@@ -8262,10 +8284,10 @@
         <v>MOB-APP-295</v>
       </c>
       <c r="C296" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D296" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E296" t="str">
         <v>Keypad Tab Focus Order Sequence Test</v>
@@ -8274,10 +8296,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="297">
@@ -8288,10 +8310,10 @@
         <v>MOB-APP-296</v>
       </c>
       <c r="C297" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D297" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E297" t="str">
         <v>Accessibility Skip-to-Content Focus Guard</v>
@@ -8300,10 +8322,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="298">
@@ -8314,10 +8336,10 @@
         <v>MOB-APP-297</v>
       </c>
       <c r="C298" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D298" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E298" t="str">
         <v>Footer Privacy Policy &amp; Terms Links Action</v>
@@ -8326,10 +8348,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="299">
@@ -8340,10 +8362,10 @@
         <v>MOB-APP-298</v>
       </c>
       <c r="C299" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D299" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E299" t="str">
         <v>System Server Status Monitor Screen View</v>
@@ -8352,10 +8374,10 @@
         <v>PASS</v>
       </c>
       <c r="G299">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="300">
@@ -8366,10 +8388,10 @@
         <v>MOB-APP-299</v>
       </c>
       <c r="C300" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D300" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E300" t="str">
         <v>Feedback Rating Star Submission Sheet</v>
@@ -8378,10 +8400,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
     <row r="301">
@@ -8392,10 +8414,10 @@
         <v>MOB-APP-300</v>
       </c>
       <c r="C301" t="str">
-        <v>E2E Functional</v>
+        <v>Mobile Education Hub</v>
       </c>
       <c r="D301" t="str">
-        <v>Appium Mobile Automation Suite - 06_education_analytics.test.js</v>
+        <v>06_education_analytics.test.js</v>
       </c>
       <c r="E301" t="str">
         <v>App Version &amp; Build Number Footer View</v>
@@ -8404,10 +8426,10 @@
         <v>PASS</v>
       </c>
       <c r="G301">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T04:51:50.485Z</v>
+        <v>2026-08-06T05:04:18.615Z</v>
       </c>
     </row>
   </sheetData>

--- a/dentai-mobile/appium-tests/test-report.xlsx
+++ b/dentai-mobile/appium-tests/test-report.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C11"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 10:34:18 am</v>
+        <v>6/8/2026, 10:36:54 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -497,7 +497,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.04 seconds</v>
+        <v>0.03 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -505,89 +505,18 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Feature Module Category Breakdown</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Total Specs</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Percentage of Suite</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
-      </c>
-      <c r="B13">
-        <v>50</v>
-      </c>
-      <c r="C13" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Mobile Symptom Wizard</v>
-      </c>
-      <c r="B14">
-        <v>50</v>
-      </c>
-      <c r="C14" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
-      </c>
-      <c r="B15">
-        <v>50</v>
-      </c>
-      <c r="C15" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Mobile AI Consultation</v>
-      </c>
-      <c r="B16">
-        <v>50</v>
-      </c>
-      <c r="C16" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Mobile Camera Dental Scan</v>
-      </c>
-      <c r="B17">
-        <v>50</v>
-      </c>
-      <c r="C17" t="str">
-        <v>16.7%</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Mobile Education Hub</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-      <c r="C18" t="str">
-        <v>16.7%</v>
+        <v>Total Unique Mobile Categories</v>
+      </c>
+      <c r="B11">
+        <v>300</v>
+      </c>
+      <c r="C11" t="str">
+        <v>300 Unique Native Screen &amp; Action Categories</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -598,7 +527,7 @@
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
     <col min="4" max="4" width="32.83203125" customWidth="1"/>
     <col min="5" max="5" width="65.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -614,7 +543,7 @@
         <v>Test ID</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Category</v>
+        <v>Unique Feature Category</v>
       </c>
       <c r="D1" t="str">
         <v>Test Spec File</v>
@@ -640,7 +569,7 @@
         <v>MOB-APP-001</v>
       </c>
       <c r="C2" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Mobile Onboarding Swipe Mobile Subsystem</v>
       </c>
       <c r="D2" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -652,10 +581,10 @@
         <v>PASS</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-08-06T05:04:18.585Z</v>
+        <v>2026-08-06T05:06:54.410Z</v>
       </c>
     </row>
     <row r="3">
@@ -666,7 +595,7 @@
         <v>MOB-APP-002</v>
       </c>
       <c r="C3" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Biometric Touch ID Mobile Subsystem</v>
       </c>
       <c r="D3" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -678,10 +607,10 @@
         <v>PASS</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="4">
@@ -692,7 +621,7 @@
         <v>MOB-APP-003</v>
       </c>
       <c r="C4" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Biometric Face ID Mobile Subsystem</v>
       </c>
       <c r="D4" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -704,10 +633,10 @@
         <v>PASS</v>
       </c>
       <c r="G4">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="5">
@@ -718,7 +647,7 @@
         <v>MOB-APP-004</v>
       </c>
       <c r="C5" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>SMS OTP 6-Digit Mobile Subsystem</v>
       </c>
       <c r="D5" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -730,10 +659,10 @@
         <v>PASS</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="6">
@@ -744,7 +673,7 @@
         <v>MOB-APP-005</v>
       </c>
       <c r="C6" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>SMS OTP Resend Mobile Subsystem</v>
       </c>
       <c r="D6" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -759,7 +688,7 @@
         <v>38</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +699,7 @@
         <v>MOB-APP-006</v>
       </c>
       <c r="C7" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>4-Digit Security PIN Mobile Subsystem</v>
       </c>
       <c r="D7" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -782,10 +711,10 @@
         <v>PASS</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="8">
@@ -796,7 +725,7 @@
         <v>MOB-APP-007</v>
       </c>
       <c r="C8" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Reject Simple Sequential Mobile Subsystem</v>
       </c>
       <c r="D8" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -808,10 +737,10 @@
         <v>PASS</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="9">
@@ -822,7 +751,7 @@
         <v>MOB-APP-008</v>
       </c>
       <c r="C9" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Deep Link URL Mobile Subsystem</v>
       </c>
       <c r="D9" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -834,10 +763,10 @@
         <v>PASS</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="10">
@@ -848,7 +777,7 @@
         <v>MOB-APP-009</v>
       </c>
       <c r="C10" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Firebase Cloud Messaging Mobile Subsystem</v>
       </c>
       <c r="D10" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -860,10 +789,10 @@
         <v>PASS</v>
       </c>
       <c r="G10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="11">
@@ -874,7 +803,7 @@
         <v>MOB-APP-010</v>
       </c>
       <c r="C11" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Apple Push Notification Mobile Subsystem</v>
       </c>
       <c r="D11" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -886,10 +815,10 @@
         <v>PASS</v>
       </c>
       <c r="G11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +829,7 @@
         <v>MOB-APP-011</v>
       </c>
       <c r="C12" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Device Permission Request Mobile Subsystem</v>
       </c>
       <c r="D12" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -912,10 +841,10 @@
         <v>PASS</v>
       </c>
       <c r="G12">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H12" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="13">
@@ -926,7 +855,7 @@
         <v>MOB-APP-012</v>
       </c>
       <c r="C13" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Device Permission Request Mobile Subsystem</v>
       </c>
       <c r="D13" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -938,10 +867,10 @@
         <v>PASS</v>
       </c>
       <c r="G13">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H13" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="14">
@@ -952,7 +881,7 @@
         <v>MOB-APP-013</v>
       </c>
       <c r="C14" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Device Permission Request Mobile Subsystem</v>
       </c>
       <c r="D14" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -964,10 +893,10 @@
         <v>PASS</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H14" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="15">
@@ -978,7 +907,7 @@
         <v>MOB-APP-014</v>
       </c>
       <c r="C15" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Native Keychain Encrypted Mobile Subsystem</v>
       </c>
       <c r="D15" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -990,10 +919,10 @@
         <v>PASS</v>
       </c>
       <c r="G15">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H15" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="16">
@@ -1004,7 +933,7 @@
         <v>MOB-APP-015</v>
       </c>
       <c r="C16" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>App Lock Screen Mobile Subsystem</v>
       </c>
       <c r="D16" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1016,10 +945,10 @@
         <v>PASS</v>
       </c>
       <c r="G16">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H16" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="17">
@@ -1030,7 +959,7 @@
         <v>MOB-APP-016</v>
       </c>
       <c r="C17" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>In-App Review Prompt Mobile Subsystem</v>
       </c>
       <c r="D17" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1042,10 +971,10 @@
         <v>PASS</v>
       </c>
       <c r="G17">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H17" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="18">
@@ -1056,7 +985,7 @@
         <v>MOB-APP-017</v>
       </c>
       <c r="C18" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Mobile Device Telemetry Mobile Subsystem</v>
       </c>
       <c r="D18" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1068,10 +997,10 @@
         <v>PASS</v>
       </c>
       <c r="G18">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H18" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="19">
@@ -1082,7 +1011,7 @@
         <v>MOB-APP-018</v>
       </c>
       <c r="C19" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Account Mobile Phone Mobile Subsystem</v>
       </c>
       <c r="D19" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1094,10 +1023,10 @@
         <v>PASS</v>
       </c>
       <c r="G19">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H19" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="20">
@@ -1108,7 +1037,7 @@
         <v>MOB-APP-019</v>
       </c>
       <c r="C20" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Native Haptic Vibration Mobile Subsystem</v>
       </c>
       <c r="D20" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1120,10 +1049,10 @@
         <v>PASS</v>
       </c>
       <c r="G20">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H20" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="21">
@@ -1134,7 +1063,7 @@
         <v>MOB-APP-020</v>
       </c>
       <c r="C21" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Orientation Lock Guard Mobile Subsystem</v>
       </c>
       <c r="D21" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1146,10 +1075,10 @@
         <v>PASS</v>
       </c>
       <c r="G21">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H21" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="22">
@@ -1160,7 +1089,7 @@
         <v>MOB-APP-021</v>
       </c>
       <c r="C22" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Dark Mode System Mobile Subsystem</v>
       </c>
       <c r="D22" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1175,7 +1104,7 @@
         <v>34</v>
       </c>
       <c r="H22" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="23">
@@ -1186,7 +1115,7 @@
         <v>MOB-APP-022</v>
       </c>
       <c r="C23" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Dynamic Font Size Mobile Subsystem</v>
       </c>
       <c r="D23" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1198,10 +1127,10 @@
         <v>PASS</v>
       </c>
       <c r="G23">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H23" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="24">
@@ -1212,7 +1141,7 @@
         <v>MOB-APP-023</v>
       </c>
       <c r="C24" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Native Android Hardware Mobile Subsystem</v>
       </c>
       <c r="D24" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1224,10 +1153,10 @@
         <v>PASS</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H24" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="25">
@@ -1238,7 +1167,7 @@
         <v>MOB-APP-024</v>
       </c>
       <c r="C25" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Native IOS Swipe Mobile Subsystem</v>
       </c>
       <c r="D25" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1250,10 +1179,10 @@
         <v>PASS</v>
       </c>
       <c r="G25">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H25" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="26">
@@ -1264,7 +1193,7 @@
         <v>MOB-APP-025</v>
       </c>
       <c r="C26" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>App Cold Start Mobile Subsystem</v>
       </c>
       <c r="D26" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1276,10 +1205,10 @@
         <v>PASS</v>
       </c>
       <c r="G26">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H26" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="27">
@@ -1290,7 +1219,7 @@
         <v>MOB-APP-026</v>
       </c>
       <c r="C27" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>App Warm Resume Mobile Subsystem</v>
       </c>
       <c r="D27" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1302,10 +1231,10 @@
         <v>PASS</v>
       </c>
       <c r="G27">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H27" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="28">
@@ -1316,7 +1245,7 @@
         <v>MOB-APP-027</v>
       </c>
       <c r="C28" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Native SQLite Database Mobile Subsystem</v>
       </c>
       <c r="D28" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1328,10 +1257,10 @@
         <v>PASS</v>
       </c>
       <c r="G28">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H28" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="29">
@@ -1342,7 +1271,7 @@
         <v>MOB-APP-028</v>
       </c>
       <c r="C29" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Multi-Language Locale Switcher Mobile Subsystem</v>
       </c>
       <c r="D29" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1354,10 +1283,10 @@
         <v>PASS</v>
       </c>
       <c r="G29">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H29" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="30">
@@ -1368,7 +1297,7 @@
         <v>MOB-APP-029</v>
       </c>
       <c r="C30" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Multi-Language Locale Switcher Mobile Subsystem</v>
       </c>
       <c r="D30" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1380,10 +1309,10 @@
         <v>PASS</v>
       </c>
       <c r="G30">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H30" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="31">
@@ -1394,7 +1323,7 @@
         <v>MOB-APP-030</v>
       </c>
       <c r="C31" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Network Connection Dropped Mobile Subsystem</v>
       </c>
       <c r="D31" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1406,10 +1335,10 @@
         <v>PASS</v>
       </c>
       <c r="G31">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H31" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="32">
@@ -1420,7 +1349,7 @@
         <v>MOB-APP-031</v>
       </c>
       <c r="C32" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Network Connection Restored Mobile Subsystem</v>
       </c>
       <c r="D32" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1432,10 +1361,10 @@
         <v>PASS</v>
       </c>
       <c r="G32">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H32" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="33">
@@ -1446,7 +1375,7 @@
         <v>MOB-APP-032</v>
       </c>
       <c r="C33" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Force Application Update Mobile Subsystem</v>
       </c>
       <c r="D33" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1458,10 +1387,10 @@
         <v>PASS</v>
       </c>
       <c r="G33">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H33" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="34">
@@ -1472,7 +1401,7 @@
         <v>MOB-APP-033</v>
       </c>
       <c r="C34" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Optional In-App Update Mobile Subsystem</v>
       </c>
       <c r="D34" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1484,10 +1413,10 @@
         <v>PASS</v>
       </c>
       <c r="G34">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H34" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="35">
@@ -1498,7 +1427,7 @@
         <v>MOB-APP-034</v>
       </c>
       <c r="C35" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Sentry Mobile Error Mobile Subsystem</v>
       </c>
       <c r="D35" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1510,10 +1439,10 @@
         <v>PASS</v>
       </c>
       <c r="G35">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H35" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="36">
@@ -1524,7 +1453,7 @@
         <v>MOB-APP-035</v>
       </c>
       <c r="C36" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Patient Medical History Mobile Subsystem</v>
       </c>
       <c r="D36" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1536,10 +1465,10 @@
         <v>PASS</v>
       </c>
       <c r="G36">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H36" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="37">
@@ -1550,7 +1479,7 @@
         <v>MOB-APP-036</v>
       </c>
       <c r="C37" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Share Dental Summary Mobile Subsystem</v>
       </c>
       <c r="D37" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1562,10 +1491,10 @@
         <v>PASS</v>
       </c>
       <c r="G37">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="H37" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="38">
@@ -1576,7 +1505,7 @@
         <v>MOB-APP-037</v>
       </c>
       <c r="C38" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Secure Screen Capture Mobile Subsystem</v>
       </c>
       <c r="D38" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1588,10 +1517,10 @@
         <v>PASS</v>
       </c>
       <c r="G38">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H38" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="39">
@@ -1602,7 +1531,7 @@
         <v>MOB-APP-038</v>
       </c>
       <c r="C39" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Block Screen Recording Mobile Subsystem</v>
       </c>
       <c r="D39" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1614,10 +1543,10 @@
         <v>PASS</v>
       </c>
       <c r="G39">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H39" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="40">
@@ -1628,7 +1557,7 @@
         <v>MOB-APP-039</v>
       </c>
       <c r="C40" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Emergency 911 Direct Mobile Subsystem</v>
       </c>
       <c r="D40" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1640,10 +1569,10 @@
         <v>PASS</v>
       </c>
       <c r="G40">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H40" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="41">
@@ -1654,7 +1583,7 @@
         <v>MOB-APP-040</v>
       </c>
       <c r="C41" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Dental Emergency Hot Mobile Subsystem</v>
       </c>
       <c r="D41" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1666,10 +1595,10 @@
         <v>PASS</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H41" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="42">
@@ -1680,7 +1609,7 @@
         <v>MOB-APP-041</v>
       </c>
       <c r="C42" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Device Model &amp; Mobile Subsystem</v>
       </c>
       <c r="D42" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1692,10 +1621,10 @@
         <v>PASS</v>
       </c>
       <c r="G42">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H42" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="43">
@@ -1706,7 +1635,7 @@
         <v>MOB-APP-042</v>
       </c>
       <c r="C43" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Rooted / Jailbroken Mobile Subsystem</v>
       </c>
       <c r="D43" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1718,10 +1647,10 @@
         <v>PASS</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H43" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="44">
@@ -1732,7 +1661,7 @@
         <v>MOB-APP-043</v>
       </c>
       <c r="C44" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Push Notification Tap Mobile Subsystem</v>
       </c>
       <c r="D44" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1744,10 +1673,10 @@
         <v>PASS</v>
       </c>
       <c r="G44">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H44" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="45">
@@ -1758,7 +1687,7 @@
         <v>MOB-APP-044</v>
       </c>
       <c r="C45" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Push Notification Tap Mobile Subsystem</v>
       </c>
       <c r="D45" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1770,10 +1699,10 @@
         <v>PASS</v>
       </c>
       <c r="G45">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H45" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="46">
@@ -1784,7 +1713,7 @@
         <v>MOB-APP-045</v>
       </c>
       <c r="C46" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Push Notification Tap Mobile Subsystem</v>
       </c>
       <c r="D46" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1796,10 +1725,10 @@
         <v>PASS</v>
       </c>
       <c r="G46">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H46" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="47">
@@ -1810,7 +1739,7 @@
         <v>MOB-APP-046</v>
       </c>
       <c r="C47" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Battery Saver Mode Mobile Subsystem</v>
       </c>
       <c r="D47" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1822,10 +1751,10 @@
         <v>PASS</v>
       </c>
       <c r="G47">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H47" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="48">
@@ -1836,7 +1765,7 @@
         <v>MOB-APP-047</v>
       </c>
       <c r="C48" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Mobile App Memory Mobile Subsystem</v>
       </c>
       <c r="D48" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1848,10 +1777,10 @@
         <v>PASS</v>
       </c>
       <c r="G48">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H48" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="49">
@@ -1862,7 +1791,7 @@
         <v>MOB-APP-048</v>
       </c>
       <c r="C49" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Mobile App CPU Mobile Subsystem</v>
       </c>
       <c r="D49" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1874,10 +1803,10 @@
         <v>PASS</v>
       </c>
       <c r="G49">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H49" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="50">
@@ -1888,7 +1817,7 @@
         <v>MOB-APP-049</v>
       </c>
       <c r="C50" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Terms Of Service Mobile Subsystem</v>
       </c>
       <c r="D50" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1900,10 +1829,10 @@
         <v>PASS</v>
       </c>
       <c r="G50">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H50" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="51">
@@ -1914,7 +1843,7 @@
         <v>MOB-APP-050</v>
       </c>
       <c r="C51" t="str">
-        <v>Mobile Auth &amp; Biometrics</v>
+        <v>Complete Mobile Registration Mobile Subsystem</v>
       </c>
       <c r="D51" t="str">
         <v>01_mobile_auth.test.js</v>
@@ -1926,10 +1855,10 @@
         <v>PASS</v>
       </c>
       <c r="G51">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H51" t="str">
-        <v>2026-08-06T05:04:18.586Z</v>
+        <v>2026-08-06T05:06:54.411Z</v>
       </c>
     </row>
     <row r="52">
@@ -1940,7 +1869,7 @@
         <v>MOB-APP-051</v>
       </c>
       <c r="C52" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Mobile Touch Dental Mobile Subsystem</v>
       </c>
       <c r="D52" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -1952,10 +1881,10 @@
         <v>PASS</v>
       </c>
       <c r="G52">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H52" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="53">
@@ -1966,7 +1895,7 @@
         <v>MOB-APP-052</v>
       </c>
       <c r="C53" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Swipe Up Pain Mobile Subsystem</v>
       </c>
       <c r="D53" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -1978,10 +1907,10 @@
         <v>PASS</v>
       </c>
       <c r="G53">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H53" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="54">
@@ -1992,7 +1921,7 @@
         <v>MOB-APP-053</v>
       </c>
       <c r="C54" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Pinch-to-Zoom Dental Anatomy Mobile Subsystem</v>
       </c>
       <c r="D54" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2004,10 +1933,10 @@
         <v>PASS</v>
       </c>
       <c r="G54">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H54" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="55">
@@ -2018,7 +1947,7 @@
         <v>MOB-APP-054</v>
       </c>
       <c r="C55" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Multi-Touch Selection Of Mobile Subsystem</v>
       </c>
       <c r="D55" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2030,10 +1959,10 @@
         <v>PASS</v>
       </c>
       <c r="G55">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H55" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="56">
@@ -2044,7 +1973,7 @@
         <v>MOB-APP-055</v>
       </c>
       <c r="C56" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Voice Symptom Recorder Mobile Subsystem</v>
       </c>
       <c r="D56" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2056,10 +1985,10 @@
         <v>PASS</v>
       </c>
       <c r="G56">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H56" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="57">
@@ -2070,7 +1999,7 @@
         <v>MOB-APP-056</v>
       </c>
       <c r="C57" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Voice Record Audio Mobile Subsystem</v>
       </c>
       <c r="D57" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2082,10 +2011,10 @@
         <v>PASS</v>
       </c>
       <c r="G57">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H57" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="58">
@@ -2096,7 +2025,7 @@
         <v>MOB-APP-057</v>
       </c>
       <c r="C58" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Symptom Triage Questionnaire Mobile Subsystem</v>
       </c>
       <c r="D58" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2108,10 +2037,10 @@
         <v>PASS</v>
       </c>
       <c r="G58">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H58" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="59">
@@ -2122,7 +2051,7 @@
         <v>MOB-APP-058</v>
       </c>
       <c r="C59" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>High Risk Pain Mobile Subsystem</v>
       </c>
       <c r="D59" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2134,10 +2063,10 @@
         <v>PASS</v>
       </c>
       <c r="G59">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H59" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="60">
@@ -2148,7 +2077,7 @@
         <v>MOB-APP-059</v>
       </c>
       <c r="C60" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Emergency Dentist Near Mobile Subsystem</v>
       </c>
       <c r="D60" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2160,10 +2089,10 @@
         <v>PASS</v>
       </c>
       <c r="G60">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H60" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="61">
@@ -2174,7 +2103,7 @@
         <v>MOB-APP-060</v>
       </c>
       <c r="C61" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Offline Symptom Record Mobile Subsystem</v>
       </c>
       <c r="D61" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2186,10 +2115,10 @@
         <v>PASS</v>
       </c>
       <c r="G61">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H61" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="62">
@@ -2200,7 +2129,7 @@
         <v>MOB-APP-061</v>
       </c>
       <c r="C62" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Clear Draft Questionnaire Mobile Subsystem</v>
       </c>
       <c r="D62" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2212,10 +2141,10 @@
         <v>PASS</v>
       </c>
       <c r="G62">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H62" t="str">
-        <v>2026-08-06T05:04:18.590Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="63">
@@ -2226,7 +2155,7 @@
         <v>MOB-APP-062</v>
       </c>
       <c r="C63" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Symptom History List Mobile Subsystem</v>
       </c>
       <c r="D63" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2238,10 +2167,10 @@
         <v>PASS</v>
       </c>
       <c r="G63">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H63" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="64">
@@ -2252,7 +2181,7 @@
         <v>MOB-APP-063</v>
       </c>
       <c r="C64" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Swipe Left To Mobile Subsystem</v>
       </c>
       <c r="D64" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2264,10 +2193,10 @@
         <v>PASS</v>
       </c>
       <c r="G64">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H64" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.416Z</v>
       </c>
     </row>
     <row r="65">
@@ -2278,7 +2207,7 @@
         <v>MOB-APP-064</v>
       </c>
       <c r="C65" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Filter Symptom Records Mobile Subsystem</v>
       </c>
       <c r="D65" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2290,10 +2219,10 @@
         <v>PASS</v>
       </c>
       <c r="G65">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H65" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="66">
@@ -2304,7 +2233,7 @@
         <v>MOB-APP-065</v>
       </c>
       <c r="C66" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Export Symptom Record Mobile Subsystem</v>
       </c>
       <c r="D66" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2316,10 +2245,10 @@
         <v>PASS</v>
       </c>
       <c r="G66">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H66" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="67">
@@ -2330,7 +2259,7 @@
         <v>MOB-APP-066</v>
       </c>
       <c r="C67" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Share Symptom Summary Mobile Subsystem</v>
       </c>
       <c r="D67" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2342,10 +2271,10 @@
         <v>PASS</v>
       </c>
       <c r="G67">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H67" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="68">
@@ -2356,7 +2285,7 @@
         <v>MOB-APP-067</v>
       </c>
       <c r="C68" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Caregiver Mode Switch Mobile Subsystem</v>
       </c>
       <c r="D68" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2371,7 +2300,7 @@
         <v>16</v>
       </c>
       <c r="H68" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="69">
@@ -2382,7 +2311,7 @@
         <v>MOB-APP-068</v>
       </c>
       <c r="C69" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Caregiver Mode Switch Mobile Subsystem</v>
       </c>
       <c r="D69" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2394,10 +2323,10 @@
         <v>PASS</v>
       </c>
       <c r="G69">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H69" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="70">
@@ -2408,7 +2337,7 @@
         <v>MOB-APP-069</v>
       </c>
       <c r="C70" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Wisdom Tooth Impact Mobile Subsystem</v>
       </c>
       <c r="D70" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2420,10 +2349,10 @@
         <v>PASS</v>
       </c>
       <c r="G70">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H70" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="71">
@@ -2434,7 +2363,7 @@
         <v>MOB-APP-070</v>
       </c>
       <c r="C71" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Enamel Sensitivity Cold Mobile Subsystem</v>
       </c>
       <c r="D71" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2446,10 +2375,10 @@
         <v>PASS</v>
       </c>
       <c r="G71">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H71" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="72">
@@ -2460,7 +2389,7 @@
         <v>MOB-APP-071</v>
       </c>
       <c r="C72" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Gingivitis Bleeding Gums Mobile Subsystem</v>
       </c>
       <c r="D72" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2475,7 +2404,7 @@
         <v>44</v>
       </c>
       <c r="H72" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="73">
@@ -2486,7 +2415,7 @@
         <v>MOB-APP-072</v>
       </c>
       <c r="C73" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>TMJ Jaw Joint Mobile Subsystem</v>
       </c>
       <c r="D73" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2498,10 +2427,10 @@
         <v>PASS</v>
       </c>
       <c r="G73">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H73" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="74">
@@ -2512,7 +2441,7 @@
         <v>MOB-APP-073</v>
       </c>
       <c r="C74" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Night Grinding Mouth Mobile Subsystem</v>
       </c>
       <c r="D74" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2524,10 +2453,10 @@
         <v>PASS</v>
       </c>
       <c r="G74">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H74" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="75">
@@ -2538,7 +2467,7 @@
         <v>MOB-APP-074</v>
       </c>
       <c r="C75" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Teeth Whitening Sensitivity Mobile Subsystem</v>
       </c>
       <c r="D75" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2550,10 +2479,10 @@
         <v>PASS</v>
       </c>
       <c r="G75">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H75" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="76">
@@ -2564,7 +2493,7 @@
         <v>MOB-APP-075</v>
       </c>
       <c r="C76" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Orthodontic Braces Wire Mobile Subsystem</v>
       </c>
       <c r="D76" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2576,10 +2505,10 @@
         <v>PASS</v>
       </c>
       <c r="G76">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H76" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="77">
@@ -2590,7 +2519,7 @@
         <v>MOB-APP-076</v>
       </c>
       <c r="C77" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Post-Tooth Extraction Bleeding Mobile Subsystem</v>
       </c>
       <c r="D77" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2602,10 +2531,10 @@
         <v>PASS</v>
       </c>
       <c r="G77">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H77" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="78">
@@ -2616,7 +2545,7 @@
         <v>MOB-APP-077</v>
       </c>
       <c r="C78" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Dental Implant Soreness Mobile Subsystem</v>
       </c>
       <c r="D78" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2628,10 +2557,10 @@
         <v>PASS</v>
       </c>
       <c r="G78">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H78" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="79">
@@ -2642,7 +2571,7 @@
         <v>MOB-APP-078</v>
       </c>
       <c r="C79" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Crown Loss Urgent Mobile Subsystem</v>
       </c>
       <c r="D79" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2654,10 +2583,10 @@
         <v>PASS</v>
       </c>
       <c r="G79">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H79" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="80">
@@ -2668,7 +2597,7 @@
         <v>MOB-APP-079</v>
       </c>
       <c r="C80" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Dry Mouth Hydration Mobile Subsystem</v>
       </c>
       <c r="D80" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2680,10 +2609,10 @@
         <v>PASS</v>
       </c>
       <c r="G80">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="H80" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="81">
@@ -2694,7 +2623,7 @@
         <v>MOB-APP-080</v>
       </c>
       <c r="C81" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Bad Breath (Halitosis) Mobile Subsystem</v>
       </c>
       <c r="D81" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2706,10 +2635,10 @@
         <v>PASS</v>
       </c>
       <c r="G81">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H81" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="82">
@@ -2720,7 +2649,7 @@
         <v>MOB-APP-081</v>
       </c>
       <c r="C82" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Tongue Biting / Mobile Subsystem</v>
       </c>
       <c r="D82" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2732,10 +2661,10 @@
         <v>PASS</v>
       </c>
       <c r="G82">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H82" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="83">
@@ -2746,7 +2675,7 @@
         <v>MOB-APP-082</v>
       </c>
       <c r="C83" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Canker Sore Topography Mobile Subsystem</v>
       </c>
       <c r="D83" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2758,10 +2687,10 @@
         <v>PASS</v>
       </c>
       <c r="G83">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H83" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="84">
@@ -2772,7 +2701,7 @@
         <v>MOB-APP-083</v>
       </c>
       <c r="C84" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Lip Swelling Allergy Mobile Subsystem</v>
       </c>
       <c r="D84" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2784,10 +2713,10 @@
         <v>PASS</v>
       </c>
       <c r="G84">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H84" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="85">
@@ -2798,7 +2727,7 @@
         <v>MOB-APP-084</v>
       </c>
       <c r="C85" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Radiating Head Pain Mobile Subsystem</v>
       </c>
       <c r="D85" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2810,10 +2739,10 @@
         <v>PASS</v>
       </c>
       <c r="G85">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H85" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="86">
@@ -2824,7 +2753,7 @@
         <v>MOB-APP-085</v>
       </c>
       <c r="C86" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Children Tooth Eruption Mobile Subsystem</v>
       </c>
       <c r="D86" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2836,10 +2765,10 @@
         <v>PASS</v>
       </c>
       <c r="G86">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H86" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="87">
@@ -2850,7 +2779,7 @@
         <v>MOB-APP-086</v>
       </c>
       <c r="C87" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Pediatric Dental Emergency Mobile Subsystem</v>
       </c>
       <c r="D87" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2862,10 +2791,10 @@
         <v>PASS</v>
       </c>
       <c r="G87">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H87" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="88">
@@ -2876,7 +2805,7 @@
         <v>MOB-APP-087</v>
       </c>
       <c r="C88" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Pregnancy Safe Dental Mobile Subsystem</v>
       </c>
       <c r="D88" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2888,10 +2817,10 @@
         <v>PASS</v>
       </c>
       <c r="G88">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H88" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="89">
@@ -2902,7 +2831,7 @@
         <v>MOB-APP-088</v>
       </c>
       <c r="C89" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Diabetes Periodontal Disease Mobile Subsystem</v>
       </c>
       <c r="D89" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2914,10 +2843,10 @@
         <v>PASS</v>
       </c>
       <c r="G89">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H89" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="90">
@@ -2928,7 +2857,7 @@
         <v>MOB-APP-089</v>
       </c>
       <c r="C90" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Smoker Stain &amp; Mobile Subsystem</v>
       </c>
       <c r="D90" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2940,10 +2869,10 @@
         <v>PASS</v>
       </c>
       <c r="G90">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H90" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="91">
@@ -2954,7 +2883,7 @@
         <v>MOB-APP-090</v>
       </c>
       <c r="C91" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Sports Mouthguard Impact Mobile Subsystem</v>
       </c>
       <c r="D91" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2966,10 +2895,10 @@
         <v>PASS</v>
       </c>
       <c r="G91">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H91" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="92">
@@ -2980,7 +2909,7 @@
         <v>MOB-APP-091</v>
       </c>
       <c r="C92" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Mobile Screen Reader Mobile Subsystem</v>
       </c>
       <c r="D92" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -2992,10 +2921,10 @@
         <v>PASS</v>
       </c>
       <c r="G92">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H92" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="93">
@@ -3006,7 +2935,7 @@
         <v>MOB-APP-092</v>
       </c>
       <c r="C93" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>VoiceOver / TalkBack Mobile Subsystem</v>
       </c>
       <c r="D93" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3018,10 +2947,10 @@
         <v>PASS</v>
       </c>
       <c r="G93">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H93" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="94">
@@ -3032,7 +2961,7 @@
         <v>MOB-APP-093</v>
       </c>
       <c r="C94" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>High Contrast Color Mobile Subsystem</v>
       </c>
       <c r="D94" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3044,10 +2973,10 @@
         <v>PASS</v>
       </c>
       <c r="G94">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H94" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="95">
@@ -3058,7 +2987,7 @@
         <v>MOB-APP-094</v>
       </c>
       <c r="C95" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Large Touch Target Mobile Subsystem</v>
       </c>
       <c r="D95" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3070,10 +2999,10 @@
         <v>PASS</v>
       </c>
       <c r="G95">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H95" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="96">
@@ -3084,7 +3013,7 @@
         <v>MOB-APP-095</v>
       </c>
       <c r="C96" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Audio Description Voiceover Mobile Subsystem</v>
       </c>
       <c r="D96" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3096,10 +3025,10 @@
         <v>PASS</v>
       </c>
       <c r="G96">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H96" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="97">
@@ -3110,7 +3039,7 @@
         <v>MOB-APP-096</v>
       </c>
       <c r="C97" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Save Diagnosis To Mobile Subsystem</v>
       </c>
       <c r="D97" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3122,10 +3051,10 @@
         <v>PASS</v>
       </c>
       <c r="G97">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H97" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="98">
@@ -3136,7 +3065,7 @@
         <v>MOB-APP-097</v>
       </c>
       <c r="C98" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Back Button Navigation Mobile Subsystem</v>
       </c>
       <c r="D98" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3148,10 +3077,10 @@
         <v>PASS</v>
       </c>
       <c r="G98">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H98" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="99">
@@ -3162,7 +3091,7 @@
         <v>MOB-APP-098</v>
       </c>
       <c r="C99" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Progress Bar Step Mobile Subsystem</v>
       </c>
       <c r="D99" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3174,10 +3103,10 @@
         <v>PASS</v>
       </c>
       <c r="G99">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H99" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="100">
@@ -3188,7 +3117,7 @@
         <v>MOB-APP-099</v>
       </c>
       <c r="C100" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Submit Symptom Survey Mobile Subsystem</v>
       </c>
       <c r="D100" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3200,10 +3129,10 @@
         <v>PASS</v>
       </c>
       <c r="G100">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H100" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="101">
@@ -3214,7 +3143,7 @@
         <v>MOB-APP-100</v>
       </c>
       <c r="C101" t="str">
-        <v>Mobile Symptom Wizard</v>
+        <v>Triage Results Doctor Mobile Subsystem</v>
       </c>
       <c r="D101" t="str">
         <v>02_symptom_checker.test.js</v>
@@ -3226,10 +3155,10 @@
         <v>PASS</v>
       </c>
       <c r="G101">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H101" t="str">
-        <v>2026-08-06T05:04:18.591Z</v>
+        <v>2026-08-06T05:06:54.417Z</v>
       </c>
     </row>
     <row r="102">
@@ -3240,7 +3169,7 @@
         <v>MOB-APP-101</v>
       </c>
       <c r="C102" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Mobile Doctor List Mobile Subsystem</v>
       </c>
       <c r="D102" t="str">
         <v>03_appointments.test.js</v>
@@ -3252,10 +3181,10 @@
         <v>PASS</v>
       </c>
       <c r="G102">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H102" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="103">
@@ -3266,7 +3195,7 @@
         <v>MOB-APP-102</v>
       </c>
       <c r="C103" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Filter Doctors By Mobile Subsystem</v>
       </c>
       <c r="D103" t="str">
         <v>03_appointments.test.js</v>
@@ -3278,10 +3207,10 @@
         <v>PASS</v>
       </c>
       <c r="G103">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="104">
@@ -3292,7 +3221,7 @@
         <v>MOB-APP-103</v>
       </c>
       <c r="C104" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Filter Doctors By Mobile Subsystem</v>
       </c>
       <c r="D104" t="str">
         <v>03_appointments.test.js</v>
@@ -3304,10 +3233,10 @@
         <v>PASS</v>
       </c>
       <c r="G104">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="105">
@@ -3318,7 +3247,7 @@
         <v>MOB-APP-104</v>
       </c>
       <c r="C105" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Doctor Card Swipe Mobile Subsystem</v>
       </c>
       <c r="D105" t="str">
         <v>03_appointments.test.js</v>
@@ -3330,10 +3259,10 @@
         <v>PASS</v>
       </c>
       <c r="G105">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H105" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="106">
@@ -3344,7 +3273,7 @@
         <v>MOB-APP-105</v>
       </c>
       <c r="C106" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Tap Doctor Card Mobile Subsystem</v>
       </c>
       <c r="D106" t="str">
         <v>03_appointments.test.js</v>
@@ -3356,10 +3285,10 @@
         <v>PASS</v>
       </c>
       <c r="G106">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H106" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="107">
@@ -3370,7 +3299,7 @@
         <v>MOB-APP-106</v>
       </c>
       <c r="C107" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Native Date Picker Mobile Subsystem</v>
       </c>
       <c r="D107" t="str">
         <v>03_appointments.test.js</v>
@@ -3382,10 +3311,10 @@
         <v>PASS</v>
       </c>
       <c r="G107">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H107" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="108">
@@ -3396,7 +3325,7 @@
         <v>MOB-APP-107</v>
       </c>
       <c r="C108" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Time Slot Grid Mobile Subsystem</v>
       </c>
       <c r="D108" t="str">
         <v>03_appointments.test.js</v>
@@ -3408,10 +3337,10 @@
         <v>PASS</v>
       </c>
       <c r="G108">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H108" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="109">
@@ -3422,7 +3351,7 @@
         <v>MOB-APP-108</v>
       </c>
       <c r="C109" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Emergency Same-Day Slot Mobile Subsystem</v>
       </c>
       <c r="D109" t="str">
         <v>03_appointments.test.js</v>
@@ -3434,10 +3363,10 @@
         <v>PASS</v>
       </c>
       <c r="G109">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H109" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="110">
@@ -3448,7 +3377,7 @@
         <v>MOB-APP-109</v>
       </c>
       <c r="C110" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Book Appointment Button Mobile Subsystem</v>
       </c>
       <c r="D110" t="str">
         <v>03_appointments.test.js</v>
@@ -3460,10 +3389,10 @@
         <v>PASS</v>
       </c>
       <c r="G110">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H110" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="111">
@@ -3474,7 +3403,7 @@
         <v>MOB-APP-110</v>
       </c>
       <c r="C111" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Insurance Card Camera Mobile Subsystem</v>
       </c>
       <c r="D111" t="str">
         <v>03_appointments.test.js</v>
@@ -3486,10 +3415,10 @@
         <v>PASS</v>
       </c>
       <c r="G111">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H111" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.422Z</v>
       </c>
     </row>
     <row r="112">
@@ -3500,7 +3429,7 @@
         <v>MOB-APP-111</v>
       </c>
       <c r="C112" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Insurance Member ID Mobile Subsystem</v>
       </c>
       <c r="D112" t="str">
         <v>03_appointments.test.js</v>
@@ -3512,10 +3441,10 @@
         <v>PASS</v>
       </c>
       <c r="G112">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H112" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="113">
@@ -3526,7 +3455,7 @@
         <v>MOB-APP-112</v>
       </c>
       <c r="C113" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Add Appointment Event Mobile Subsystem</v>
       </c>
       <c r="D113" t="str">
         <v>03_appointments.test.js</v>
@@ -3538,10 +3467,10 @@
         <v>PASS</v>
       </c>
       <c r="G113">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H113" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="114">
@@ -3552,7 +3481,7 @@
         <v>MOB-APP-113</v>
       </c>
       <c r="C114" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Add Appointment Event Mobile Subsystem</v>
       </c>
       <c r="D114" t="str">
         <v>03_appointments.test.js</v>
@@ -3564,10 +3493,10 @@
         <v>PASS</v>
       </c>
       <c r="G114">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H114" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="115">
@@ -3578,7 +3507,7 @@
         <v>MOB-APP-114</v>
       </c>
       <c r="C115" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Set Native Push Mobile Subsystem</v>
       </c>
       <c r="D115" t="str">
         <v>03_appointments.test.js</v>
@@ -3590,10 +3519,10 @@
         <v>PASS</v>
       </c>
       <c r="G115">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H115" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="116">
@@ -3604,7 +3533,7 @@
         <v>MOB-APP-115</v>
       </c>
       <c r="C116" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Reschedule Slot Drag-and-Drop Mobile Subsystem</v>
       </c>
       <c r="D116" t="str">
         <v>03_appointments.test.js</v>
@@ -3616,10 +3545,10 @@
         <v>PASS</v>
       </c>
       <c r="G116">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H116" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="117">
@@ -3630,7 +3559,7 @@
         <v>MOB-APP-116</v>
       </c>
       <c r="C117" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Cancellation Reason Bottom Mobile Subsystem</v>
       </c>
       <c r="D117" t="str">
         <v>03_appointments.test.js</v>
@@ -3642,10 +3571,10 @@
         <v>PASS</v>
       </c>
       <c r="G117">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H117" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="118">
@@ -3656,7 +3585,7 @@
         <v>MOB-APP-117</v>
       </c>
       <c r="C118" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Cancellation Refund Processing Mobile Subsystem</v>
       </c>
       <c r="D118" t="str">
         <v>03_appointments.test.js</v>
@@ -3668,10 +3597,10 @@
         <v>PASS</v>
       </c>
       <c r="G118">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H118" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="119">
@@ -3682,7 +3611,7 @@
         <v>MOB-APP-118</v>
       </c>
       <c r="C119" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Past Appointments Accordion Mobile Subsystem</v>
       </c>
       <c r="D119" t="str">
         <v>03_appointments.test.js</v>
@@ -3694,10 +3623,10 @@
         <v>PASS</v>
       </c>
       <c r="G119">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H119" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="120">
@@ -3708,7 +3637,7 @@
         <v>MOB-APP-119</v>
       </c>
       <c r="C120" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Download PDF Visit Mobile Subsystem</v>
       </c>
       <c r="D120" t="str">
         <v>03_appointments.test.js</v>
@@ -3720,10 +3649,10 @@
         <v>PASS</v>
       </c>
       <c r="G120">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H120" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="121">
@@ -3734,7 +3663,7 @@
         <v>MOB-APP-120</v>
       </c>
       <c r="C121" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Clinic Directions Tap Mobile Subsystem</v>
       </c>
       <c r="D121" t="str">
         <v>03_appointments.test.js</v>
@@ -3746,10 +3675,10 @@
         <v>PASS</v>
       </c>
       <c r="G121">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H121" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="122">
@@ -3760,7 +3689,7 @@
         <v>MOB-APP-121</v>
       </c>
       <c r="C122" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Clinic Directions Tap Mobile Subsystem</v>
       </c>
       <c r="D122" t="str">
         <v>03_appointments.test.js</v>
@@ -3772,10 +3701,10 @@
         <v>PASS</v>
       </c>
       <c r="G122">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H122" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="123">
@@ -3786,7 +3715,7 @@
         <v>MOB-APP-122</v>
       </c>
       <c r="C123" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Call Clinic Desk Mobile Subsystem</v>
       </c>
       <c r="D123" t="str">
         <v>03_appointments.test.js</v>
@@ -3798,10 +3727,10 @@
         <v>PASS</v>
       </c>
       <c r="G123">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H123" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="124">
@@ -3812,7 +3741,7 @@
         <v>MOB-APP-123</v>
       </c>
       <c r="C124" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Doctor Rating 5-Star Mobile Subsystem</v>
       </c>
       <c r="D124" t="str">
         <v>03_appointments.test.js</v>
@@ -3824,10 +3753,10 @@
         <v>PASS</v>
       </c>
       <c r="G124">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H124" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="125">
@@ -3838,7 +3767,7 @@
         <v>MOB-APP-124</v>
       </c>
       <c r="C125" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Submit Patient Review Mobile Subsystem</v>
       </c>
       <c r="D125" t="str">
         <v>03_appointments.test.js</v>
@@ -3850,10 +3779,10 @@
         <v>PASS</v>
       </c>
       <c r="G125">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H125" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="126">
@@ -3864,7 +3793,7 @@
         <v>MOB-APP-125</v>
       </c>
       <c r="C126" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Payment Checkout Via Mobile Subsystem</v>
       </c>
       <c r="D126" t="str">
         <v>03_appointments.test.js</v>
@@ -3876,10 +3805,10 @@
         <v>PASS</v>
       </c>
       <c r="G126">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H126" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="127">
@@ -3890,7 +3819,7 @@
         <v>MOB-APP-126</v>
       </c>
       <c r="C127" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Payment Checkout Via Mobile Subsystem</v>
       </c>
       <c r="D127" t="str">
         <v>03_appointments.test.js</v>
@@ -3902,10 +3831,10 @@
         <v>PASS</v>
       </c>
       <c r="G127">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H127" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="128">
@@ -3916,7 +3845,7 @@
         <v>MOB-APP-127</v>
       </c>
       <c r="C128" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Saved Credit Card Mobile Subsystem</v>
       </c>
       <c r="D128" t="str">
         <v>03_appointments.test.js</v>
@@ -3928,10 +3857,10 @@
         <v>PASS</v>
       </c>
       <c r="G128">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H128" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="129">
@@ -3942,7 +3871,7 @@
         <v>MOB-APP-128</v>
       </c>
       <c r="C129" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Add New Payment Mobile Subsystem</v>
       </c>
       <c r="D129" t="str">
         <v>03_appointments.test.js</v>
@@ -3954,10 +3883,10 @@
         <v>PASS</v>
       </c>
       <c r="G129">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H129" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="130">
@@ -3968,7 +3897,7 @@
         <v>MOB-APP-129</v>
       </c>
       <c r="C130" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Waiting List Notification Mobile Subsystem</v>
       </c>
       <c r="D130" t="str">
         <v>03_appointments.test.js</v>
@@ -3980,10 +3909,10 @@
         <v>PASS</v>
       </c>
       <c r="G130">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H130" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="131">
@@ -3994,7 +3923,7 @@
         <v>MOB-APP-130</v>
       </c>
       <c r="C131" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Family Member Profile Mobile Subsystem</v>
       </c>
       <c r="D131" t="str">
         <v>03_appointments.test.js</v>
@@ -4006,10 +3935,10 @@
         <v>PASS</v>
       </c>
       <c r="G131">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H131" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="132">
@@ -4020,7 +3949,7 @@
         <v>MOB-APP-131</v>
       </c>
       <c r="C132" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Virtual Waiting Room Mobile Subsystem</v>
       </c>
       <c r="D132" t="str">
         <v>03_appointments.test.js</v>
@@ -4032,10 +3961,10 @@
         <v>PASS</v>
       </c>
       <c r="G132">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H132" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="133">
@@ -4046,7 +3975,7 @@
         <v>MOB-APP-132</v>
       </c>
       <c r="C133" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Mobile Check-In Button Mobile Subsystem</v>
       </c>
       <c r="D133" t="str">
         <v>03_appointments.test.js</v>
@@ -4058,10 +3987,10 @@
         <v>PASS</v>
       </c>
       <c r="G133">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H133" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="134">
@@ -4072,7 +4001,7 @@
         <v>MOB-APP-133</v>
       </c>
       <c r="C134" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Pre-Visit Health Form Mobile Subsystem</v>
       </c>
       <c r="D134" t="str">
         <v>03_appointments.test.js</v>
@@ -4084,10 +4013,10 @@
         <v>PASS</v>
       </c>
       <c r="G134">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H134" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="135">
@@ -4098,7 +4027,7 @@
         <v>MOB-APP-134</v>
       </c>
       <c r="C135" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Upload Prior Dental Mobile Subsystem</v>
       </c>
       <c r="D135" t="str">
         <v>03_appointments.test.js</v>
@@ -4110,10 +4039,10 @@
         <v>PASS</v>
       </c>
       <c r="G135">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H135" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="136">
@@ -4124,7 +4053,7 @@
         <v>MOB-APP-135</v>
       </c>
       <c r="C136" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Appointment Confirmation QR Mobile Subsystem</v>
       </c>
       <c r="D136" t="str">
         <v>03_appointments.test.js</v>
@@ -4136,10 +4065,10 @@
         <v>PASS</v>
       </c>
       <c r="G136">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H136" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="137">
@@ -4150,7 +4079,7 @@
         <v>MOB-APP-136</v>
       </c>
       <c r="C137" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>QR Code Scan Mobile Subsystem</v>
       </c>
       <c r="D137" t="str">
         <v>03_appointments.test.js</v>
@@ -4162,10 +4091,10 @@
         <v>PASS</v>
       </c>
       <c r="G137">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H137" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="138">
@@ -4176,7 +4105,7 @@
         <v>MOB-APP-137</v>
       </c>
       <c r="C138" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Doctor Bio Video Mobile Subsystem</v>
       </c>
       <c r="D138" t="str">
         <v>03_appointments.test.js</v>
@@ -4188,10 +4117,10 @@
         <v>PASS</v>
       </c>
       <c r="G138">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H138" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="139">
@@ -4202,7 +4131,7 @@
         <v>MOB-APP-138</v>
       </c>
       <c r="C139" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Doctor Languages Spoken Mobile Subsystem</v>
       </c>
       <c r="D139" t="str">
         <v>03_appointments.test.js</v>
@@ -4214,10 +4143,10 @@
         <v>PASS</v>
       </c>
       <c r="G139">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H139" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="140">
@@ -4228,7 +4157,7 @@
         <v>MOB-APP-139</v>
       </c>
       <c r="C140" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>In-App Telehealth Video Mobile Subsystem</v>
       </c>
       <c r="D140" t="str">
         <v>03_appointments.test.js</v>
@@ -4240,10 +4169,10 @@
         <v>PASS</v>
       </c>
       <c r="G140">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H140" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="141">
@@ -4254,7 +4183,7 @@
         <v>MOB-APP-140</v>
       </c>
       <c r="C141" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Telehealth Video Camera Mobile Subsystem</v>
       </c>
       <c r="D141" t="str">
         <v>03_appointments.test.js</v>
@@ -4266,10 +4195,10 @@
         <v>PASS</v>
       </c>
       <c r="G141">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H141" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="142">
@@ -4280,7 +4209,7 @@
         <v>MOB-APP-141</v>
       </c>
       <c r="C142" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Telehealth Video Mute Mobile Subsystem</v>
       </c>
       <c r="D142" t="str">
         <v>03_appointments.test.js</v>
@@ -4292,10 +4221,10 @@
         <v>PASS</v>
       </c>
       <c r="G142">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H142" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="143">
@@ -4306,7 +4235,7 @@
         <v>MOB-APP-142</v>
       </c>
       <c r="C143" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Telehealth In-Call Chat Mobile Subsystem</v>
       </c>
       <c r="D143" t="str">
         <v>03_appointments.test.js</v>
@@ -4318,10 +4247,10 @@
         <v>PASS</v>
       </c>
       <c r="G143">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H143" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="144">
@@ -4332,7 +4261,7 @@
         <v>MOB-APP-143</v>
       </c>
       <c r="C144" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>End Telehealth Call Mobile Subsystem</v>
       </c>
       <c r="D144" t="str">
         <v>03_appointments.test.js</v>
@@ -4344,10 +4273,10 @@
         <v>PASS</v>
       </c>
       <c r="G144">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H144" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="145">
@@ -4358,7 +4287,7 @@
         <v>MOB-APP-144</v>
       </c>
       <c r="C145" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Post-Consultation Prescription Notification Mobile Subsystem</v>
       </c>
       <c r="D145" t="str">
         <v>03_appointments.test.js</v>
@@ -4370,10 +4299,10 @@
         <v>PASS</v>
       </c>
       <c r="G145">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H145" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="146">
@@ -4384,7 +4313,7 @@
         <v>MOB-APP-145</v>
       </c>
       <c r="C146" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Pharmacy Selection Map Mobile Subsystem</v>
       </c>
       <c r="D146" t="str">
         <v>03_appointments.test.js</v>
@@ -4396,10 +4325,10 @@
         <v>PASS</v>
       </c>
       <c r="G146">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H146" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="147">
@@ -4410,7 +4339,7 @@
         <v>MOB-APP-146</v>
       </c>
       <c r="C147" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Send Rx Directly Mobile Subsystem</v>
       </c>
       <c r="D147" t="str">
         <v>03_appointments.test.js</v>
@@ -4422,10 +4351,10 @@
         <v>PASS</v>
       </c>
       <c r="G147">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H147" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="148">
@@ -4436,7 +4365,7 @@
         <v>MOB-APP-147</v>
       </c>
       <c r="C148" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Appointment Follow-Up Booking Mobile Subsystem</v>
       </c>
       <c r="D148" t="str">
         <v>03_appointments.test.js</v>
@@ -4448,10 +4377,10 @@
         <v>PASS</v>
       </c>
       <c r="G148">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H148" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="149">
@@ -4462,7 +4391,7 @@
         <v>MOB-APP-148</v>
       </c>
       <c r="C149" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Cancel Confirmation Toast Mobile Subsystem</v>
       </c>
       <c r="D149" t="str">
         <v>03_appointments.test.js</v>
@@ -4474,10 +4403,10 @@
         <v>PASS</v>
       </c>
       <c r="G149">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H149" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="150">
@@ -4488,7 +4417,7 @@
         <v>MOB-APP-149</v>
       </c>
       <c r="C150" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Appointment History Search Mobile Subsystem</v>
       </c>
       <c r="D150" t="str">
         <v>03_appointments.test.js</v>
@@ -4500,10 +4429,10 @@
         <v>PASS</v>
       </c>
       <c r="G150">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H150" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="151">
@@ -4514,7 +4443,7 @@
         <v>MOB-APP-150</v>
       </c>
       <c r="C151" t="str">
-        <v>Mobile Booking &amp; Calendar</v>
+        <v>Re-book Past Doctor Mobile Subsystem</v>
       </c>
       <c r="D151" t="str">
         <v>03_appointments.test.js</v>
@@ -4526,10 +4455,10 @@
         <v>PASS</v>
       </c>
       <c r="G151">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H151" t="str">
-        <v>2026-08-06T05:04:18.598Z</v>
+        <v>2026-08-06T05:06:54.423Z</v>
       </c>
     </row>
     <row r="152">
@@ -4540,7 +4469,7 @@
         <v>MOB-APP-151</v>
       </c>
       <c r="C152" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Mobile AI Consultation Mobile Subsystem</v>
       </c>
       <c r="D152" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4552,10 +4481,10 @@
         <v>PASS</v>
       </c>
       <c r="G152">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H152" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="153">
@@ -4566,7 +4495,7 @@
         <v>MOB-APP-152</v>
       </c>
       <c r="C153" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Expand Mobile Chat Mobile Subsystem</v>
       </c>
       <c r="D153" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4581,7 +4510,7 @@
         <v>23</v>
       </c>
       <c r="H153" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="154">
@@ -4592,7 +4521,7 @@
         <v>MOB-APP-153</v>
       </c>
       <c r="C154" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Send Text Message Mobile Subsystem</v>
       </c>
       <c r="D154" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4604,10 +4533,10 @@
         <v>PASS</v>
       </c>
       <c r="G154">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H154" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="155">
@@ -4618,7 +4547,7 @@
         <v>MOB-APP-154</v>
       </c>
       <c r="C155" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Verify Real-Time Streaming Mobile Subsystem</v>
       </c>
       <c r="D155" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4630,10 +4559,10 @@
         <v>PASS</v>
       </c>
       <c r="G155">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H155" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="156">
@@ -4644,7 +4573,7 @@
         <v>MOB-APP-155</v>
       </c>
       <c r="C156" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Typing Dots Animation Mobile Subsystem</v>
       </c>
       <c r="D156" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4656,10 +4585,10 @@
         <v>PASS</v>
       </c>
       <c r="G156">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H156" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="157">
@@ -4670,7 +4599,7 @@
         <v>MOB-APP-156</v>
       </c>
       <c r="C157" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Clinical Disclaimer Sticky Mobile Subsystem</v>
       </c>
       <c r="D157" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4682,10 +4611,10 @@
         <v>PASS</v>
       </c>
       <c r="G157">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H157" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="158">
@@ -4696,7 +4625,7 @@
         <v>MOB-APP-157</v>
       </c>
       <c r="C158" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Quick Reply Chips Mobile Subsystem</v>
       </c>
       <c r="D158" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4708,10 +4637,10 @@
         <v>PASS</v>
       </c>
       <c r="G158">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H158" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="159">
@@ -4722,7 +4651,7 @@
         <v>MOB-APP-158</v>
       </c>
       <c r="C159" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Capture Photo With Mobile Subsystem</v>
       </c>
       <c r="D159" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4737,7 +4666,7 @@
         <v>28</v>
       </c>
       <c r="H159" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="160">
@@ -4748,7 +4677,7 @@
         <v>MOB-APP-159</v>
       </c>
       <c r="C160" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Pick X-Ray Photo Mobile Subsystem</v>
       </c>
       <c r="D160" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4760,10 +4689,10 @@
         <v>PASS</v>
       </c>
       <c r="G160">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H160" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="161">
@@ -4774,7 +4703,7 @@
         <v>MOB-APP-160</v>
       </c>
       <c r="C161" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Voice Message Push-to-Talk Mobile Subsystem</v>
       </c>
       <c r="D161" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4786,10 +4715,10 @@
         <v>PASS</v>
       </c>
       <c r="G161">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H161" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="162">
@@ -4800,7 +4729,7 @@
         <v>MOB-APP-161</v>
       </c>
       <c r="C162" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Voice Message Recording Mobile Subsystem</v>
       </c>
       <c r="D162" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4812,10 +4741,10 @@
         <v>PASS</v>
       </c>
       <c r="G162">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H162" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="163">
@@ -4826,7 +4755,7 @@
         <v>MOB-APP-162</v>
       </c>
       <c r="C163" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Cancel Voice Recording Mobile Subsystem</v>
       </c>
       <c r="D163" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4838,10 +4767,10 @@
         <v>PASS</v>
       </c>
       <c r="G163">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H163" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="164">
@@ -4852,7 +4781,7 @@
         <v>MOB-APP-163</v>
       </c>
       <c r="C164" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Voice Message Audio Mobile Subsystem</v>
       </c>
       <c r="D164" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4864,10 +4793,10 @@
         <v>PASS</v>
       </c>
       <c r="G164">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H164" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="165">
@@ -4878,7 +4807,7 @@
         <v>MOB-APP-164</v>
       </c>
       <c r="C165" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Audio Playback Speed Mobile Subsystem</v>
       </c>
       <c r="D165" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4890,10 +4819,10 @@
         <v>PASS</v>
       </c>
       <c r="G165">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H165" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="166">
@@ -4904,7 +4833,7 @@
         <v>MOB-APP-165</v>
       </c>
       <c r="C166" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Long Press Message Mobile Subsystem</v>
       </c>
       <c r="D166" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4916,10 +4845,10 @@
         <v>PASS</v>
       </c>
       <c r="G166">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H166" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="167">
@@ -4930,7 +4859,7 @@
         <v>MOB-APP-166</v>
       </c>
       <c r="C167" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Copy Message Text Mobile Subsystem</v>
       </c>
       <c r="D167" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4942,10 +4871,10 @@
         <v>PASS</v>
       </c>
       <c r="G167">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H167" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="168">
@@ -4956,7 +4885,7 @@
         <v>MOB-APP-167</v>
       </c>
       <c r="C168" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Share Message Text Mobile Subsystem</v>
       </c>
       <c r="D168" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4968,10 +4897,10 @@
         <v>PASS</v>
       </c>
       <c r="G168">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H168" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="169">
@@ -4982,7 +4911,7 @@
         <v>MOB-APP-168</v>
       </c>
       <c r="C169" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Rate Response Thumbs Mobile Subsystem</v>
       </c>
       <c r="D169" t="str">
         <v>04_ai_chat.test.js</v>
@@ -4994,10 +4923,10 @@
         <v>PASS</v>
       </c>
       <c r="G169">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H169" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="170">
@@ -5008,7 +4937,7 @@
         <v>MOB-APP-169</v>
       </c>
       <c r="C170" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Regenerate Response Swipe Mobile Subsystem</v>
       </c>
       <c r="D170" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5020,10 +4949,10 @@
         <v>PASS</v>
       </c>
       <c r="G170">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H170" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="171">
@@ -5034,7 +4963,7 @@
         <v>MOB-APP-170</v>
       </c>
       <c r="C171" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Chat Thread Sidebar Mobile Subsystem</v>
       </c>
       <c r="D171" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5046,10 +4975,10 @@
         <v>PASS</v>
       </c>
       <c r="G171">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H171" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="172">
@@ -5060,7 +4989,7 @@
         <v>MOB-APP-171</v>
       </c>
       <c r="C172" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Search Chat History Mobile Subsystem</v>
       </c>
       <c r="D172" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5072,10 +5001,10 @@
         <v>PASS</v>
       </c>
       <c r="G172">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H172" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="173">
@@ -5086,7 +5015,7 @@
         <v>MOB-APP-172</v>
       </c>
       <c r="C173" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Rename Chat Session Mobile Subsystem</v>
       </c>
       <c r="D173" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5098,10 +5027,10 @@
         <v>PASS</v>
       </c>
       <c r="G173">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H173" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="174">
@@ -5112,7 +5041,7 @@
         <v>MOB-APP-173</v>
       </c>
       <c r="C174" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Swipe To Delete Mobile Subsystem</v>
       </c>
       <c r="D174" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5124,10 +5053,10 @@
         <v>PASS</v>
       </c>
       <c r="G174">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H174" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="175">
@@ -5138,7 +5067,7 @@
         <v>MOB-APP-174</v>
       </c>
       <c r="C175" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Export Full Chat Mobile Subsystem</v>
       </c>
       <c r="D175" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5153,7 +5082,7 @@
         <v>19</v>
       </c>
       <c r="H175" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="176">
@@ -5164,7 +5093,7 @@
         <v>MOB-APP-175</v>
       </c>
       <c r="C176" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Export Full Chat Mobile Subsystem</v>
       </c>
       <c r="D176" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5176,10 +5105,10 @@
         <v>PASS</v>
       </c>
       <c r="G176">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H176" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="177">
@@ -5190,7 +5119,7 @@
         <v>MOB-APP-176</v>
       </c>
       <c r="C177" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Medical Terminology Highlighted Mobile Subsystem</v>
       </c>
       <c r="D177" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5202,10 +5131,10 @@
         <v>PASS</v>
       </c>
       <c r="G177">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H177" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="178">
@@ -5216,7 +5145,7 @@
         <v>MOB-APP-177</v>
       </c>
       <c r="C178" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Medication Dosage Alert Mobile Subsystem</v>
       </c>
       <c r="D178" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5228,10 +5157,10 @@
         <v>PASS</v>
       </c>
       <c r="G178">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H178" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="179">
@@ -5242,7 +5171,7 @@
         <v>MOB-APP-178</v>
       </c>
       <c r="C179" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Emergency Upgrade Red Mobile Subsystem</v>
       </c>
       <c r="D179" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5254,10 +5183,10 @@
         <v>PASS</v>
       </c>
       <c r="G179">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H179" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="180">
@@ -5268,7 +5197,7 @@
         <v>MOB-APP-179</v>
       </c>
       <c r="C180" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Book Appointment Direct Mobile Subsystem</v>
       </c>
       <c r="D180" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5280,10 +5209,10 @@
         <v>PASS</v>
       </c>
       <c r="G180">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H180" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="181">
@@ -5294,7 +5223,7 @@
         <v>MOB-APP-180</v>
       </c>
       <c r="C181" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Clear Active Chat Mobile Subsystem</v>
       </c>
       <c r="D181" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5306,10 +5235,10 @@
         <v>PASS</v>
       </c>
       <c r="G181">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H181" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="182">
@@ -5320,7 +5249,7 @@
         <v>MOB-APP-181</v>
       </c>
       <c r="C182" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Switch AI Persona Mobile Subsystem</v>
       </c>
       <c r="D182" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5332,10 +5261,10 @@
         <v>PASS</v>
       </c>
       <c r="G182">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H182" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="183">
@@ -5346,7 +5275,7 @@
         <v>MOB-APP-182</v>
       </c>
       <c r="C183" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Switch AI Persona Mobile Subsystem</v>
       </c>
       <c r="D183" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5358,10 +5287,10 @@
         <v>PASS</v>
       </c>
       <c r="G183">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H183" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="184">
@@ -5372,7 +5301,7 @@
         <v>MOB-APP-183</v>
       </c>
       <c r="C184" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Token Counter &amp; Mobile Subsystem</v>
       </c>
       <c r="D184" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5384,10 +5313,10 @@
         <v>PASS</v>
       </c>
       <c r="G184">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H184" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="185">
@@ -5398,7 +5327,7 @@
         <v>MOB-APP-184</v>
       </c>
       <c r="C185" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Markdown Formatted List Mobile Subsystem</v>
       </c>
       <c r="D185" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5410,10 +5339,10 @@
         <v>PASS</v>
       </c>
       <c r="G185">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H185" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="186">
@@ -5424,7 +5353,7 @@
         <v>MOB-APP-185</v>
       </c>
       <c r="C186" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Markdown Formatted Table Mobile Subsystem</v>
       </c>
       <c r="D186" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5436,10 +5365,10 @@
         <v>PASS</v>
       </c>
       <c r="G186">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H186" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="187">
@@ -5450,7 +5379,7 @@
         <v>MOB-APP-186</v>
       </c>
       <c r="C187" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Hyperlink Tap Launches Mobile Subsystem</v>
       </c>
       <c r="D187" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5462,10 +5391,10 @@
         <v>PASS</v>
       </c>
       <c r="G187">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H187" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="188">
@@ -5476,7 +5405,7 @@
         <v>MOB-APP-187</v>
       </c>
       <c r="C188" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Network Reconnection Auto-Resume Mobile Subsystem</v>
       </c>
       <c r="D188" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5488,10 +5417,10 @@
         <v>PASS</v>
       </c>
       <c r="G188">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H188" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="189">
@@ -5502,7 +5431,7 @@
         <v>MOB-APP-188</v>
       </c>
       <c r="C189" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Chat List Auto-Scroll Mobile Subsystem</v>
       </c>
       <c r="D189" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5514,10 +5443,10 @@
         <v>PASS</v>
       </c>
       <c r="G189">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H189" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="190">
@@ -5528,7 +5457,7 @@
         <v>MOB-APP-189</v>
       </c>
       <c r="C190" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Dismiss Keyboard On Mobile Subsystem</v>
       </c>
       <c r="D190" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5540,10 +5469,10 @@
         <v>PASS</v>
       </c>
       <c r="G190">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="H190" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="191">
@@ -5554,7 +5483,7 @@
         <v>MOB-APP-190</v>
       </c>
       <c r="C191" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Unread Message Count Mobile Subsystem</v>
       </c>
       <c r="D191" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5566,10 +5495,10 @@
         <v>PASS</v>
       </c>
       <c r="G191">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H191" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="192">
@@ -5580,7 +5509,7 @@
         <v>MOB-APP-191</v>
       </c>
       <c r="C192" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Multi-Line Expandable Chat Mobile Subsystem</v>
       </c>
       <c r="D192" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5592,10 +5521,10 @@
         <v>PASS</v>
       </c>
       <c r="G192">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H192" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="193">
@@ -5606,7 +5535,7 @@
         <v>MOB-APP-192</v>
       </c>
       <c r="C193" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Max Input Length Mobile Subsystem</v>
       </c>
       <c r="D193" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5618,10 +5547,10 @@
         <v>PASS</v>
       </c>
       <c r="G193">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H193" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="194">
@@ -5632,7 +5561,7 @@
         <v>MOB-APP-193</v>
       </c>
       <c r="C194" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Empty Message Submit Mobile Subsystem</v>
       </c>
       <c r="D194" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5644,10 +5573,10 @@
         <v>PASS</v>
       </c>
       <c r="G194">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H194" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="195">
@@ -5658,7 +5587,7 @@
         <v>MOB-APP-194</v>
       </c>
       <c r="C195" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Emoji Picker Keyboard Mobile Subsystem</v>
       </c>
       <c r="D195" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5670,10 +5599,10 @@
         <v>PASS</v>
       </c>
       <c r="G195">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H195" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="196">
@@ -5684,7 +5613,7 @@
         <v>MOB-APP-195</v>
       </c>
       <c r="C196" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Chat Drawer Landscape Mobile Subsystem</v>
       </c>
       <c r="D196" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5696,10 +5625,10 @@
         <v>PASS</v>
       </c>
       <c r="G196">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H196" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="197">
@@ -5710,7 +5639,7 @@
         <v>MOB-APP-196</v>
       </c>
       <c r="C197" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Font Size Adjuster Mobile Subsystem</v>
       </c>
       <c r="D197" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5722,10 +5651,10 @@
         <v>PASS</v>
       </c>
       <c r="G197">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H197" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="198">
@@ -5736,7 +5665,7 @@
         <v>MOB-APP-197</v>
       </c>
       <c r="C198" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>High Contrast Mode Mobile Subsystem</v>
       </c>
       <c r="D198" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5748,10 +5677,10 @@
         <v>PASS</v>
       </c>
       <c r="G198">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H198" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="199">
@@ -5762,7 +5691,7 @@
         <v>MOB-APP-198</v>
       </c>
       <c r="C199" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Offline Banner Display Mobile Subsystem</v>
       </c>
       <c r="D199" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5774,10 +5703,10 @@
         <v>PASS</v>
       </c>
       <c r="G199">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H199" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="200">
@@ -5788,7 +5717,7 @@
         <v>MOB-APP-199</v>
       </c>
       <c r="C200" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Socket Re-connection Retry Mobile Subsystem</v>
       </c>
       <c r="D200" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5800,10 +5729,10 @@
         <v>PASS</v>
       </c>
       <c r="G200">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H200" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="201">
@@ -5814,7 +5743,7 @@
         <v>MOB-APP-200</v>
       </c>
       <c r="C201" t="str">
-        <v>Mobile AI Consultation</v>
+        <v>Chat Session Encryption Mobile Subsystem</v>
       </c>
       <c r="D201" t="str">
         <v>04_ai_chat.test.js</v>
@@ -5826,10 +5755,10 @@
         <v>PASS</v>
       </c>
       <c r="G201">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H201" t="str">
-        <v>2026-08-06T05:04:18.604Z</v>
+        <v>2026-08-06T05:06:54.428Z</v>
       </c>
     </row>
     <row r="202">
@@ -5840,7 +5769,7 @@
         <v>MOB-APP-201</v>
       </c>
       <c r="C202" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Mobile Camera Viewfinder Mobile Subsystem</v>
       </c>
       <c r="D202" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5852,10 +5781,10 @@
         <v>PASS</v>
       </c>
       <c r="G202">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H202" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="203">
@@ -5866,7 +5795,7 @@
         <v>MOB-APP-202</v>
       </c>
       <c r="C203" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Front / Rear Mobile Subsystem</v>
       </c>
       <c r="D203" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5878,10 +5807,10 @@
         <v>PASS</v>
       </c>
       <c r="G203">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H203" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="204">
@@ -5892,7 +5821,7 @@
         <v>MOB-APP-203</v>
       </c>
       <c r="C204" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Camera Flash Mode Mobile Subsystem</v>
       </c>
       <c r="D204" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5904,10 +5833,10 @@
         <v>PASS</v>
       </c>
       <c r="G204">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H204" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="205">
@@ -5918,7 +5847,7 @@
         <v>MOB-APP-204</v>
       </c>
       <c r="C205" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Auto-Focus Target Box Mobile Subsystem</v>
       </c>
       <c r="D205" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5930,10 +5859,10 @@
         <v>PASS</v>
       </c>
       <c r="G205">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H205" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="206">
@@ -5944,7 +5873,7 @@
         <v>MOB-APP-205</v>
       </c>
       <c r="C206" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Grid Line Alignment Mobile Subsystem</v>
       </c>
       <c r="D206" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5956,10 +5885,10 @@
         <v>PASS</v>
       </c>
       <c r="G206">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H206" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="207">
@@ -5970,7 +5899,7 @@
         <v>MOB-APP-206</v>
       </c>
       <c r="C207" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Grid Line Alignment Mobile Subsystem</v>
       </c>
       <c r="D207" t="str">
         <v>05_dental_scan.test.js</v>
@@ -5982,10 +5911,10 @@
         <v>PASS</v>
       </c>
       <c r="G207">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H207" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="208">
@@ -5996,7 +5925,7 @@
         <v>MOB-APP-207</v>
       </c>
       <c r="C208" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Capture Photo Shutter Mobile Subsystem</v>
       </c>
       <c r="D208" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6008,10 +5937,10 @@
         <v>PASS</v>
       </c>
       <c r="G208">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H208" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="209">
@@ -6022,7 +5951,7 @@
         <v>MOB-APP-208</v>
       </c>
       <c r="C209" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Captured Image Review Mobile Subsystem</v>
       </c>
       <c r="D209" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6034,10 +5963,10 @@
         <v>PASS</v>
       </c>
       <c r="G209">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H209" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="210">
@@ -6048,7 +5977,7 @@
         <v>MOB-APP-209</v>
       </c>
       <c r="C210" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Crop &amp; Rotate Mobile Subsystem</v>
       </c>
       <c r="D210" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6060,10 +5989,10 @@
         <v>PASS</v>
       </c>
       <c r="G210">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="H210" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="211">
@@ -6074,7 +6003,7 @@
         <v>MOB-APP-210</v>
       </c>
       <c r="C211" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Image Brightness Slider Mobile Subsystem</v>
       </c>
       <c r="D211" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6086,10 +6015,10 @@
         <v>PASS</v>
       </c>
       <c r="G211">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H211" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="212">
@@ -6100,7 +6029,7 @@
         <v>MOB-APP-211</v>
       </c>
       <c r="C212" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Image Contrast Slider Mobile Subsystem</v>
       </c>
       <c r="D212" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6112,10 +6041,10 @@
         <v>PASS</v>
       </c>
       <c r="G212">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H212" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="213">
@@ -6126,7 +6055,7 @@
         <v>MOB-APP-212</v>
       </c>
       <c r="C213" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Upload Scan Photo Mobile Subsystem</v>
       </c>
       <c r="D213" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6138,10 +6067,10 @@
         <v>PASS</v>
       </c>
       <c r="G213">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H213" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="214">
@@ -6152,7 +6081,7 @@
         <v>MOB-APP-213</v>
       </c>
       <c r="C214" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Cavity Heatmap Color Mobile Subsystem</v>
       </c>
       <c r="D214" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6164,10 +6093,10 @@
         <v>PASS</v>
       </c>
       <c r="G214">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H214" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="215">
@@ -6178,7 +6107,7 @@
         <v>MOB-APP-214</v>
       </c>
       <c r="C215" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Plaque Accumulation Layer Mobile Subsystem</v>
       </c>
       <c r="D215" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6190,10 +6119,10 @@
         <v>PASS</v>
       </c>
       <c r="G215">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H215" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="216">
@@ -6204,7 +6133,7 @@
         <v>MOB-APP-215</v>
       </c>
       <c r="C216" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Gingivitis Redness Detection Mobile Subsystem</v>
       </c>
       <c r="D216" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6216,10 +6145,10 @@
         <v>PASS</v>
       </c>
       <c r="G216">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H216" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="217">
@@ -6230,7 +6159,7 @@
         <v>MOB-APP-216</v>
       </c>
       <c r="C217" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Enamel Micro-crack Trace Mobile Subsystem</v>
       </c>
       <c r="D217" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6242,10 +6171,10 @@
         <v>PASS</v>
       </c>
       <c r="G217">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H217" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="218">
@@ -6256,7 +6185,7 @@
         <v>MOB-APP-217</v>
       </c>
       <c r="C218" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Tooth Label Bounding Mobile Subsystem</v>
       </c>
       <c r="D218" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6268,10 +6197,10 @@
         <v>PASS</v>
       </c>
       <c r="G218">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H218" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="219">
@@ -6282,7 +6211,7 @@
         <v>MOB-APP-218</v>
       </c>
       <c r="C219" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>AI Confidence Score Mobile Subsystem</v>
       </c>
       <c r="D219" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6294,10 +6223,10 @@
         <v>PASS</v>
       </c>
       <c r="G219">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H219" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="220">
@@ -6308,7 +6237,7 @@
         <v>MOB-APP-219</v>
       </c>
       <c r="C220" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>High Risk Cavity Mobile Subsystem</v>
       </c>
       <c r="D220" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6320,10 +6249,10 @@
         <v>PASS</v>
       </c>
       <c r="G220">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H220" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="221">
@@ -6334,7 +6263,7 @@
         <v>MOB-APP-220</v>
       </c>
       <c r="C221" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Compare Current Scan Mobile Subsystem</v>
       </c>
       <c r="D221" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6349,7 +6278,7 @@
         <v>40</v>
       </c>
       <c r="H221" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="222">
@@ -6360,7 +6289,7 @@
         <v>MOB-APP-221</v>
       </c>
       <c r="C222" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Split View Dual Mobile Subsystem</v>
       </c>
       <c r="D222" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6372,10 +6301,10 @@
         <v>PASS</v>
       </c>
       <c r="G222">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H222" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="223">
@@ -6386,7 +6315,7 @@
         <v>MOB-APP-222</v>
       </c>
       <c r="C223" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Save Scan Image Mobile Subsystem</v>
       </c>
       <c r="D223" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6398,10 +6327,10 @@
         <v>PASS</v>
       </c>
       <c r="G223">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H223" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="224">
@@ -6412,7 +6341,7 @@
         <v>MOB-APP-223</v>
       </c>
       <c r="C224" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Download Detailed Analysis Mobile Subsystem</v>
       </c>
       <c r="D224" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6424,10 +6353,10 @@
         <v>PASS</v>
       </c>
       <c r="G224">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H224" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="225">
@@ -6438,7 +6367,7 @@
         <v>MOB-APP-224</v>
       </c>
       <c r="C225" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Share Scan Analysis Mobile Subsystem</v>
       </c>
       <c r="D225" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6450,10 +6379,10 @@
         <v>PASS</v>
       </c>
       <c r="G225">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H225" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="226">
@@ -6464,7 +6393,7 @@
         <v>MOB-APP-225</v>
       </c>
       <c r="C226" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>DICOM File Viewer Mobile Subsystem</v>
       </c>
       <c r="D226" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6476,10 +6405,10 @@
         <v>PASS</v>
       </c>
       <c r="G226">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H226" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="227">
@@ -6490,7 +6419,7 @@
         <v>MOB-APP-226</v>
       </c>
       <c r="C227" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>DICOM Windowing Contrast Mobile Subsystem</v>
       </c>
       <c r="D227" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6502,10 +6431,10 @@
         <v>PASS</v>
       </c>
       <c r="G227">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H227" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="228">
@@ -6516,7 +6445,7 @@
         <v>MOB-APP-227</v>
       </c>
       <c r="C228" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Distance Measurement Tool Mobile Subsystem</v>
       </c>
       <c r="D228" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6531,7 +6460,7 @@
         <v>25</v>
       </c>
       <c r="H228" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="229">
@@ -6542,7 +6471,7 @@
         <v>MOB-APP-228</v>
       </c>
       <c r="C229" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Angle Measurement Drag Mobile Subsystem</v>
       </c>
       <c r="D229" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6554,10 +6483,10 @@
         <v>PASS</v>
       </c>
       <c r="G229">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H229" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="230">
@@ -6568,7 +6497,7 @@
         <v>MOB-APP-229</v>
       </c>
       <c r="C230" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Tooth FDI Numbering Mobile Subsystem</v>
       </c>
       <c r="D230" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6580,10 +6509,10 @@
         <v>PASS</v>
       </c>
       <c r="G230">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H230" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="231">
@@ -6594,7 +6523,7 @@
         <v>MOB-APP-230</v>
       </c>
       <c r="C231" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Tooth Universal Numbering Mobile Subsystem</v>
       </c>
       <c r="D231" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6606,10 +6535,10 @@
         <v>PASS</v>
       </c>
       <c r="G231">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H231" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="232">
@@ -6620,7 +6549,7 @@
         <v>MOB-APP-231</v>
       </c>
       <c r="C232" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Diagnostic Disclaimer Acceptance Mobile Subsystem</v>
       </c>
       <c r="D232" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6632,10 +6561,10 @@
         <v>PASS</v>
       </c>
       <c r="G232">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H232" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="233">
@@ -6646,7 +6575,7 @@
         <v>MOB-APP-232</v>
       </c>
       <c r="C233" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Scan Quality Warning Mobile Subsystem</v>
       </c>
       <c r="D233" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6658,10 +6587,10 @@
         <v>PASS</v>
       </c>
       <c r="G233">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H233" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="234">
@@ -6672,7 +6601,7 @@
         <v>MOB-APP-233</v>
       </c>
       <c r="C234" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Re-take Guidance Overlay Mobile Subsystem</v>
       </c>
       <c r="D234" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6684,10 +6613,10 @@
         <v>PASS</v>
       </c>
       <c r="G234">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H234" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="235">
@@ -6698,7 +6627,7 @@
         <v>MOB-APP-234</v>
       </c>
       <c r="C235" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Incisor View Camera Mobile Subsystem</v>
       </c>
       <c r="D235" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6710,10 +6639,10 @@
         <v>PASS</v>
       </c>
       <c r="G235">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H235" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="236">
@@ -6724,7 +6653,7 @@
         <v>MOB-APP-235</v>
       </c>
       <c r="C236" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Molar View Camera Mobile Subsystem</v>
       </c>
       <c r="D236" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6736,10 +6665,10 @@
         <v>PASS</v>
       </c>
       <c r="G236">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="H236" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="237">
@@ -6750,7 +6679,7 @@
         <v>MOB-APP-236</v>
       </c>
       <c r="C237" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Bite-wing X-Ray Mode Mobile Subsystem</v>
       </c>
       <c r="D237" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6762,10 +6691,10 @@
         <v>PASS</v>
       </c>
       <c r="G237">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H237" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="238">
@@ -6776,7 +6705,7 @@
         <v>MOB-APP-237</v>
       </c>
       <c r="C238" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Panoramic Radiograph View Mobile Subsystem</v>
       </c>
       <c r="D238" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6788,10 +6717,10 @@
         <v>PASS</v>
       </c>
       <c r="G238">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H238" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="239">
@@ -6802,7 +6731,7 @@
         <v>MOB-APP-238</v>
       </c>
       <c r="C239" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>3D CBCT Volume Mobile Subsystem</v>
       </c>
       <c r="D239" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6814,10 +6743,10 @@
         <v>PASS</v>
       </c>
       <c r="G239">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H239" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="240">
@@ -6828,7 +6757,7 @@
         <v>MOB-APP-239</v>
       </c>
       <c r="C240" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Invert Image Color Mobile Subsystem</v>
       </c>
       <c r="D240" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6840,10 +6769,10 @@
         <v>PASS</v>
       </c>
       <c r="G240">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H240" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="241">
@@ -6854,7 +6783,7 @@
         <v>MOB-APP-240</v>
       </c>
       <c r="C241" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Magnifying Glass Touch Mobile Subsystem</v>
       </c>
       <c r="D241" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6866,10 +6795,10 @@
         <v>PASS</v>
       </c>
       <c r="G241">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H241" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="242">
@@ -6880,7 +6809,7 @@
         <v>MOB-APP-241</v>
       </c>
       <c r="C242" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Add Custom Note Mobile Subsystem</v>
       </c>
       <c r="D242" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6892,10 +6821,10 @@
         <v>PASS</v>
       </c>
       <c r="G242">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H242" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="243">
@@ -6906,7 +6835,7 @@
         <v>MOB-APP-242</v>
       </c>
       <c r="C243" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Save Scan To Mobile Subsystem</v>
       </c>
       <c r="D243" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6918,10 +6847,10 @@
         <v>PASS</v>
       </c>
       <c r="G243">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H243" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="244">
@@ -6932,7 +6861,7 @@
         <v>MOB-APP-243</v>
       </c>
       <c r="C244" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Tag Scan Category Mobile Subsystem</v>
       </c>
       <c r="D244" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6944,10 +6873,10 @@
         <v>PASS</v>
       </c>
       <c r="G244">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H244" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="245">
@@ -6958,7 +6887,7 @@
         <v>MOB-APP-244</v>
       </c>
       <c r="C245" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Filter Saved Scans Mobile Subsystem</v>
       </c>
       <c r="D245" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6970,10 +6899,10 @@
         <v>PASS</v>
       </c>
       <c r="G245">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H245" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="246">
@@ -6984,7 +6913,7 @@
         <v>MOB-APP-245</v>
       </c>
       <c r="C246" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Delete Scan File Mobile Subsystem</v>
       </c>
       <c r="D246" t="str">
         <v>05_dental_scan.test.js</v>
@@ -6996,10 +6925,10 @@
         <v>PASS</v>
       </c>
       <c r="G246">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H246" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="247">
@@ -7010,7 +6939,7 @@
         <v>MOB-APP-246</v>
       </c>
       <c r="C247" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Print Scan Summary Mobile Subsystem</v>
       </c>
       <c r="D247" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7022,10 +6951,10 @@
         <v>PASS</v>
       </c>
       <c r="G247">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H247" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="248">
@@ -7036,7 +6965,7 @@
         <v>MOB-APP-247</v>
       </c>
       <c r="C248" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>AI Model Diagnostic Mobile Subsystem</v>
       </c>
       <c r="D248" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7048,10 +6977,10 @@
         <v>PASS</v>
       </c>
       <c r="G248">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H248" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="249">
@@ -7062,7 +6991,7 @@
         <v>MOB-APP-248</v>
       </c>
       <c r="C249" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Request Second Doctor Mobile Subsystem</v>
       </c>
       <c r="D249" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7074,10 +7003,10 @@
         <v>PASS</v>
       </c>
       <c r="G249">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H249" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="250">
@@ -7088,7 +7017,7 @@
         <v>MOB-APP-249</v>
       </c>
       <c r="C250" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>Scan Analysis Finished Mobile Subsystem</v>
       </c>
       <c r="D250" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7100,10 +7029,10 @@
         <v>PASS</v>
       </c>
       <c r="G250">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H250" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="251">
@@ -7114,7 +7043,7 @@
         <v>MOB-APP-250</v>
       </c>
       <c r="C251" t="str">
-        <v>Mobile Camera Dental Scan</v>
+        <v>3D Tooth Model Mobile Subsystem</v>
       </c>
       <c r="D251" t="str">
         <v>05_dental_scan.test.js</v>
@@ -7126,10 +7055,10 @@
         <v>PASS</v>
       </c>
       <c r="G251">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H251" t="str">
-        <v>2026-08-06T05:04:18.610Z</v>
+        <v>2026-08-06T05:06:54.433Z</v>
       </c>
     </row>
     <row r="252">
@@ -7140,7 +7069,7 @@
         <v>MOB-APP-251</v>
       </c>
       <c r="C252" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Education Hub Mobile Mobile Subsystem</v>
       </c>
       <c r="D252" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7152,10 +7081,10 @@
         <v>PASS</v>
       </c>
       <c r="G252">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="H252" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="253">
@@ -7166,7 +7095,7 @@
         <v>MOB-APP-252</v>
       </c>
       <c r="C253" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Category Filter Chips Mobile Subsystem</v>
       </c>
       <c r="D253" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7178,10 +7107,10 @@
         <v>PASS</v>
       </c>
       <c r="G253">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H253" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="254">
@@ -7192,7 +7121,7 @@
         <v>MOB-APP-253</v>
       </c>
       <c r="C254" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Pediatric Dental Care Mobile Subsystem</v>
       </c>
       <c r="D254" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7204,10 +7133,10 @@
         <v>PASS</v>
       </c>
       <c r="G254">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="H254" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="255">
@@ -7218,7 +7147,7 @@
         <v>MOB-APP-254</v>
       </c>
       <c r="C255" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Cosmetic Dental &amp; Mobile Subsystem</v>
       </c>
       <c r="D255" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7230,10 +7159,10 @@
         <v>PASS</v>
       </c>
       <c r="G255">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H255" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="256">
@@ -7244,7 +7173,7 @@
         <v>MOB-APP-255</v>
       </c>
       <c r="C256" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Periodontal Disease Care Mobile Subsystem</v>
       </c>
       <c r="D256" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7256,10 +7185,10 @@
         <v>PASS</v>
       </c>
       <c r="G256">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H256" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="257">
@@ -7270,7 +7199,7 @@
         <v>MOB-APP-256</v>
       </c>
       <c r="C257" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Article Estimated Read Mobile Subsystem</v>
       </c>
       <c r="D257" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7282,10 +7211,10 @@
         <v>PASS</v>
       </c>
       <c r="G257">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H257" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="258">
@@ -7296,7 +7225,7 @@
         <v>MOB-APP-257</v>
       </c>
       <c r="C258" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Bookmark Article Saved Mobile Subsystem</v>
       </c>
       <c r="D258" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7308,10 +7237,10 @@
         <v>PASS</v>
       </c>
       <c r="G258">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="H258" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="259">
@@ -7322,7 +7251,7 @@
         <v>MOB-APP-258</v>
       </c>
       <c r="C259" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Remove Saved Bookmark Mobile Subsystem</v>
       </c>
       <c r="D259" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7334,10 +7263,10 @@
         <v>PASS</v>
       </c>
       <c r="G259">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H259" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="260">
@@ -7348,7 +7277,7 @@
         <v>MOB-APP-259</v>
       </c>
       <c r="C260" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Share Article Via Mobile Subsystem</v>
       </c>
       <c r="D260" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7360,10 +7289,10 @@
         <v>PASS</v>
       </c>
       <c r="G260">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H260" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="261">
@@ -7374,7 +7303,7 @@
         <v>MOB-APP-260</v>
       </c>
       <c r="C261" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Text-to-Speech Native Audio Mobile Subsystem</v>
       </c>
       <c r="D261" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7386,10 +7315,10 @@
         <v>PASS</v>
       </c>
       <c r="G261">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H261" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="262">
@@ -7400,7 +7329,7 @@
         <v>MOB-APP-261</v>
       </c>
       <c r="C262" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Video Tutorial In-App Mobile Subsystem</v>
       </c>
       <c r="D262" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7412,10 +7341,10 @@
         <v>PASS</v>
       </c>
       <c r="G262">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H262" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="263">
@@ -7426,7 +7355,7 @@
         <v>MOB-APP-262</v>
       </c>
       <c r="C263" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Video Full-Screen Landscape Mobile Subsystem</v>
       </c>
       <c r="D263" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7438,10 +7367,10 @@
         <v>PASS</v>
       </c>
       <c r="G263">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H263" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="264">
@@ -7452,7 +7381,7 @@
         <v>MOB-APP-263</v>
       </c>
       <c r="C264" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Interactive Dental Hygiene Mobile Subsystem</v>
       </c>
       <c r="D264" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7464,10 +7393,10 @@
         <v>PASS</v>
       </c>
       <c r="G264">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H264" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="265">
@@ -7478,7 +7407,7 @@
         <v>MOB-APP-264</v>
       </c>
       <c r="C265" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Quiz Score Results Mobile Subsystem</v>
       </c>
       <c r="D265" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7490,10 +7419,10 @@
         <v>PASS</v>
       </c>
       <c r="G265">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H265" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="266">
@@ -7504,7 +7433,7 @@
         <v>MOB-APP-265</v>
       </c>
       <c r="C266" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Daily Dental Care Mobile Subsystem</v>
       </c>
       <c r="D266" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7516,10 +7445,10 @@
         <v>PASS</v>
       </c>
       <c r="G266">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H266" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="267">
@@ -7530,7 +7459,7 @@
         <v>MOB-APP-266</v>
       </c>
       <c r="C267" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Download Care Infographic Mobile Subsystem</v>
       </c>
       <c r="D267" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7542,10 +7471,10 @@
         <v>PASS</v>
       </c>
       <c r="G267">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H267" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="268">
@@ -7556,7 +7485,7 @@
         <v>MOB-APP-267</v>
       </c>
       <c r="C268" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Doctor Mobile Analytics Mobile Subsystem</v>
       </c>
       <c r="D268" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7568,10 +7497,10 @@
         <v>PASS</v>
       </c>
       <c r="G268">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H268" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="269">
@@ -7582,7 +7511,7 @@
         <v>MOB-APP-268</v>
       </c>
       <c r="C269" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Doctor Mobile Analytics Mobile Subsystem</v>
       </c>
       <c r="D269" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7594,10 +7523,10 @@
         <v>PASS</v>
       </c>
       <c r="G269">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H269" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="270">
@@ -7608,7 +7537,7 @@
         <v>MOB-APP-269</v>
       </c>
       <c r="C270" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Doctor Mobile Analytics Mobile Subsystem</v>
       </c>
       <c r="D270" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7620,10 +7549,10 @@
         <v>PASS</v>
       </c>
       <c r="G270">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H270" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="271">
@@ -7634,7 +7563,7 @@
         <v>MOB-APP-270</v>
       </c>
       <c r="C271" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Doctor Mobile Analytics Mobile Subsystem</v>
       </c>
       <c r="D271" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7646,10 +7575,10 @@
         <v>PASS</v>
       </c>
       <c r="G271">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H271" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="272">
@@ -7660,7 +7589,7 @@
         <v>MOB-APP-271</v>
       </c>
       <c r="C272" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Filter Analytics Date Mobile Subsystem</v>
       </c>
       <c r="D272" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7672,10 +7601,10 @@
         <v>PASS</v>
       </c>
       <c r="G272">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H272" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="273">
@@ -7686,7 +7615,7 @@
         <v>MOB-APP-272</v>
       </c>
       <c r="C273" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Filter Analytics Date Mobile Subsystem</v>
       </c>
       <c r="D273" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7698,10 +7627,10 @@
         <v>PASS</v>
       </c>
       <c r="G273">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H273" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="274">
@@ -7712,7 +7641,7 @@
         <v>MOB-APP-273</v>
       </c>
       <c r="C274" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Export Mobile Analytics Mobile Subsystem</v>
       </c>
       <c r="D274" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7724,10 +7653,10 @@
         <v>PASS</v>
       </c>
       <c r="G274">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H274" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="275">
@@ -7738,7 +7667,7 @@
         <v>MOB-APP-274</v>
       </c>
       <c r="C275" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Export Analytics Chart Mobile Subsystem</v>
       </c>
       <c r="D275" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7750,10 +7679,10 @@
         <v>PASS</v>
       </c>
       <c r="G275">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H275" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="276">
@@ -7764,7 +7693,7 @@
         <v>MOB-APP-275</v>
       </c>
       <c r="C276" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Clinic Key Performance Mobile Subsystem</v>
       </c>
       <c r="D276" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7776,10 +7705,10 @@
         <v>PASS</v>
       </c>
       <c r="G276">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H276" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="277">
@@ -7790,7 +7719,7 @@
         <v>MOB-APP-276</v>
       </c>
       <c r="C277" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Patient Age Demographic Mobile Subsystem</v>
       </c>
       <c r="D277" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7802,10 +7731,10 @@
         <v>PASS</v>
       </c>
       <c r="G277">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H277" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="278">
@@ -7816,7 +7745,7 @@
         <v>MOB-APP-277</v>
       </c>
       <c r="C278" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Revenue Performance Native Mobile Subsystem</v>
       </c>
       <c r="D278" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7828,10 +7757,10 @@
         <v>PASS</v>
       </c>
       <c r="G278">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H278" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="279">
@@ -7842,7 +7771,7 @@
         <v>MOB-APP-278</v>
       </c>
       <c r="C279" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Weekly No-Show Trends Mobile Subsystem</v>
       </c>
       <c r="D279" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7854,10 +7783,10 @@
         <v>PASS</v>
       </c>
       <c r="G279">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H279" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="280">
@@ -7868,7 +7797,7 @@
         <v>MOB-APP-279</v>
       </c>
       <c r="C280" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Mobile Patient Portal Mobile Subsystem</v>
       </c>
       <c r="D280" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7880,10 +7809,10 @@
         <v>PASS</v>
       </c>
       <c r="G280">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H280" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="281">
@@ -7894,7 +7823,7 @@
         <v>MOB-APP-280</v>
       </c>
       <c r="C281" t="str">
-        <v>Mobile Education Hub</v>
+        <v>High Risk Patient Mobile Subsystem</v>
       </c>
       <c r="D281" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7906,10 +7835,10 @@
         <v>PASS</v>
       </c>
       <c r="G281">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H281" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="282">
@@ -7920,7 +7849,7 @@
         <v>MOB-APP-281</v>
       </c>
       <c r="C282" t="str">
-        <v>Mobile Education Hub</v>
+        <v>System Activity Audit Mobile Subsystem</v>
       </c>
       <c r="D282" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7932,10 +7861,10 @@
         <v>PASS</v>
       </c>
       <c r="G282">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H282" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="283">
@@ -7946,7 +7875,7 @@
         <v>MOB-APP-282</v>
       </c>
       <c r="C283" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Filter Audit Logs Mobile Subsystem</v>
       </c>
       <c r="D283" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7958,10 +7887,10 @@
         <v>PASS</v>
       </c>
       <c r="G283">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H283" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="284">
@@ -7972,7 +7901,7 @@
         <v>MOB-APP-283</v>
       </c>
       <c r="C284" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Export Mobile Audit Mobile Subsystem</v>
       </c>
       <c r="D284" t="str">
         <v>06_education_analytics.test.js</v>
@@ -7984,10 +7913,10 @@
         <v>PASS</v>
       </c>
       <c r="G284">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H284" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="285">
@@ -7998,7 +7927,7 @@
         <v>MOB-APP-284</v>
       </c>
       <c r="C285" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Mobile Notification Center Mobile Subsystem</v>
       </c>
       <c r="D285" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8010,10 +7939,10 @@
         <v>PASS</v>
       </c>
       <c r="G285">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H285" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="286">
@@ -8024,7 +7953,7 @@
         <v>MOB-APP-285</v>
       </c>
       <c r="C286" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Notification Push Preference Mobile Subsystem</v>
       </c>
       <c r="D286" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8036,10 +7965,10 @@
         <v>PASS</v>
       </c>
       <c r="G286">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H286" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="287">
@@ -8050,7 +7979,7 @@
         <v>MOB-APP-286</v>
       </c>
       <c r="C287" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Email Notification Frequency Mobile Subsystem</v>
       </c>
       <c r="D287" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8065,7 +7994,7 @@
         <v>19</v>
       </c>
       <c r="H287" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="288">
@@ -8076,7 +8005,7 @@
         <v>MOB-APP-287</v>
       </c>
       <c r="C288" t="str">
-        <v>Mobile Education Hub</v>
+        <v>SMS Notification Preferences Mobile Subsystem</v>
       </c>
       <c r="D288" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8088,10 +8017,10 @@
         <v>PASS</v>
       </c>
       <c r="G288">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H288" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="289">
@@ -8102,7 +8031,7 @@
         <v>MOB-APP-288</v>
       </c>
       <c r="C289" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Push Notification Channel Mobile Subsystem</v>
       </c>
       <c r="D289" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8114,10 +8043,10 @@
         <v>PASS</v>
       </c>
       <c r="G289">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H289" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="290">
@@ -8128,7 +8057,7 @@
         <v>MOB-APP-289</v>
       </c>
       <c r="C290" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Mobile App Dark Mobile Subsystem</v>
       </c>
       <c r="D290" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8140,10 +8069,10 @@
         <v>PASS</v>
       </c>
       <c r="G290">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H290" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="291">
@@ -8154,7 +8083,7 @@
         <v>MOB-APP-290</v>
       </c>
       <c r="C291" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Mobile App Light Mobile Subsystem</v>
       </c>
       <c r="D291" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8166,10 +8095,10 @@
         <v>PASS</v>
       </c>
       <c r="G291">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H291" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="292">
@@ -8180,7 +8109,7 @@
         <v>MOB-APP-291</v>
       </c>
       <c r="C292" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Device System Theme Mobile Subsystem</v>
       </c>
       <c r="D292" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8192,10 +8121,10 @@
         <v>PASS</v>
       </c>
       <c r="G292">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H292" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="293">
@@ -8206,7 +8135,7 @@
         <v>MOB-APP-292</v>
       </c>
       <c r="C293" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Accessibility Font Size Mobile Subsystem</v>
       </c>
       <c r="D293" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8218,10 +8147,10 @@
         <v>PASS</v>
       </c>
       <c r="G293">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H293" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="294">
@@ -8232,7 +8161,7 @@
         <v>MOB-APP-293</v>
       </c>
       <c r="C294" t="str">
-        <v>Mobile Education Hub</v>
+        <v>High Contrast Theme Mobile Subsystem</v>
       </c>
       <c r="D294" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8244,10 +8173,10 @@
         <v>PASS</v>
       </c>
       <c r="G294">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H294" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="295">
@@ -8258,7 +8187,7 @@
         <v>MOB-APP-294</v>
       </c>
       <c r="C295" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Screen Reader Accessibility Mobile Subsystem</v>
       </c>
       <c r="D295" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8270,10 +8199,10 @@
         <v>PASS</v>
       </c>
       <c r="G295">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H295" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="296">
@@ -8284,7 +8213,7 @@
         <v>MOB-APP-295</v>
       </c>
       <c r="C296" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Keypad Tab Focus Mobile Subsystem</v>
       </c>
       <c r="D296" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8296,10 +8225,10 @@
         <v>PASS</v>
       </c>
       <c r="G296">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H296" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="297">
@@ -8310,7 +8239,7 @@
         <v>MOB-APP-296</v>
       </c>
       <c r="C297" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Accessibility Skip-to-Content Focus Mobile Subsystem</v>
       </c>
       <c r="D297" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8322,10 +8251,10 @@
         <v>PASS</v>
       </c>
       <c r="G297">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H297" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="298">
@@ -8336,7 +8265,7 @@
         <v>MOB-APP-297</v>
       </c>
       <c r="C298" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Footer Privacy Policy Mobile Subsystem</v>
       </c>
       <c r="D298" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8348,10 +8277,10 @@
         <v>PASS</v>
       </c>
       <c r="G298">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H298" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="299">
@@ -8362,7 +8291,7 @@
         <v>MOB-APP-298</v>
       </c>
       <c r="C299" t="str">
-        <v>Mobile Education Hub</v>
+        <v>System Server Status Mobile Subsystem</v>
       </c>
       <c r="D299" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8374,10 +8303,10 @@
         <v>PASS</v>
       </c>
       <c r="G299">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H299" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="300">
@@ -8388,7 +8317,7 @@
         <v>MOB-APP-299</v>
       </c>
       <c r="C300" t="str">
-        <v>Mobile Education Hub</v>
+        <v>Feedback Rating Star Mobile Subsystem</v>
       </c>
       <c r="D300" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8400,10 +8329,10 @@
         <v>PASS</v>
       </c>
       <c r="G300">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H300" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
     <row r="301">
@@ -8414,7 +8343,7 @@
         <v>MOB-APP-300</v>
       </c>
       <c r="C301" t="str">
-        <v>Mobile Education Hub</v>
+        <v>App Version &amp; Mobile Subsystem</v>
       </c>
       <c r="D301" t="str">
         <v>06_education_analytics.test.js</v>
@@ -8426,10 +8355,10 @@
         <v>PASS</v>
       </c>
       <c r="G301">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H301" t="str">
-        <v>2026-08-06T05:04:18.615Z</v>
+        <v>2026-08-06T05:06:54.437Z</v>
       </c>
     </row>
   </sheetData>
